--- a/research/traditional_assets/database/data/norway/norway_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_metals_mining.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -581,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -596,40 +596,40 @@
         <v>0.5570000000000001</v>
       </c>
       <c r="G2">
-        <v>0.2613045822102426</v>
+        <v>0.2610587460345689</v>
       </c>
       <c r="H2">
-        <v>0.2562264150943396</v>
+        <v>0.2559805791924216</v>
       </c>
       <c r="I2">
-        <v>0.1950512129380054</v>
+        <v>0.1947644099857461</v>
       </c>
       <c r="J2">
-        <v>0.09752560646900268</v>
+        <v>0.1623036749881217</v>
       </c>
       <c r="K2">
-        <v>127.3</v>
+        <v>125.402</v>
       </c>
       <c r="L2">
-        <v>0.006862533692722372</v>
+        <v>0.006760215268991091</v>
       </c>
       <c r="M2">
         <v>677.2</v>
       </c>
       <c r="N2">
-        <v>0.06193864671556881</v>
+        <v>0.06050291034008318</v>
       </c>
       <c r="O2">
-        <v>5.319717203456403</v>
+        <v>5.4002328511507</v>
       </c>
       <c r="P2">
         <v>476.3</v>
       </c>
       <c r="Q2">
-        <v>0.04356375875756855</v>
+        <v>0.042553951853192</v>
       </c>
       <c r="R2">
-        <v>3.741555380989788</v>
+        <v>3.798185036921261</v>
       </c>
       <c r="S2">
         <v>200.9</v>
@@ -638,73 +638,73 @@
         <v>0.2966627288836385</v>
       </c>
       <c r="U2">
-        <v>1792.5</v>
+        <v>1848.639</v>
       </c>
       <c r="V2">
-        <v>0.1639471710538351</v>
+        <v>0.1651624921266701</v>
       </c>
       <c r="W2">
-        <v>0.01317246303328815</v>
+        <v>-0.0008339222614840989</v>
       </c>
       <c r="X2">
-        <v>0.09936469487924454</v>
+        <v>0.09933025754290266</v>
       </c>
       <c r="Y2">
-        <v>-0.0861922318459564</v>
+        <v>-0.1001641798043868</v>
       </c>
       <c r="Z2">
-        <v>1.653165075885178</v>
+        <v>1.624810015486059</v>
       </c>
       <c r="AA2">
-        <v>0.1612259266190769</v>
+        <v>-0.01807967313585291</v>
       </c>
       <c r="AB2">
-        <v>0.08594832206794273</v>
+        <v>0.08592239648967651</v>
       </c>
       <c r="AC2">
-        <v>0.07527760455113414</v>
+        <v>-0.102779460024559</v>
       </c>
       <c r="AD2">
-        <v>3589.6</v>
+        <v>3738.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3589.6</v>
+        <v>3738.4</v>
       </c>
       <c r="AG2">
-        <v>1797.1</v>
+        <v>1889.761</v>
       </c>
       <c r="AH2">
-        <v>0.2471665633822213</v>
+        <v>0.2503742151527836</v>
       </c>
       <c r="AI2">
-        <v>0.2637782546074484</v>
+        <v>0.2689365417238311</v>
       </c>
       <c r="AJ2">
-        <v>0.1411649188955658</v>
+        <v>0.1444483062287796</v>
       </c>
       <c r="AK2">
-        <v>0.1520916730845725</v>
+        <v>0.1568001196146245</v>
       </c>
       <c r="AL2">
         <v>252.6</v>
       </c>
       <c r="AM2">
-        <v>114.8</v>
+        <v>110.62</v>
       </c>
       <c r="AN2">
-        <v>0.7865030674846626</v>
+        <v>0.8197220961414912</v>
       </c>
       <c r="AO2">
-        <v>14.32383214568488</v>
+        <v>14.3027711797308</v>
       </c>
       <c r="AP2">
-        <v>0.3937554776511831</v>
+        <v>0.4143694757453565</v>
       </c>
       <c r="AQ2">
-        <v>31.51742160278746</v>
+        <v>32.66027843066354</v>
       </c>
     </row>
     <row r="3">
@@ -781,10 +781,10 @@
         <v>0.01317246303328815</v>
       </c>
       <c r="X3">
-        <v>0.09936469487924454</v>
+        <v>0.09933025754290266</v>
       </c>
       <c r="Y3">
-        <v>-0.0861922318459564</v>
+        <v>-0.08615779450961451</v>
       </c>
       <c r="Z3">
         <v>1.653165075885178</v>
@@ -793,10 +793,10 @@
         <v>0.1612259266190769</v>
       </c>
       <c r="AB3">
-        <v>0.08594832206794273</v>
+        <v>0.08592239648967651</v>
       </c>
       <c r="AC3">
-        <v>0.07527760455113414</v>
+        <v>0.07530353012940036</v>
       </c>
       <c r="AD3">
         <v>3589.6</v>
@@ -839,6 +839,226 @@
       </c>
       <c r="AQ3">
         <v>31.51742160278746</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Nordic Mining ASA (OB:NOM)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+      <c r="K4">
+        <v>-0.118</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>55.7</v>
+      </c>
+      <c r="V4">
+        <v>0.2182601880877743</v>
+      </c>
+      <c r="W4">
+        <v>-0.0008339222614840989</v>
+      </c>
+      <c r="X4">
+        <v>0.1077986469554753</v>
+      </c>
+      <c r="Y4">
+        <v>-0.1086325692169594</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>-0.01807967313585291</v>
+      </c>
+      <c r="AB4">
+        <v>0.08469978688870614</v>
+      </c>
+      <c r="AC4">
+        <v>-0.102779460024559</v>
+      </c>
+      <c r="AD4">
+        <v>148.8</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>148.8</v>
+      </c>
+      <c r="AG4">
+        <v>93.10000000000001</v>
+      </c>
+      <c r="AH4">
+        <v>0.3683168316831684</v>
+      </c>
+      <c r="AI4">
+        <v>0.5097636176772868</v>
+      </c>
+      <c r="AJ4">
+        <v>0.267298306057996</v>
+      </c>
+      <c r="AK4">
+        <v>0.3941574936494497</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>-4.18</v>
+      </c>
+      <c r="AN4">
+        <v>-43.38192419825073</v>
+      </c>
+      <c r="AP4">
+        <v>-27.14285714285714</v>
+      </c>
+      <c r="AQ4">
+        <v>0.8468899521531101</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Green Minerals AS (OB:GEM)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>-1780</v>
+      </c>
+      <c r="J5">
+        <v>-1780</v>
+      </c>
+      <c r="K5">
+        <v>-1.78</v>
+      </c>
+      <c r="L5">
+        <v>-1780</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0.439</v>
+      </c>
+      <c r="V5">
+        <v>0.1032941176470588</v>
+      </c>
+      <c r="W5">
+        <v>-1.358778625954199</v>
+      </c>
+      <c r="X5">
+        <v>0.08841672207118731</v>
+      </c>
+      <c r="Y5">
+        <v>-1.447195348025386</v>
+      </c>
+      <c r="Z5">
+        <v>0.04999999999999995</v>
+      </c>
+      <c r="AA5">
+        <v>-1</v>
+      </c>
+      <c r="AB5">
+        <v>0.08841672207118731</v>
+      </c>
+      <c r="AC5">
+        <v>-1.088416722071187</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>-0.439</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.1151928627656783</v>
+      </c>
+      <c r="AK5">
+        <v>7.080645161290323</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1133,7 +1353,7 @@
         <v>14.3238321456849</v>
       </c>
       <c r="F2">
-        <v>4.45402437604005</v>
+        <v>4.63448208556653</v>
       </c>
       <c r="G2">
         <v>0.786503067484663</v>
@@ -1151,13 +1371,13 @@
         <v>10933.4</v>
       </c>
       <c r="L2">
-        <v>786.532043904288</v>
+        <v>922.111338692681</v>
       </c>
       <c r="M2">
         <v>12730.5</v>
       </c>
       <c r="N2">
-        <v>13371.8020439043</v>
+        <v>13507.3813386927</v>
       </c>
       <c r="O2">
         <v>3589.6</v>
@@ -1166,16 +1386,16 @@
         <v>14377.77</v>
       </c>
       <c r="Q2">
-        <v>0.0859483220679427</v>
+        <v>0.08592239648967651</v>
       </c>
       <c r="R2">
-        <v>0.0774435451039631</v>
+        <v>0.07572326000408269</v>
       </c>
       <c r="S2">
         <v>0.045084</v>
       </c>
       <c r="T2">
-        <v>0.04407</v>
+        <v>0.042354</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1188,10 +1408,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.0993646948792445</v>
+        <v>0.0993302575429027</v>
       </c>
       <c r="X2">
-        <v>3.38142451039631</v>
+        <v>3.37928000040827</v>
       </c>
       <c r="Y2">
         <v>1.23626460838112</v>
@@ -1230,7 +1450,7 @@
         <v>10933.4</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.0433</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1638,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08844413846070455</v>
+        <v>0.08841672207118731</v>
       </c>
       <c r="C2">
-        <v>14346.31562866846</v>
+        <v>14346.41554537598</v>
       </c>
       <c r="D2">
-        <v>12553.81562866846</v>
+        <v>12553.91554537598</v>
       </c>
       <c r="E2">
         <v>-3589.6</v>
@@ -1469,19 +1689,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08844413846070455</v>
+        <v>0.08841672207118731</v>
       </c>
       <c r="T2">
         <v>0.9842199092652959</v>
       </c>
       <c r="U2">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.22</v>
       </c>
       <c r="W2">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1720,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08829558135609099</v>
+        <v>0.0882573052826307</v>
       </c>
       <c r="C3">
-        <v>14211.46493031141</v>
+        <v>14212.32470188606</v>
       </c>
       <c r="D3">
-        <v>12564.19493031141</v>
+        <v>12565.05470188606</v>
       </c>
       <c r="E3">
         <v>-3444.37</v>
@@ -1533,37 +1753,37 @@
         <v>3618.2</v>
       </c>
       <c r="M3">
-        <v>7.508391</v>
+        <v>7.305069</v>
       </c>
       <c r="N3">
-        <v>3610.691609</v>
+        <v>3610.894931</v>
       </c>
       <c r="O3">
-        <v>794.35215398</v>
+        <v>794.39688482</v>
       </c>
       <c r="P3">
-        <v>2816.33945502</v>
+        <v>2816.49804618</v>
       </c>
       <c r="Q3">
-        <v>3762.13945502</v>
+        <v>3762.29804618</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08878012258191009</v>
+        <v>0.08875249018447545</v>
       </c>
       <c r="T3">
         <v>0.991974369156477</v>
       </c>
       <c r="U3">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.22</v>
       </c>
       <c r="W3">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1791,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>481.8875308970989</v>
+        <v>495.2999075025848</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1802,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08814702425147745</v>
+        <v>0.08809788849407407</v>
       </c>
       <c r="C4">
-        <v>14076.63140904999</v>
+        <v>14078.25364361815</v>
       </c>
       <c r="D4">
-        <v>12574.59140904998</v>
+        <v>12576.21364361815</v>
       </c>
       <c r="E4">
         <v>-3299.14</v>
@@ -1615,37 +1835,37 @@
         <v>3618.2</v>
       </c>
       <c r="M4">
-        <v>15.016782</v>
+        <v>14.610138</v>
       </c>
       <c r="N4">
-        <v>3603.183218</v>
+        <v>3603.589862</v>
       </c>
       <c r="O4">
-        <v>792.7003079599999</v>
+        <v>792.7897696399999</v>
       </c>
       <c r="P4">
-        <v>2810.48291004</v>
+        <v>2810.80009236</v>
       </c>
       <c r="Q4">
-        <v>3756.282910039999</v>
+        <v>3756.60009236</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08912296352191576</v>
+        <v>0.08909511070823886</v>
       </c>
       <c r="T4">
         <v>0.9998870833311516</v>
       </c>
       <c r="U4">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.22</v>
       </c>
       <c r="W4">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +1873,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>240.9437654485495</v>
+        <v>247.6499537512924</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +1884,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08799846714686389</v>
+        <v>0.08793847170551748</v>
       </c>
       <c r="C5">
-        <v>13941.81510756002</v>
+        <v>13944.20242333249</v>
       </c>
       <c r="D5">
-        <v>12585.00510756002</v>
+        <v>12587.39242333249</v>
       </c>
       <c r="E5">
         <v>-3153.91</v>
@@ -1697,37 +1917,37 @@
         <v>3618.2</v>
       </c>
       <c r="M5">
-        <v>22.52517300000001</v>
+        <v>21.915207</v>
       </c>
       <c r="N5">
-        <v>3595.674827</v>
+        <v>3596.284793</v>
       </c>
       <c r="O5">
-        <v>791.0484619399999</v>
+        <v>791.18265446</v>
       </c>
       <c r="P5">
-        <v>2804.62636506</v>
+        <v>2805.10213854</v>
       </c>
       <c r="Q5">
-        <v>3750.42636506</v>
+        <v>3750.90213854</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.08947287334728238</v>
+        <v>0.08944479557269844</v>
       </c>
       <c r="T5">
         <v>1.007962946251696</v>
       </c>
       <c r="U5">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.22</v>
       </c>
       <c r="W5">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +1955,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>160.6291769656996</v>
+        <v>165.0999691675283</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +1966,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08784991004225033</v>
+        <v>0.08777905491696086</v>
       </c>
       <c r="C6">
-        <v>13807.01606865885</v>
+        <v>13810.17109397705</v>
       </c>
       <c r="D6">
-        <v>12595.43606865885</v>
+        <v>12598.59109397705</v>
       </c>
       <c r="E6">
         <v>-3008.68</v>
@@ -1779,37 +1999,37 @@
         <v>3618.2</v>
       </c>
       <c r="M6">
-        <v>30.033564</v>
+        <v>29.220276</v>
       </c>
       <c r="N6">
-        <v>3588.166436</v>
+        <v>3588.979724</v>
       </c>
       <c r="O6">
-        <v>789.39661592</v>
+        <v>789.5755392799999</v>
       </c>
       <c r="P6">
-        <v>2798.76982008</v>
+        <v>2799.40418472</v>
       </c>
       <c r="Q6">
-        <v>3744.56982008</v>
+        <v>3745.20418472</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08983007296067744</v>
+        <v>0.0898017655385009</v>
       </c>
       <c r="T6">
         <v>1.016207056316418</v>
       </c>
       <c r="U6">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.22</v>
       </c>
       <c r="W6">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +2037,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>120.4718827242747</v>
+        <v>123.8249768756462</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +2048,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.0877013529376368</v>
+        <v>0.08761963812840425</v>
       </c>
       <c r="C7">
-        <v>13672.23433530587</v>
+        <v>13676.15970868842</v>
       </c>
       <c r="D7">
-        <v>12605.88433530587</v>
+        <v>12609.80970868842</v>
       </c>
       <c r="E7">
         <v>-2863.45</v>
@@ -1861,37 +2081,37 @@
         <v>3618.2</v>
       </c>
       <c r="M7">
-        <v>37.54195500000001</v>
+        <v>36.52534500000001</v>
       </c>
       <c r="N7">
-        <v>3580.658045</v>
+        <v>3581.674655</v>
       </c>
       <c r="O7">
-        <v>787.7447698999999</v>
+        <v>787.9684241</v>
       </c>
       <c r="P7">
-        <v>2792.9132751</v>
+        <v>2793.7062309</v>
       </c>
       <c r="Q7">
-        <v>3738.7132751</v>
+        <v>3739.5062309</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.09019479256593348</v>
+        <v>0.09016625066147817</v>
       </c>
       <c r="T7">
         <v>1.024624726593029</v>
       </c>
       <c r="U7">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.22</v>
       </c>
       <c r="W7">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +2119,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>96.37750617941977</v>
+        <v>99.05998150051694</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +2130,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08755279583302324</v>
+        <v>0.08746022133984764</v>
       </c>
       <c r="C8">
-        <v>13537.46995060314</v>
+        <v>13542.16832079262</v>
       </c>
       <c r="D8">
-        <v>12616.34995060314</v>
+        <v>12621.04832079262</v>
       </c>
       <c r="E8">
         <v>-2718.22</v>
@@ -1943,37 +2163,37 @@
         <v>3618.2</v>
       </c>
       <c r="M8">
-        <v>45.05034600000001</v>
+        <v>43.830414</v>
       </c>
       <c r="N8">
-        <v>3573.149654</v>
+        <v>3574.369586</v>
       </c>
       <c r="O8">
-        <v>786.0929238799999</v>
+        <v>786.3613089199999</v>
       </c>
       <c r="P8">
-        <v>2787.05673012</v>
+        <v>2788.00827708</v>
       </c>
       <c r="Q8">
-        <v>3732.85673012</v>
+        <v>3733.80827708</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.09056727216279069</v>
+        <v>0.09053849078707196</v>
       </c>
       <c r="T8">
         <v>1.033221496237228</v>
       </c>
       <c r="U8">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.22</v>
       </c>
       <c r="W8">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +2201,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>80.31458848284981</v>
+        <v>82.54998458376413</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +2212,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08740423872840969</v>
+        <v>0.08730080455129102</v>
       </c>
       <c r="C9">
-        <v>13402.72295779599</v>
+        <v>13408.19698380593</v>
       </c>
       <c r="D9">
-        <v>12626.83295779599</v>
+        <v>12632.30698380593</v>
       </c>
       <c r="E9">
         <v>-2572.99</v>
@@ -2025,37 +2245,37 @@
         <v>3618.2</v>
       </c>
       <c r="M9">
-        <v>52.55873700000001</v>
+        <v>51.13548300000001</v>
       </c>
       <c r="N9">
-        <v>3565.641263</v>
+        <v>3567.064517</v>
       </c>
       <c r="O9">
-        <v>784.44107786</v>
+        <v>784.75419374</v>
       </c>
       <c r="P9">
-        <v>2781.20018514</v>
+        <v>2782.31032326</v>
       </c>
       <c r="Q9">
-        <v>3727.00018514</v>
+        <v>3728.11032326</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.09094776207355881</v>
+        <v>0.09091873607665701</v>
       </c>
       <c r="T9">
         <v>1.042003142647968</v>
       </c>
       <c r="U9">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.22</v>
       </c>
       <c r="W9">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2283,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>68.84107584244269</v>
+        <v>70.75712964322639</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2294,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08725568162379616</v>
+        <v>0.08714138776273442</v>
       </c>
       <c r="C10">
-        <v>13267.99340027358</v>
+        <v>13274.24575143578</v>
       </c>
       <c r="D10">
-        <v>12637.33340027358</v>
+        <v>12643.58575143578</v>
       </c>
       <c r="E10">
         <v>-2427.76</v>
@@ -2107,37 +2327,37 @@
         <v>3618.2</v>
       </c>
       <c r="M10">
-        <v>60.067128</v>
+        <v>58.440552</v>
       </c>
       <c r="N10">
-        <v>3558.132872</v>
+        <v>3559.759448</v>
       </c>
       <c r="O10">
-        <v>782.78923184</v>
+        <v>783.14707856</v>
       </c>
       <c r="P10">
-        <v>2775.34364016</v>
+        <v>2776.61236944</v>
       </c>
       <c r="Q10">
-        <v>3721.143640159999</v>
+        <v>3722.41236944</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.09133652350412624</v>
+        <v>0.09130724756818959</v>
       </c>
       <c r="T10">
         <v>1.050975694415464</v>
       </c>
       <c r="U10">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.22</v>
       </c>
       <c r="W10">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2365,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>60.23594136213737</v>
+        <v>61.9124884378231</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2376,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08710712451918261</v>
+        <v>0.08698197097417781</v>
       </c>
       <c r="C11">
-        <v>13133.28132156954</v>
+        <v>13140.31467758158</v>
       </c>
       <c r="D11">
-        <v>12647.85132156954</v>
+        <v>12654.88467758158</v>
       </c>
       <c r="E11">
         <v>-2282.53</v>
@@ -2189,37 +2409,37 @@
         <v>3618.2</v>
       </c>
       <c r="M11">
-        <v>67.57551900000001</v>
+        <v>65.745621</v>
       </c>
       <c r="N11">
-        <v>3550.624481</v>
+        <v>3552.454379</v>
       </c>
       <c r="O11">
-        <v>781.13738582</v>
+        <v>781.5399633799999</v>
       </c>
       <c r="P11">
-        <v>2769.48709518</v>
+        <v>2770.91441562</v>
       </c>
       <c r="Q11">
-        <v>3715.28709518</v>
+        <v>3716.71441562</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.09173382914195891</v>
+        <v>0.09170429777382176</v>
       </c>
       <c r="T11">
         <v>1.060145445122904</v>
       </c>
       <c r="U11">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V11">
         <v>0.22</v>
       </c>
       <c r="W11">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2447,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>53.54305898856654</v>
+        <v>55.03332305584276</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2458,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08695856741456905</v>
+        <v>0.08682255418562121</v>
       </c>
       <c r="C12">
-        <v>12998.58676536254</v>
+        <v>13006.40381633555</v>
       </c>
       <c r="D12">
-        <v>12658.38676536254</v>
+        <v>12666.20381633556</v>
       </c>
       <c r="E12">
         <v>-2137.3</v>
@@ -2271,37 +2491,37 @@
         <v>3618.2</v>
       </c>
       <c r="M12">
-        <v>75.08391000000002</v>
+        <v>73.05069000000002</v>
       </c>
       <c r="N12">
-        <v>3543.11609</v>
+        <v>3545.14931</v>
       </c>
       <c r="O12">
-        <v>779.4855398</v>
+        <v>779.9328482</v>
       </c>
       <c r="P12">
-        <v>2763.6305502</v>
+        <v>2765.2164618</v>
       </c>
       <c r="Q12">
-        <v>3709.4305502</v>
+        <v>3711.0164618</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.09213996379396561</v>
+        <v>0.09211017131735688</v>
       </c>
       <c r="T12">
         <v>1.069518968068288</v>
       </c>
       <c r="U12">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V12">
         <v>0.22</v>
       </c>
       <c r="W12">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2529,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>48.18875308970989</v>
+        <v>49.52999075025847</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2540,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08681001030995551</v>
+        <v>0.08666313739706458</v>
       </c>
       <c r="C13">
-        <v>12863.90977547689</v>
+        <v>12872.51322198367</v>
       </c>
       <c r="D13">
-        <v>12668.93977547689</v>
+        <v>12677.54322198367</v>
       </c>
       <c r="E13">
         <v>-1992.07</v>
@@ -2353,37 +2573,37 @@
         <v>3618.2</v>
       </c>
       <c r="M13">
-        <v>82.59230100000002</v>
+        <v>80.35575900000001</v>
       </c>
       <c r="N13">
-        <v>3535.607699</v>
+        <v>3537.844241</v>
       </c>
       <c r="O13">
-        <v>777.83369378</v>
+        <v>778.3257330199999</v>
       </c>
       <c r="P13">
-        <v>2757.77400522</v>
+        <v>2759.51850798</v>
       </c>
       <c r="Q13">
-        <v>3703.57400522</v>
+        <v>3705.31850798</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.09255522506736574</v>
+        <v>0.0925251656146793</v>
       </c>
       <c r="T13">
         <v>1.079103131978737</v>
       </c>
       <c r="U13">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V13">
         <v>0.22</v>
       </c>
       <c r="W13">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2611,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>43.80795735428171</v>
+        <v>45.0272643184168</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2622,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08666145320534195</v>
+        <v>0.08650372060850796</v>
       </c>
       <c r="C14">
-        <v>12729.25039588319</v>
+        <v>12738.64294900644</v>
       </c>
       <c r="D14">
-        <v>12679.51039588319</v>
+        <v>12688.90294900644</v>
       </c>
       <c r="E14">
         <v>-1846.84</v>
@@ -2435,37 +2655,37 @@
         <v>3618.2</v>
       </c>
       <c r="M14">
-        <v>90.10069200000002</v>
+        <v>87.66082800000001</v>
       </c>
       <c r="N14">
-        <v>3528.099308</v>
+        <v>3530.539172</v>
       </c>
       <c r="O14">
-        <v>776.18184776</v>
+        <v>776.71861784</v>
       </c>
       <c r="P14">
-        <v>2751.91746024</v>
+        <v>2753.82055416</v>
       </c>
       <c r="Q14">
-        <v>3697.71746024</v>
+        <v>3699.62055416</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.09297992409697949</v>
+        <v>0.09294959160057722</v>
       </c>
       <c r="T14">
         <v>1.088905117796241</v>
       </c>
       <c r="U14">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V14">
         <v>0.22</v>
       </c>
       <c r="W14">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2693,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>40.15729424142491</v>
+        <v>41.27499229188206</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2704,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.0865128961007284</v>
+        <v>0.08634430381995135</v>
       </c>
       <c r="C15">
-        <v>12594.6086706989</v>
+        <v>12604.79305207983</v>
       </c>
       <c r="D15">
-        <v>12690.0986706989</v>
+        <v>12700.28305207983</v>
       </c>
       <c r="E15">
         <v>-1701.61</v>
@@ -2517,37 +2737,37 @@
         <v>3618.2</v>
       </c>
       <c r="M15">
-        <v>97.60908300000001</v>
+        <v>94.96589700000001</v>
       </c>
       <c r="N15">
-        <v>3520.590917</v>
+        <v>3523.234103</v>
       </c>
       <c r="O15">
-        <v>774.53000174</v>
+        <v>775.1115026599999</v>
       </c>
       <c r="P15">
-        <v>2746.06091526</v>
+        <v>2748.12260034</v>
       </c>
       <c r="Q15">
-        <v>3691.86091526</v>
+        <v>3693.92260034</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.09341438632267632</v>
+        <v>0.09338377450569121</v>
       </c>
       <c r="T15">
         <v>1.098932436621044</v>
       </c>
       <c r="U15">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V15">
         <v>0.22</v>
       </c>
       <c r="W15">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2775,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>37.06827160746915</v>
+        <v>38.09999288481421</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2786,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.08636433899611486</v>
+        <v>0.08618488703139474</v>
       </c>
       <c r="C16">
-        <v>12459.98464418897</v>
+        <v>12470.96358607613</v>
       </c>
       <c r="D16">
-        <v>12700.70464418897</v>
+        <v>12711.68358607613</v>
       </c>
       <c r="E16">
         <v>-1556.38</v>
@@ -2599,37 +2819,37 @@
         <v>3618.2</v>
       </c>
       <c r="M16">
-        <v>105.117474</v>
+        <v>102.270966</v>
       </c>
       <c r="N16">
-        <v>3513.082526</v>
+        <v>3515.929034</v>
       </c>
       <c r="O16">
-        <v>772.8781557199999</v>
+        <v>773.50438748</v>
       </c>
       <c r="P16">
-        <v>2740.20437028</v>
+        <v>2742.42464652</v>
       </c>
       <c r="Q16">
-        <v>3686.004370279999</v>
+        <v>3688.22464652</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.09385895232106378</v>
+        <v>0.09382805468766831</v>
       </c>
       <c r="T16">
         <v>1.109192948906889</v>
       </c>
       <c r="U16">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V16">
         <v>0.22</v>
       </c>
       <c r="W16">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2857,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>34.42053792122135</v>
+        <v>35.3785648216132</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +2868,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08621578189150128</v>
+        <v>0.08602547024283813</v>
       </c>
       <c r="C17">
-        <v>12325.37836076647</v>
+        <v>12337.15460606483</v>
       </c>
       <c r="D17">
-        <v>12711.32836076647</v>
+        <v>12723.10460606482</v>
       </c>
       <c r="E17">
         <v>-1411.15</v>
@@ -2681,37 +2901,37 @@
         <v>3618.2</v>
       </c>
       <c r="M17">
-        <v>112.625865</v>
+        <v>109.576035</v>
       </c>
       <c r="N17">
-        <v>3505.574135</v>
+        <v>3508.623965</v>
       </c>
       <c r="O17">
-        <v>771.2263097</v>
+        <v>771.8972722999999</v>
       </c>
       <c r="P17">
-        <v>2734.3478253</v>
+        <v>2736.7266927</v>
       </c>
       <c r="Q17">
-        <v>3680.1478253</v>
+        <v>3682.5266927</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.09431397869588387</v>
+        <v>0.09428278852098604</v>
       </c>
       <c r="T17">
         <v>1.119694885011225</v>
       </c>
       <c r="U17">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V17">
         <v>0.22</v>
       </c>
       <c r="W17">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2939,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>32.12583539313992</v>
+        <v>33.01999383350565</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +2950,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08606722478688775</v>
+        <v>0.08586605345428151</v>
       </c>
       <c r="C18">
-        <v>12190.78986499316</v>
+        <v>12203.3661673135</v>
       </c>
       <c r="D18">
-        <v>12721.96986499316</v>
+        <v>12734.5461673135</v>
       </c>
       <c r="E18">
         <v>-1265.92</v>
@@ -2763,37 +2983,37 @@
         <v>3618.2</v>
       </c>
       <c r="M18">
-        <v>120.134256</v>
+        <v>116.881104</v>
       </c>
       <c r="N18">
-        <v>3498.065744</v>
+        <v>3501.318896</v>
       </c>
       <c r="O18">
-        <v>769.57446368</v>
+        <v>770.29015712</v>
       </c>
       <c r="P18">
-        <v>2728.49128032</v>
+        <v>2731.02873888</v>
       </c>
       <c r="Q18">
-        <v>3674.29128032</v>
+        <v>3676.82873888</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.09477983903200923</v>
+        <v>0.09474834935033515</v>
       </c>
       <c r="T18">
         <v>1.130446867213283</v>
       </c>
       <c r="U18">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V18">
         <v>0.22</v>
       </c>
       <c r="W18">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +3021,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>30.11797068106868</v>
+        <v>30.95624421891155</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +3032,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.0859186676822742</v>
+        <v>0.08570663666572489</v>
       </c>
       <c r="C19">
-        <v>12056.21920158017</v>
+        <v>12069.59832528871</v>
       </c>
       <c r="D19">
-        <v>12732.62920158017</v>
+        <v>12746.00832528871</v>
       </c>
       <c r="E19">
         <v>-1120.69</v>
@@ -2845,37 +3065,37 @@
         <v>3618.2</v>
       </c>
       <c r="M19">
-        <v>127.642647</v>
+        <v>124.186173</v>
       </c>
       <c r="N19">
-        <v>3490.557353</v>
+        <v>3494.013827</v>
       </c>
       <c r="O19">
-        <v>767.9226176599999</v>
+        <v>768.68304194</v>
       </c>
       <c r="P19">
-        <v>2722.63473534</v>
+        <v>2725.33078506</v>
       </c>
       <c r="Q19">
-        <v>3668.43473534</v>
+        <v>3671.13078506</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.09525692491840265</v>
+        <v>0.09522512851292157</v>
       </c>
       <c r="T19">
         <v>1.141457933323824</v>
       </c>
       <c r="U19">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V19">
         <v>0.22</v>
       </c>
       <c r="W19">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +3103,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>28.34632534688816</v>
+        <v>29.13528867662263</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +3114,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08577011057766065</v>
+        <v>0.0855472198771683</v>
       </c>
       <c r="C20">
-        <v>11921.66641538862</v>
+        <v>11935.85113565691</v>
       </c>
       <c r="D20">
-        <v>12743.30641538862</v>
+        <v>12757.49113565691</v>
       </c>
       <c r="E20">
         <v>-975.46</v>
@@ -2927,37 +3147,37 @@
         <v>3618.2</v>
       </c>
       <c r="M20">
-        <v>135.151038</v>
+        <v>131.491242</v>
       </c>
       <c r="N20">
-        <v>3483.048962</v>
+        <v>3486.708758</v>
       </c>
       <c r="O20">
-        <v>766.27077164</v>
+        <v>767.0759267599999</v>
       </c>
       <c r="P20">
-        <v>2716.77819036</v>
+        <v>2719.63283124</v>
       </c>
       <c r="Q20">
-        <v>3662.57819036</v>
+        <v>3665.43283124</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.09574564704592761</v>
+        <v>0.09571353643557109</v>
       </c>
       <c r="T20">
         <v>1.152737562022427</v>
       </c>
       <c r="U20">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V20">
         <v>0.22</v>
       </c>
       <c r="W20">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +3185,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>26.77152949428327</v>
+        <v>27.51666152792138</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +3196,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.0856215534730471</v>
+        <v>0.08538780308861169</v>
       </c>
       <c r="C21">
-        <v>11787.1315514302</v>
+        <v>11802.1246542853</v>
       </c>
       <c r="D21">
-        <v>12754.0015514302</v>
+        <v>12768.9946542853</v>
       </c>
       <c r="E21">
         <v>-830.23</v>
@@ -3009,37 +3229,37 @@
         <v>3618.2</v>
       </c>
       <c r="M21">
-        <v>142.659429</v>
+        <v>138.796311</v>
       </c>
       <c r="N21">
-        <v>3475.540571</v>
+        <v>3479.403689</v>
       </c>
       <c r="O21">
-        <v>764.61892562</v>
+        <v>765.46881158</v>
       </c>
       <c r="P21">
-        <v>2710.92164538</v>
+        <v>2713.93487742</v>
       </c>
       <c r="Q21">
-        <v>3656.72164538</v>
+        <v>3659.73487742</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.0962464363864779</v>
+        <v>0.09621400381310084</v>
       </c>
       <c r="T21">
         <v>1.164295700071613</v>
       </c>
       <c r="U21">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V21">
         <v>0.22</v>
       </c>
       <c r="W21">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3267,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>25.3625016261631</v>
+        <v>26.06841618434657</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3278,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08547299636843356</v>
+        <v>0.08522838630005508</v>
       </c>
       <c r="C22">
-        <v>11652.61465486784</v>
+        <v>11668.41893724281</v>
       </c>
       <c r="D22">
-        <v>12764.71465486784</v>
+        <v>12780.51893724281</v>
       </c>
       <c r="E22">
         <v>-684.9999999999995</v>
@@ -3091,37 +3311,37 @@
         <v>3618.2</v>
       </c>
       <c r="M22">
-        <v>150.16782</v>
+        <v>146.10138</v>
       </c>
       <c r="N22">
-        <v>3468.03218</v>
+        <v>3472.09862</v>
       </c>
       <c r="O22">
-        <v>762.9670795999999</v>
+        <v>763.8616963999999</v>
       </c>
       <c r="P22">
-        <v>2705.0651004</v>
+        <v>2708.2369236</v>
       </c>
       <c r="Q22">
-        <v>3650.865100399999</v>
+        <v>3654.0369236</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.09675974546054193</v>
+        <v>0.09672698287506884</v>
       </c>
       <c r="T22">
         <v>1.176142791572029</v>
       </c>
       <c r="U22">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V22">
         <v>0.22</v>
       </c>
       <c r="W22">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3349,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>24.09437654485494</v>
+        <v>24.76499537512924</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3360,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08532443926382</v>
+        <v>0.08506896951149846</v>
       </c>
       <c r="C23">
-        <v>11518.11577101638</v>
+        <v>11534.73404080092</v>
       </c>
       <c r="D23">
-        <v>12775.44577101638</v>
+        <v>12792.06404080092</v>
       </c>
       <c r="E23">
         <v>-539.77</v>
@@ -3173,37 +3393,37 @@
         <v>3618.2</v>
       </c>
       <c r="M23">
-        <v>157.676211</v>
+        <v>153.406449</v>
       </c>
       <c r="N23">
-        <v>3460.523789</v>
+        <v>3464.793551</v>
       </c>
       <c r="O23">
-        <v>761.3152335799999</v>
+        <v>762.25458122</v>
       </c>
       <c r="P23">
-        <v>2699.20855542</v>
+        <v>2702.53896978</v>
       </c>
       <c r="Q23">
-        <v>3645.00855542</v>
+        <v>3648.338969779999</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.09728604970103796</v>
+        <v>0.09725294874873222</v>
       </c>
       <c r="T23">
         <v>1.188289809439543</v>
       </c>
       <c r="U23">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V23">
         <v>0.22</v>
       </c>
       <c r="W23">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3431,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>22.94702528081423</v>
+        <v>23.58570988107547</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3442,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08517588215920645</v>
+        <v>0.08490955272294184</v>
       </c>
       <c r="C24">
-        <v>11383.63494534312</v>
+        <v>11401.07002143466</v>
       </c>
       <c r="D24">
-        <v>12786.19494534312</v>
+        <v>12803.63002143466</v>
       </c>
       <c r="E24">
         <v>-394.54</v>
@@ -3255,37 +3475,37 @@
         <v>3618.2</v>
       </c>
       <c r="M24">
-        <v>165.184602</v>
+        <v>160.711518</v>
       </c>
       <c r="N24">
-        <v>3453.015398</v>
+        <v>3457.488482</v>
       </c>
       <c r="O24">
-        <v>759.6633875599999</v>
+        <v>760.6474660399999</v>
       </c>
       <c r="P24">
-        <v>2693.35201044</v>
+        <v>2696.84101596</v>
       </c>
       <c r="Q24">
-        <v>3639.15201044</v>
+        <v>3642.64101596</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.09782584892205955</v>
+        <v>0.09779240092684852</v>
       </c>
       <c r="T24">
         <v>1.200748289303661</v>
       </c>
       <c r="U24">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V24">
         <v>0.22</v>
       </c>
       <c r="W24">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3513,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>21.90397867714086</v>
+        <v>22.5136321592084</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3524,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.0850273250545929</v>
+        <v>0.08475013593438523</v>
       </c>
       <c r="C25">
-        <v>11249.17222346854</v>
+        <v>11267.42693582346</v>
       </c>
       <c r="D25">
-        <v>12796.96222346854</v>
+        <v>12815.21693582346</v>
       </c>
       <c r="E25">
         <v>-249.3099999999999</v>
@@ -3337,37 +3557,37 @@
         <v>3618.2</v>
       </c>
       <c r="M25">
-        <v>172.692993</v>
+        <v>168.016587</v>
       </c>
       <c r="N25">
-        <v>3445.507007</v>
+        <v>3450.183413</v>
       </c>
       <c r="O25">
-        <v>758.0115415399999</v>
+        <v>759.04035086</v>
       </c>
       <c r="P25">
-        <v>2687.49546546</v>
+        <v>2691.14306214</v>
       </c>
       <c r="Q25">
-        <v>3633.29546546</v>
+        <v>3636.94306214</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.0983796689020687</v>
+        <v>0.09834586484985094</v>
       </c>
       <c r="T25">
         <v>1.213530366047366</v>
       </c>
       <c r="U25">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V25">
         <v>0.22</v>
       </c>
       <c r="W25">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3595,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>20.95163177813473</v>
+        <v>21.5347785870689</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3606,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08487876794997935</v>
+        <v>0.08459071914582864</v>
       </c>
       <c r="C26">
-        <v>11114.72765116692</v>
+        <v>11133.80484085213</v>
       </c>
       <c r="D26">
-        <v>12807.74765116692</v>
+        <v>12826.82484085213</v>
       </c>
       <c r="E26">
         <v>-104.0799999999999</v>
@@ -3419,37 +3639,37 @@
         <v>3618.2</v>
       </c>
       <c r="M26">
-        <v>180.201384</v>
+        <v>175.321656</v>
       </c>
       <c r="N26">
-        <v>3437.998616</v>
+        <v>3442.878344</v>
       </c>
       <c r="O26">
-        <v>756.3596955199999</v>
+        <v>757.4332356799999</v>
       </c>
       <c r="P26">
-        <v>2681.63892048</v>
+        <v>2685.44510832</v>
       </c>
       <c r="Q26">
-        <v>3627.43892048</v>
+        <v>3631.245108319999</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.09894806309207808</v>
+        <v>0.0989138936129324</v>
       </c>
       <c r="T26">
         <v>1.226648813231695</v>
       </c>
       <c r="U26">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V26">
         <v>0.22</v>
       </c>
       <c r="W26">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3677,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>20.07864712071245</v>
+        <v>20.63749614594103</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3688,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08473021084536579</v>
+        <v>0.08443130235727202</v>
       </c>
       <c r="C27">
-        <v>10980.30127436697</v>
+        <v>11000.20379361178</v>
       </c>
       <c r="D27">
-        <v>12818.55127436697</v>
+        <v>12838.45379361178</v>
       </c>
       <c r="E27">
         <v>41.15000000000009</v>
@@ -3501,37 +3721,37 @@
         <v>3618.2</v>
       </c>
       <c r="M27">
-        <v>187.709775</v>
+        <v>182.626725</v>
       </c>
       <c r="N27">
-        <v>3430.490225</v>
+        <v>3435.573275</v>
       </c>
       <c r="O27">
-        <v>754.7078495</v>
+        <v>755.8261205</v>
       </c>
       <c r="P27">
-        <v>2675.782375499999</v>
+        <v>2679.7471545</v>
       </c>
       <c r="Q27">
-        <v>3621.582375499999</v>
+        <v>3625.5471545</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.09953161446048772</v>
+        <v>0.09949706980969603</v>
       </c>
       <c r="T27">
         <v>1.240117085674273</v>
       </c>
       <c r="U27">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V27">
         <v>0.22</v>
       </c>
       <c r="W27">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3759,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>19.27550123588395</v>
+        <v>19.81199630010339</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3770,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08458165374075224</v>
+        <v>0.0842718855687154</v>
       </c>
       <c r="C28">
-        <v>10845.89313915251</v>
+        <v>10866.62385140071</v>
       </c>
       <c r="D28">
-        <v>12829.37313915251</v>
+        <v>12850.10385140071</v>
       </c>
       <c r="E28">
         <v>186.3800000000001</v>
@@ -3583,37 +3803,37 @@
         <v>3618.2</v>
       </c>
       <c r="M28">
-        <v>195.218166</v>
+        <v>189.931794</v>
       </c>
       <c r="N28">
-        <v>3422.981834</v>
+        <v>3428.268206</v>
       </c>
       <c r="O28">
-        <v>753.05600348</v>
+        <v>754.21900532</v>
       </c>
       <c r="P28">
-        <v>2669.92583052</v>
+        <v>2674.04920068</v>
       </c>
       <c r="Q28">
-        <v>3615.725830519999</v>
+        <v>3619.84920068</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.100130937487503</v>
+        <v>0.1000960075252911</v>
       </c>
       <c r="T28">
         <v>1.253949365480164</v>
       </c>
       <c r="U28">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V28">
         <v>0.22</v>
       </c>
       <c r="W28">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3841,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>18.53413580373457</v>
+        <v>19.04999644240711</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +3852,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.0844330966361387</v>
+        <v>0.08411246878015879</v>
       </c>
       <c r="C29">
-        <v>10711.5032917631</v>
+        <v>10733.06507172542</v>
       </c>
       <c r="D29">
-        <v>12840.2132917631</v>
+        <v>12861.77507172542</v>
       </c>
       <c r="E29">
         <v>331.6100000000001</v>
@@ -3665,37 +3885,37 @@
         <v>3618.2</v>
       </c>
       <c r="M29">
-        <v>202.726557</v>
+        <v>197.236863</v>
       </c>
       <c r="N29">
-        <v>3415.473443</v>
+        <v>3420.963137</v>
       </c>
       <c r="O29">
-        <v>751.40415746</v>
+        <v>752.6118901399999</v>
       </c>
       <c r="P29">
-        <v>2664.06928554</v>
+        <v>2668.35124686</v>
       </c>
       <c r="Q29">
-        <v>3609.86928554</v>
+        <v>3614.151246859999</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1007466803234777</v>
+        <v>0.1007113544933682</v>
       </c>
       <c r="T29">
         <v>1.268160611856079</v>
       </c>
       <c r="U29">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V29">
         <v>0.22</v>
       </c>
       <c r="W29">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3923,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>17.84768632952218</v>
+        <v>18.34444101861425</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +3934,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08428453953152515</v>
+        <v>0.08395305199160218</v>
       </c>
       <c r="C30">
-        <v>10577.13177859475</v>
+        <v>10599.52751230151</v>
       </c>
       <c r="D30">
-        <v>12851.07177859475</v>
+        <v>12873.46751230151</v>
       </c>
       <c r="E30">
         <v>476.8400000000006</v>
@@ -3747,37 +3967,37 @@
         <v>3618.2</v>
       </c>
       <c r="M30">
-        <v>210.2349480000001</v>
+        <v>204.541932</v>
       </c>
       <c r="N30">
-        <v>3407.965052</v>
+        <v>3413.658068</v>
       </c>
       <c r="O30">
-        <v>749.7523114399999</v>
+        <v>751.00477496</v>
       </c>
       <c r="P30">
-        <v>2658.212740559999</v>
+        <v>2662.65329304</v>
       </c>
       <c r="Q30">
-        <v>3604.01274056</v>
+        <v>3608.45329304</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1013795271271183</v>
+        <v>0.1013437944327808</v>
       </c>
       <c r="T30">
         <v>1.282766615075769</v>
       </c>
       <c r="U30">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V30">
         <v>0.22</v>
       </c>
       <c r="W30">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +4005,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>17.21026896061067</v>
+        <v>17.6892824108066</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +4016,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.08413598242691159</v>
+        <v>0.08379363520304556</v>
       </c>
       <c r="C31">
-        <v>10442.77864620049</v>
+        <v>10466.01123105465</v>
       </c>
       <c r="D31">
-        <v>12861.94864620049</v>
+        <v>12885.18123105465</v>
       </c>
       <c r="E31">
         <v>622.0700000000002</v>
@@ -3829,37 +4049,37 @@
         <v>3618.2</v>
       </c>
       <c r="M31">
-        <v>217.743339</v>
+        <v>211.847001</v>
       </c>
       <c r="N31">
-        <v>3400.456661</v>
+        <v>3406.352999</v>
       </c>
       <c r="O31">
-        <v>748.10046542</v>
+        <v>749.3976597799999</v>
       </c>
       <c r="P31">
-        <v>2652.35619558</v>
+        <v>2656.95533922</v>
       </c>
       <c r="Q31">
-        <v>3598.15619558</v>
+        <v>3602.75533922</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1020302006012839</v>
+        <v>0.1019940495817543</v>
       </c>
       <c r="T31">
         <v>1.297784055005873</v>
       </c>
       <c r="U31">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V31">
         <v>0.22</v>
       </c>
       <c r="W31">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +4087,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>16.61681141024479</v>
+        <v>17.07930715526154</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +4098,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08398742532229804</v>
+        <v>0.08363421841448895</v>
       </c>
       <c r="C32">
-        <v>10308.44394129114</v>
+        <v>10332.51628612151</v>
       </c>
       <c r="D32">
-        <v>12872.84394129114</v>
+        <v>12896.91628612151</v>
       </c>
       <c r="E32">
         <v>767.2999999999997</v>
@@ -3911,37 +4131,37 @@
         <v>3618.2</v>
       </c>
       <c r="M32">
-        <v>225.25173</v>
+        <v>219.15207</v>
       </c>
       <c r="N32">
-        <v>3392.94827</v>
+        <v>3399.04793</v>
       </c>
       <c r="O32">
-        <v>746.4486194</v>
+        <v>747.7905446</v>
       </c>
       <c r="P32">
-        <v>2646.4996506</v>
+        <v>2651.2573854</v>
       </c>
       <c r="Q32">
-        <v>3592.2996506</v>
+        <v>3597.057385399999</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1026994647461401</v>
+        <v>0.1026628834492699</v>
       </c>
       <c r="T32">
         <v>1.313230564648266</v>
       </c>
       <c r="U32">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V32">
         <v>0.22</v>
       </c>
       <c r="W32">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +4169,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>16.06291769656996</v>
+        <v>16.50999691675283</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +4180,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08383886821768451</v>
+        <v>0.08347480162593233</v>
       </c>
       <c r="C33">
-        <v>10174.12771073589</v>
+        <v>10199.04273585077</v>
       </c>
       <c r="D33">
-        <v>12883.75771073589</v>
+        <v>12908.67273585077</v>
       </c>
       <c r="E33">
         <v>912.5300000000002</v>
@@ -3993,37 +4213,37 @@
         <v>3618.2</v>
       </c>
       <c r="M33">
-        <v>232.7601210000001</v>
+        <v>226.457139</v>
       </c>
       <c r="N33">
-        <v>3385.439879</v>
+        <v>3391.742861</v>
       </c>
       <c r="O33">
-        <v>744.7967733799999</v>
+        <v>746.1834294199999</v>
       </c>
       <c r="P33">
-        <v>2640.64310562</v>
+        <v>2645.55943158</v>
       </c>
       <c r="Q33">
-        <v>3586.44310562</v>
+        <v>3591.35943158</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1033881278517167</v>
+        <v>0.103351103805699</v>
       </c>
       <c r="T33">
         <v>1.32912479920783</v>
       </c>
       <c r="U33">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V33">
         <v>0.22</v>
       </c>
       <c r="W33">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4251,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>15.54475906119674</v>
+        <v>15.97741637105112</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4262,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08369031111307094</v>
+        <v>0.08331538483737573</v>
       </c>
       <c r="C34">
-        <v>10039.83000156303</v>
+        <v>10065.59063880405</v>
       </c>
       <c r="D34">
-        <v>12894.69000156303</v>
+        <v>12920.45063880405</v>
       </c>
       <c r="E34">
         <v>1057.76</v>
@@ -4075,37 +4295,37 @@
         <v>3618.2</v>
       </c>
       <c r="M34">
-        <v>240.268512</v>
+        <v>233.762208</v>
       </c>
       <c r="N34">
-        <v>3377.931488</v>
+        <v>3384.437792</v>
       </c>
       <c r="O34">
-        <v>743.14492736</v>
+        <v>744.57631424</v>
       </c>
       <c r="P34">
-        <v>2634.78656064</v>
+        <v>2639.86147776</v>
       </c>
       <c r="Q34">
-        <v>3580.586560639999</v>
+        <v>3585.66147776</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1040970457545161</v>
+        <v>0.1040595659373172</v>
       </c>
       <c r="T34">
         <v>1.34548651125444</v>
       </c>
       <c r="U34">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V34">
         <v>0.22</v>
       </c>
       <c r="W34">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4333,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>15.05898534053434</v>
+        <v>15.47812210945578</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4344,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.08354175400845738</v>
+        <v>0.08315596804881911</v>
       </c>
       <c r="C35">
-        <v>9905.550860960599</v>
+        <v>9932.16005375689</v>
       </c>
       <c r="D35">
-        <v>12905.6408609606</v>
+        <v>12932.25005375689</v>
       </c>
       <c r="E35">
         <v>1202.99</v>
@@ -4157,37 +4377,37 @@
         <v>3618.2</v>
       </c>
       <c r="M35">
-        <v>247.7769030000001</v>
+        <v>241.067277</v>
       </c>
       <c r="N35">
-        <v>3370.423097</v>
+        <v>3377.132723</v>
       </c>
       <c r="O35">
-        <v>741.49308134</v>
+        <v>742.9691990599999</v>
       </c>
       <c r="P35">
-        <v>2628.93001566</v>
+        <v>2634.16352394</v>
       </c>
       <c r="Q35">
-        <v>3574.730015659999</v>
+        <v>3579.96352394</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1048271253857573</v>
+        <v>0.1047891761922673</v>
       </c>
       <c r="T35">
         <v>1.362336632615874</v>
       </c>
       <c r="U35">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V35">
         <v>0.22</v>
       </c>
       <c r="W35">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4415,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>14.60265245142724</v>
+        <v>15.00908810613893</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4426,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.08339319690384384</v>
+        <v>0.08299655126026249</v>
       </c>
       <c r="C36">
-        <v>9771.290336277078</v>
+        <v>9798.751039699731</v>
       </c>
       <c r="D36">
-        <v>12916.61033627708</v>
+        <v>12944.07103969973</v>
       </c>
       <c r="E36">
         <v>1348.220000000001</v>
@@ -4239,37 +4459,37 @@
         <v>3618.2</v>
       </c>
       <c r="M36">
-        <v>255.2852940000001</v>
+        <v>248.3723460000001</v>
       </c>
       <c r="N36">
-        <v>3362.914706</v>
+        <v>3369.827654</v>
       </c>
       <c r="O36">
-        <v>739.8412353199999</v>
+        <v>741.3620838799999</v>
       </c>
       <c r="P36">
-        <v>2623.073470679999</v>
+        <v>2628.46557012</v>
       </c>
       <c r="Q36">
-        <v>3568.87347068</v>
+        <v>3574.26557012</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1055793286421876</v>
+        <v>0.1055408958488826</v>
       </c>
       <c r="T36">
         <v>1.379697363715533</v>
       </c>
       <c r="U36">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V36">
         <v>0.22</v>
       </c>
       <c r="W36">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4497,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>14.17316267344408</v>
+        <v>14.56764433831131</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4508,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.0832446397992303</v>
+        <v>0.08283713447170589</v>
       </c>
       <c r="C37">
-        <v>9637.048475022053</v>
+        <v>9665.36365583889</v>
       </c>
       <c r="D37">
-        <v>12927.59847502205</v>
+        <v>12955.91365583889</v>
       </c>
       <c r="E37">
         <v>1493.45</v>
@@ -4321,37 +4541,37 @@
         <v>3618.2</v>
       </c>
       <c r="M37">
-        <v>262.793685</v>
+        <v>255.677415</v>
       </c>
       <c r="N37">
-        <v>3355.406315</v>
+        <v>3362.522585</v>
       </c>
       <c r="O37">
-        <v>738.1893892999999</v>
+        <v>739.7549686999999</v>
       </c>
       <c r="P37">
-        <v>2617.2169257</v>
+        <v>2622.7676163</v>
       </c>
       <c r="Q37">
-        <v>3563.0169257</v>
+        <v>3568.5676163</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1063546766142005</v>
+        <v>0.106315745341086</v>
       </c>
       <c r="T37">
         <v>1.39759227115672</v>
       </c>
       <c r="U37">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V37">
         <v>0.22</v>
       </c>
       <c r="W37">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4579,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>13.76821516848854</v>
+        <v>14.15142592864528</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4590,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.08309608269461675</v>
+        <v>0.08267771768314927</v>
       </c>
       <c r="C38">
-        <v>9502.825324866928</v>
+        <v>9531.997961597572</v>
       </c>
       <c r="D38">
-        <v>12938.60532486693</v>
+        <v>12967.77796159757</v>
       </c>
       <c r="E38">
         <v>1638.68</v>
@@ -4403,37 +4623,37 @@
         <v>3618.2</v>
       </c>
       <c r="M38">
-        <v>270.3020760000001</v>
+        <v>262.982484</v>
       </c>
       <c r="N38">
-        <v>3347.897924</v>
+        <v>3355.217516</v>
       </c>
       <c r="O38">
-        <v>736.53754328</v>
+        <v>738.1478535199999</v>
       </c>
       <c r="P38">
-        <v>2611.36038072</v>
+        <v>2617.06966248</v>
       </c>
       <c r="Q38">
-        <v>3557.16038072</v>
+        <v>3562.86966248</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1071542542103387</v>
+        <v>0.1071148088799207</v>
       </c>
       <c r="T38">
         <v>1.416046394455444</v>
       </c>
       <c r="U38">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V38">
         <v>0.22</v>
       </c>
       <c r="W38">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4661,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>13.38576474714164</v>
+        <v>13.75833076396069</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4672,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.08294752559000321</v>
+        <v>0.08251830089459267</v>
       </c>
       <c r="C39">
-        <v>9368.620933645587</v>
+        <v>9398.654016616831</v>
       </c>
       <c r="D39">
-        <v>12949.63093364559</v>
+        <v>12979.66401661683</v>
       </c>
       <c r="E39">
         <v>1783.91</v>
@@ -4485,37 +4705,37 @@
         <v>3618.2</v>
       </c>
       <c r="M39">
-        <v>277.8104670000001</v>
+        <v>270.2875530000001</v>
       </c>
       <c r="N39">
-        <v>3340.389533</v>
+        <v>3347.912447</v>
       </c>
       <c r="O39">
-        <v>734.8856972599999</v>
+        <v>736.54073834</v>
       </c>
       <c r="P39">
-        <v>2605.50383574</v>
+        <v>2611.37170866</v>
       </c>
       <c r="Q39">
-        <v>3551.30383574</v>
+        <v>3557.17170866</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1079792152222273</v>
+        <v>0.1079392395152265</v>
       </c>
       <c r="T39">
         <v>1.435086362938255</v>
       </c>
       <c r="U39">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V39">
         <v>0.22</v>
       </c>
       <c r="W39">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4743,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>13.02398732154321</v>
+        <v>13.38648398655634</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4754,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.08279896848538965</v>
+        <v>0.08235888410603605</v>
       </c>
       <c r="C40">
-        <v>9234.435349355103</v>
+        <v>9265.331880756597</v>
       </c>
       <c r="D40">
-        <v>12960.6753493551</v>
+        <v>12991.5718807566</v>
       </c>
       <c r="E40">
         <v>1929.14</v>
@@ -4567,37 +4787,37 @@
         <v>3618.2</v>
       </c>
       <c r="M40">
-        <v>285.318858</v>
+        <v>277.592622</v>
       </c>
       <c r="N40">
-        <v>3332.881142</v>
+        <v>3340.607378</v>
       </c>
       <c r="O40">
-        <v>733.2338512399999</v>
+        <v>734.9336231599999</v>
       </c>
       <c r="P40">
-        <v>2599.64729076</v>
+        <v>2605.67375484</v>
       </c>
       <c r="Q40">
-        <v>3545.44729076</v>
+        <v>3551.47375484</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1088307878796607</v>
+        <v>0.1087902646871549</v>
       </c>
       <c r="T40">
         <v>1.45474052395277</v>
       </c>
       <c r="U40">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V40">
         <v>0.22</v>
       </c>
       <c r="W40">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4825,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>12.68125081308155</v>
+        <v>13.03420809217328</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +4836,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.08265041138077608</v>
+        <v>0.08219946731747943</v>
       </c>
       <c r="C41">
-        <v>9100.268620156436</v>
+        <v>9132.031614096664</v>
       </c>
       <c r="D41">
-        <v>12971.73862015643</v>
+        <v>13003.50161409666</v>
       </c>
       <c r="E41">
         <v>2074.37</v>
@@ -4649,37 +4869,37 @@
         <v>3618.2</v>
       </c>
       <c r="M41">
-        <v>292.8272490000001</v>
+        <v>284.8976910000001</v>
       </c>
       <c r="N41">
-        <v>3325.372751</v>
+        <v>3333.302309</v>
       </c>
       <c r="O41">
-        <v>731.5820052199999</v>
+        <v>733.32650798</v>
       </c>
       <c r="P41">
-        <v>2593.79074578</v>
+        <v>2599.97580102</v>
       </c>
       <c r="Q41">
-        <v>3539.59074578</v>
+        <v>3545.77580102</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.109710280952092</v>
+        <v>0.1096691923237368</v>
       </c>
       <c r="T41">
         <v>1.475039083689071</v>
       </c>
       <c r="U41">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V41">
         <v>0.22</v>
       </c>
       <c r="W41">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4907,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>12.35609053582305</v>
+        <v>12.6999976282714</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +4918,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.08250185427616255</v>
+        <v>0.08204005052892283</v>
       </c>
       <c r="C42">
-        <v>8966.120794375111</v>
+        <v>8998.753276937703</v>
       </c>
       <c r="D42">
-        <v>12982.82079437511</v>
+        <v>13015.4532769377</v>
       </c>
       <c r="E42">
         <v>2219.600000000001</v>
@@ -4731,37 +4951,37 @@
         <v>3618.2</v>
       </c>
       <c r="M42">
-        <v>300.3356400000001</v>
+        <v>292.2027600000001</v>
       </c>
       <c r="N42">
-        <v>3317.86436</v>
+        <v>3325.99724</v>
       </c>
       <c r="O42">
-        <v>729.9301591999999</v>
+        <v>731.7193927999999</v>
       </c>
       <c r="P42">
-        <v>2587.934200799999</v>
+        <v>2594.2778472</v>
       </c>
       <c r="Q42">
-        <v>3533.7342008</v>
+        <v>3540.0778472</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1106190904602709</v>
+        <v>0.1105774175482047</v>
       </c>
       <c r="T42">
         <v>1.49601426208325</v>
       </c>
       <c r="U42">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V42">
         <v>0.22</v>
       </c>
       <c r="W42">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4989,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>12.04718827242747</v>
+        <v>12.38249768756462</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +5000,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.082353297171549</v>
+        <v>0.08188063374036622</v>
       </c>
       <c r="C43">
-        <v>8831.991920501965</v>
+        <v>8865.496929802288</v>
       </c>
       <c r="D43">
-        <v>12993.92192050197</v>
+        <v>13027.42692980229</v>
       </c>
       <c r="E43">
         <v>2364.83</v>
@@ -4813,37 +5033,37 @@
         <v>3618.2</v>
       </c>
       <c r="M43">
-        <v>307.8440310000001</v>
+        <v>299.507829</v>
       </c>
       <c r="N43">
-        <v>3310.355969</v>
+        <v>3318.692171</v>
       </c>
       <c r="O43">
-        <v>728.2783131799999</v>
+        <v>730.11227762</v>
       </c>
       <c r="P43">
-        <v>2582.07765582</v>
+        <v>2588.57989338</v>
       </c>
       <c r="Q43">
-        <v>3527.87765582</v>
+        <v>3534.37989338</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.111558707070422</v>
+        <v>0.1115164300684173</v>
       </c>
       <c r="T43">
         <v>1.517700463473841</v>
       </c>
       <c r="U43">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V43">
         <v>0.22</v>
       </c>
       <c r="W43">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +5071,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>11.75335441212436</v>
+        <v>12.08048554884353</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +5082,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.08220474006693546</v>
+        <v>0.08172121695180962</v>
       </c>
       <c r="C44">
-        <v>8697.882047193807</v>
+        <v>8732.26263343591</v>
       </c>
       <c r="D44">
-        <v>13005.04204719381</v>
+        <v>13039.42263343591</v>
       </c>
       <c r="E44">
         <v>2510.06</v>
@@ -4895,37 +5115,37 @@
         <v>3618.2</v>
       </c>
       <c r="M44">
-        <v>315.352422</v>
+        <v>306.812898</v>
       </c>
       <c r="N44">
-        <v>3302.847578</v>
+        <v>3311.387102</v>
       </c>
       <c r="O44">
-        <v>726.6264671599999</v>
+        <v>728.5051624399999</v>
       </c>
       <c r="P44">
-        <v>2576.22111084</v>
+        <v>2582.88193956</v>
       </c>
       <c r="Q44">
-        <v>3522.02111084</v>
+        <v>3528.68193956</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.112530724253337</v>
+        <v>0.1124878223307062</v>
       </c>
       <c r="T44">
         <v>1.540134464912384</v>
       </c>
       <c r="U44">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V44">
         <v>0.22</v>
       </c>
       <c r="W44">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +5153,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>11.47351264040712</v>
+        <v>11.79285494053773</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +5164,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.08205618296232189</v>
+        <v>0.081561800163253</v>
       </c>
       <c r="C45">
-        <v>8563.791223274158</v>
+        <v>8599.050448808004</v>
       </c>
       <c r="D45">
-        <v>13016.18122327416</v>
+        <v>13051.440448808</v>
       </c>
       <c r="E45">
         <v>2655.29</v>
@@ -4977,37 +5197,37 @@
         <v>3618.2</v>
       </c>
       <c r="M45">
-        <v>322.8608130000001</v>
+        <v>314.117967</v>
       </c>
       <c r="N45">
-        <v>3295.339187</v>
+        <v>3304.082033</v>
       </c>
       <c r="O45">
-        <v>724.97462114</v>
+        <v>726.8980472599999</v>
       </c>
       <c r="P45">
-        <v>2570.36456586</v>
+        <v>2577.18398574</v>
       </c>
       <c r="Q45">
-        <v>3516.16456586</v>
+        <v>3522.98398574</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1135368473023191</v>
+        <v>0.1134932985320228</v>
       </c>
       <c r="T45">
         <v>1.563355624296138</v>
       </c>
       <c r="U45">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V45">
         <v>0.22</v>
       </c>
       <c r="W45">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5235,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>11.20668676504881</v>
+        <v>11.51860250006011</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5246,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.08190762585770835</v>
+        <v>0.08140238337469638</v>
       </c>
       <c r="C46">
-        <v>8429.719497733953</v>
+        <v>8465.860437112973</v>
       </c>
       <c r="D46">
-        <v>13027.33949773395</v>
+        <v>13063.48043711297</v>
       </c>
       <c r="E46">
         <v>2800.52</v>
@@ -5059,37 +5279,37 @@
         <v>3618.2</v>
       </c>
       <c r="M46">
-        <v>330.3692040000001</v>
+        <v>321.423036</v>
       </c>
       <c r="N46">
-        <v>3287.830796</v>
+        <v>3296.776964</v>
       </c>
       <c r="O46">
-        <v>723.32277512</v>
+        <v>725.2909320799999</v>
       </c>
       <c r="P46">
-        <v>2564.50802088</v>
+        <v>2571.48603192</v>
       </c>
       <c r="Q46">
-        <v>3510.30802088</v>
+        <v>3517.28603192</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1145789033173363</v>
+        <v>0.1145346845976721</v>
       </c>
       <c r="T46">
         <v>1.587406110800742</v>
       </c>
       <c r="U46">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V46">
         <v>0.22</v>
       </c>
       <c r="W46">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5317,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>10.95198933857043</v>
+        <v>11.2568160796042</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5328,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.0817590687530948</v>
+        <v>0.08124296658613978</v>
       </c>
       <c r="C47">
-        <v>8295.666919732261</v>
+        <v>8332.692659771254</v>
       </c>
       <c r="D47">
-        <v>13038.51691973226</v>
+        <v>13075.54265977125</v>
       </c>
       <c r="E47">
         <v>2945.75</v>
@@ -5141,37 +5361,37 @@
         <v>3618.2</v>
       </c>
       <c r="M47">
-        <v>337.8775950000001</v>
+        <v>328.728105</v>
       </c>
       <c r="N47">
-        <v>3280.322405</v>
+        <v>3289.471895</v>
       </c>
       <c r="O47">
-        <v>721.6709291</v>
+        <v>723.6838168999999</v>
       </c>
       <c r="P47">
-        <v>2558.6514759</v>
+        <v>2565.7880781</v>
       </c>
       <c r="Q47">
-        <v>3504.4514759</v>
+        <v>3511.5880781</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1156588522783542</v>
+        <v>0.1156139392475269</v>
       </c>
       <c r="T47">
         <v>1.612331160450966</v>
       </c>
       <c r="U47">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V47">
         <v>0.22</v>
       </c>
       <c r="W47">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5399,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>10.70861179771331</v>
+        <v>11.00666461116855</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5410,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.08161051164848125</v>
+        <v>0.08108354979758316</v>
       </c>
       <c r="C48">
-        <v>8161.633538597021</v>
+        <v>8199.54717843033</v>
       </c>
       <c r="D48">
-        <v>13049.71353859702</v>
+        <v>13087.62717843033</v>
       </c>
       <c r="E48">
         <v>3090.98</v>
@@ -5223,37 +5443,37 @@
         <v>3618.2</v>
       </c>
       <c r="M48">
-        <v>345.3859860000001</v>
+        <v>336.033174</v>
       </c>
       <c r="N48">
-        <v>3272.814014</v>
+        <v>3282.166826</v>
       </c>
       <c r="O48">
-        <v>720.0190830799999</v>
+        <v>722.07670172</v>
       </c>
       <c r="P48">
-        <v>2552.79493092</v>
+        <v>2560.09012428</v>
       </c>
       <c r="Q48">
-        <v>3498.59493092</v>
+        <v>3505.890124279999</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1167787993490393</v>
+        <v>0.1167331662918207</v>
       </c>
       <c r="T48">
         <v>1.638179360088237</v>
       </c>
       <c r="U48">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V48">
         <v>0.22</v>
       </c>
       <c r="W48">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5481,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>10.47581588906737</v>
+        <v>10.76738929353445</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5492,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.0814619545438677</v>
+        <v>0.08092413300902655</v>
       </c>
       <c r="C49">
-        <v>8027.61940382575</v>
+        <v>8066.424054965803</v>
       </c>
       <c r="D49">
-        <v>13060.92940382575</v>
+        <v>13099.7340549658</v>
       </c>
       <c r="E49">
         <v>3236.21</v>
@@ -5305,37 +5525,37 @@
         <v>3618.2</v>
       </c>
       <c r="M49">
-        <v>352.8943770000001</v>
+        <v>343.338243</v>
       </c>
       <c r="N49">
-        <v>3265.305623</v>
+        <v>3274.861757</v>
       </c>
       <c r="O49">
-        <v>718.36723706</v>
+        <v>720.4695865399999</v>
       </c>
       <c r="P49">
-        <v>2546.93838594</v>
+        <v>2554.39217046</v>
       </c>
       <c r="Q49">
-        <v>3492.73838594</v>
+        <v>3500.19217046</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1179410085733353</v>
+        <v>0.117894628318918</v>
       </c>
       <c r="T49">
         <v>1.665002963485404</v>
       </c>
       <c r="U49">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V49">
         <v>0.22</v>
       </c>
       <c r="W49">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5563,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>10.25292618929998</v>
+        <v>10.53829590431031</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5574,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.08131339743925416</v>
+        <v>0.08076471622046993</v>
       </c>
       <c r="C50">
-        <v>7893.62456508627</v>
+        <v>7933.323351482443</v>
       </c>
       <c r="D50">
-        <v>13072.16456508627</v>
+        <v>13111.86335148244</v>
       </c>
       <c r="E50">
         <v>3381.44</v>
@@ -5387,37 +5607,37 @@
         <v>3618.2</v>
       </c>
       <c r="M50">
-        <v>360.4027680000001</v>
+        <v>350.643312</v>
       </c>
       <c r="N50">
-        <v>3257.797232</v>
+        <v>3267.556688</v>
       </c>
       <c r="O50">
-        <v>716.71539104</v>
+        <v>718.86247136</v>
       </c>
       <c r="P50">
-        <v>2541.08184096</v>
+        <v>2548.694216639999</v>
       </c>
       <c r="Q50">
-        <v>3486.88184096</v>
+        <v>3494.49421664</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1191479181524118</v>
+        <v>0.1191007619624422</v>
       </c>
       <c r="T50">
         <v>1.692858243936309</v>
       </c>
       <c r="U50">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V50">
         <v>0.22</v>
       </c>
       <c r="W50">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5645,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>10.03932356035623</v>
+        <v>10.31874807297052</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5656,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.08116484033464061</v>
+        <v>0.08060529943191332</v>
       </c>
       <c r="C51">
-        <v>7759.649072217463</v>
+        <v>7800.245130315247</v>
       </c>
       <c r="D51">
-        <v>13083.41907221746</v>
+        <v>13124.01513031525</v>
       </c>
       <c r="E51">
         <v>3526.67</v>
@@ -5469,37 +5689,37 @@
         <v>3618.2</v>
       </c>
       <c r="M51">
-        <v>367.9111590000001</v>
+        <v>357.948381</v>
       </c>
       <c r="N51">
-        <v>3250.288841</v>
+        <v>3260.251619</v>
       </c>
       <c r="O51">
-        <v>715.0635450199999</v>
+        <v>717.2553561799999</v>
       </c>
       <c r="P51">
-        <v>2535.22529598</v>
+        <v>2542.99626282</v>
       </c>
       <c r="Q51">
-        <v>3481.02529598</v>
+        <v>3488.796262819999</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1204021575189031</v>
+        <v>0.1203541949645359</v>
       </c>
       <c r="T51">
         <v>1.721805888326465</v>
       </c>
       <c r="U51">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V51">
         <v>0.22</v>
       </c>
       <c r="W51">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5727,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>9.834439406063243</v>
+        <v>10.10816137760377</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5738,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.08101628323002705</v>
+        <v>0.0804458826433567</v>
       </c>
       <c r="C52">
-        <v>7625.692975229984</v>
+        <v>7667.189454030502</v>
       </c>
       <c r="D52">
-        <v>13094.69297522998</v>
+        <v>13136.1894540305</v>
       </c>
       <c r="E52">
         <v>3671.9</v>
@@ -5551,37 +5771,37 @@
         <v>3618.2</v>
       </c>
       <c r="M52">
-        <v>375.4195500000001</v>
+        <v>365.25345</v>
       </c>
       <c r="N52">
-        <v>3242.78045</v>
+        <v>3252.94655</v>
       </c>
       <c r="O52">
-        <v>713.411699</v>
+        <v>715.648241</v>
       </c>
       <c r="P52">
-        <v>2529.368751</v>
+        <v>2537.298309</v>
       </c>
       <c r="Q52">
-        <v>3475.168751</v>
+        <v>3483.098309</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1217065664600541</v>
+        <v>0.1216577652867134</v>
       </c>
       <c r="T52">
         <v>1.751911438492227</v>
       </c>
       <c r="U52">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V52">
         <v>0.22</v>
       </c>
       <c r="W52">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5809,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>9.637750617941977</v>
+        <v>9.905998150051696</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5820,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.08086772612541351</v>
+        <v>0.08028646585480011</v>
       </c>
       <c r="C53">
-        <v>7491.756324307012</v>
+        <v>7534.156385426876</v>
       </c>
       <c r="D53">
-        <v>13105.98632430701</v>
+        <v>13148.38638542688</v>
       </c>
       <c r="E53">
         <v>3817.130000000001</v>
@@ -5633,37 +5853,37 @@
         <v>3618.2</v>
       </c>
       <c r="M53">
-        <v>382.9279410000001</v>
+        <v>372.558519</v>
       </c>
       <c r="N53">
-        <v>3235.272059</v>
+        <v>3245.641481</v>
       </c>
       <c r="O53">
-        <v>711.75985298</v>
+        <v>714.0411258199999</v>
       </c>
       <c r="P53">
-        <v>2523.51220602</v>
+        <v>2531.600355179999</v>
       </c>
       <c r="Q53">
-        <v>3469.31220602</v>
+        <v>3477.40035518</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1230642165824765</v>
+        <v>0.1230145425608165</v>
       </c>
       <c r="T53">
         <v>1.783245786623938</v>
       </c>
       <c r="U53">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V53">
         <v>0.22</v>
       </c>
       <c r="W53">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5891,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>9.44877511562939</v>
+        <v>9.711762892207544</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +5902,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.08071916902079995</v>
+        <v>0.08012704906624349</v>
       </c>
       <c r="C54">
-        <v>7357.839169805012</v>
+        <v>7401.145987536486</v>
       </c>
       <c r="D54">
-        <v>13117.29916980501</v>
+        <v>13160.60598753649</v>
       </c>
       <c r="E54">
         <v>3962.36</v>
@@ -5715,37 +5935,37 @@
         <v>3618.2</v>
       </c>
       <c r="M54">
-        <v>390.436332</v>
+        <v>379.863588</v>
       </c>
       <c r="N54">
-        <v>3227.763668</v>
+        <v>3238.336412</v>
       </c>
       <c r="O54">
-        <v>710.1080069599999</v>
+        <v>712.4340106399999</v>
       </c>
       <c r="P54">
-        <v>2517.65566104</v>
+        <v>2525.90240136</v>
       </c>
       <c r="Q54">
-        <v>3463.45566104</v>
+        <v>3471.702401359999</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1244784354599999</v>
+        <v>0.1244278522213406</v>
       </c>
       <c r="T54">
         <v>1.815885732594471</v>
       </c>
       <c r="U54">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V54">
         <v>0.22</v>
       </c>
       <c r="W54">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5973,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>9.267067901867286</v>
+        <v>9.524998221203553</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +5984,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.08057061191618639</v>
+        <v>0.07996763227768688</v>
       </c>
       <c r="C55">
-        <v>7223.94156225444</v>
+        <v>7268.158323625985</v>
       </c>
       <c r="D55">
-        <v>13128.63156225444</v>
+        <v>13172.84832362599</v>
       </c>
       <c r="E55">
         <v>4107.59</v>
@@ -5797,37 +6017,37 @@
         <v>3618.2</v>
       </c>
       <c r="M55">
-        <v>397.9447230000001</v>
+        <v>387.1686570000001</v>
       </c>
       <c r="N55">
-        <v>3220.255277</v>
+        <v>3231.031343</v>
       </c>
       <c r="O55">
-        <v>708.4561609399999</v>
+        <v>710.8268954599999</v>
       </c>
       <c r="P55">
-        <v>2511.79911606</v>
+        <v>2520.20444754</v>
       </c>
       <c r="Q55">
-        <v>3457.59911606</v>
+        <v>3466.00444754</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1259528338642264</v>
+        <v>0.1259013027184827</v>
       </c>
       <c r="T55">
         <v>1.84991461243609</v>
       </c>
       <c r="U55">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V55">
         <v>0.22</v>
       </c>
       <c r="W55">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +6055,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>9.092217564096204</v>
+        <v>9.345281273633674</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +6066,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.08042205481157286</v>
+        <v>0.07980821548913027</v>
       </c>
       <c r="C56">
-        <v>7090.06355236054</v>
+        <v>7135.193457197649</v>
       </c>
       <c r="D56">
-        <v>13139.98355236054</v>
+        <v>13185.11345719765</v>
       </c>
       <c r="E56">
         <v>4252.82</v>
@@ -5879,37 +6099,37 @@
         <v>3618.2</v>
       </c>
       <c r="M56">
-        <v>405.4531140000001</v>
+        <v>394.4737260000001</v>
       </c>
       <c r="N56">
-        <v>3212.746886</v>
+        <v>3223.726274</v>
       </c>
       <c r="O56">
-        <v>706.80431492</v>
+        <v>709.2197802799999</v>
       </c>
       <c r="P56">
-        <v>2505.94257108</v>
+        <v>2514.50649372</v>
       </c>
       <c r="Q56">
-        <v>3451.74257108</v>
+        <v>3460.30649372</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1274913365468975</v>
+        <v>0.127438816280718</v>
       </c>
       <c r="T56">
         <v>1.885423008792563</v>
       </c>
       <c r="U56">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V56">
         <v>0.22</v>
       </c>
       <c r="W56">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +6137,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>8.923843164761092</v>
+        <v>9.172220509307126</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +6148,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.0802734977069593</v>
+        <v>0.07964879870057365</v>
       </c>
       <c r="C57">
-        <v>6956.205191004078</v>
+        <v>7002.251451990483</v>
       </c>
       <c r="D57">
-        <v>13151.35519100408</v>
+        <v>13197.40145199048</v>
       </c>
       <c r="E57">
         <v>4398.050000000001</v>
@@ -5961,37 +6181,37 @@
         <v>3618.2</v>
       </c>
       <c r="M57">
-        <v>412.9615050000001</v>
+        <v>401.7787950000001</v>
       </c>
       <c r="N57">
-        <v>3205.238495</v>
+        <v>3216.421205</v>
       </c>
       <c r="O57">
-        <v>705.1524688999999</v>
+        <v>707.6126651</v>
       </c>
       <c r="P57">
-        <v>2500.0860261</v>
+        <v>2508.8085399</v>
       </c>
       <c r="Q57">
-        <v>3445.8860261</v>
+        <v>3454.608539899999</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1290982171265762</v>
+        <v>0.1290446637790525</v>
       </c>
       <c r="T57">
         <v>1.922509556098212</v>
       </c>
       <c r="U57">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V57">
         <v>0.22</v>
       </c>
       <c r="W57">
-        <v>0.04032600000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +6219,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>8.761591470856342</v>
+        <v>9.00545286368336</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6230,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08060542060234574</v>
+        <v>0.07948938191201704</v>
       </c>
       <c r="C58">
-        <v>6785.594492577144</v>
+        <v>6869.332371981327</v>
       </c>
       <c r="D58">
-        <v>13125.97449257714</v>
+        <v>13209.71237198133</v>
       </c>
       <c r="E58">
         <v>4543.280000000001</v>
@@ -6043,45 +6263,45 @@
         <v>3618.2</v>
       </c>
       <c r="M58">
-        <v>429.4160640000001</v>
+        <v>409.0838640000001</v>
       </c>
       <c r="N58">
-        <v>3188.783936</v>
+        <v>3209.116136</v>
       </c>
       <c r="O58">
-        <v>701.5324659199999</v>
+        <v>706.0055499199999</v>
       </c>
       <c r="P58">
-        <v>2487.25147008</v>
+        <v>2503.11058608</v>
       </c>
       <c r="Q58">
-        <v>3433.051470079999</v>
+        <v>3448.91058608</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.130778137732604</v>
+        <v>0.1307235043454933</v>
       </c>
       <c r="T58">
         <v>1.961281855554117</v>
       </c>
       <c r="U58">
-        <v>0.05280000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V58">
         <v>0.22</v>
       </c>
       <c r="W58">
-        <v>0.04118400000000001</v>
+        <v>0.039234</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y58">
-        <v>8.425860845298976</v>
+        <v>8.844641205403299</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6312,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.0804654434977322</v>
+        <v>0.07999686512346042</v>
       </c>
       <c r="C59">
-        <v>6651.055977175722</v>
+        <v>6684.991696148094</v>
       </c>
       <c r="D59">
-        <v>13136.66597717572</v>
+        <v>13170.60169614809</v>
       </c>
       <c r="E59">
         <v>4688.51</v>
@@ -6125,37 +6345,37 @@
         <v>3618.2</v>
       </c>
       <c r="M59">
-        <v>437.0842080000001</v>
+        <v>428.8060980000001</v>
       </c>
       <c r="N59">
-        <v>3181.115792</v>
+        <v>3189.393902</v>
       </c>
       <c r="O59">
-        <v>699.8454742399999</v>
+        <v>701.66665844</v>
       </c>
       <c r="P59">
-        <v>2481.27031776</v>
+        <v>2487.72724356</v>
       </c>
       <c r="Q59">
-        <v>3427.07031776</v>
+        <v>3433.52724356</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1325361941807726</v>
+        <v>0.1324804305196754</v>
       </c>
       <c r="T59">
         <v>2.001857517775414</v>
       </c>
       <c r="U59">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V59">
         <v>0.22</v>
       </c>
       <c r="W59">
-        <v>0.04118400000000001</v>
+        <v>0.040404</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6383,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>8.278038725206009</v>
+        <v>8.437846422603812</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6394,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.08032546639311865</v>
+        <v>0.07984914833490381</v>
       </c>
       <c r="C60">
-        <v>6516.534893017357</v>
+        <v>6551.122006410442</v>
       </c>
       <c r="D60">
-        <v>13147.37489301736</v>
+        <v>13181.96200641044</v>
       </c>
       <c r="E60">
         <v>4833.74</v>
@@ -6207,37 +6427,37 @@
         <v>3618.2</v>
       </c>
       <c r="M60">
-        <v>444.7523520000001</v>
+        <v>436.329012</v>
       </c>
       <c r="N60">
-        <v>3173.447648</v>
+        <v>3181.870988</v>
       </c>
       <c r="O60">
-        <v>698.1584825599999</v>
+        <v>700.0116173599999</v>
       </c>
       <c r="P60">
-        <v>2475.28916544</v>
+        <v>2481.85937064</v>
       </c>
       <c r="Q60">
-        <v>3421.08916544</v>
+        <v>3427.65937064</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1343779676026634</v>
+        <v>0.134321019845009</v>
       </c>
       <c r="T60">
         <v>2.0443653543882</v>
       </c>
       <c r="U60">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V60">
         <v>0.22</v>
       </c>
       <c r="W60">
-        <v>0.04118400000000001</v>
+        <v>0.040404</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6465,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>8.13531391959901</v>
+        <v>8.292366311869262</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6476,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.08018548928850509</v>
+        <v>0.07970143154634721</v>
       </c>
       <c r="C61">
-        <v>6382.031282766296</v>
+        <v>6417.271931276011</v>
       </c>
       <c r="D61">
-        <v>13158.1012827663</v>
+        <v>13193.34193127601</v>
       </c>
       <c r="E61">
         <v>4978.969999999999</v>
@@ -6289,37 +6509,37 @@
         <v>3618.2</v>
       </c>
       <c r="M61">
-        <v>452.420496</v>
+        <v>443.851926</v>
       </c>
       <c r="N61">
-        <v>3165.779504</v>
+        <v>3174.348074</v>
       </c>
       <c r="O61">
-        <v>696.4714908799999</v>
+        <v>698.3565762799999</v>
       </c>
       <c r="P61">
-        <v>2469.308013119999</v>
+        <v>2475.99149772</v>
       </c>
       <c r="Q61">
-        <v>3415.10801312</v>
+        <v>3421.79149772</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1363095836305002</v>
+        <v>0.136251394015481</v>
       </c>
       <c r="T61">
         <v>2.088946744006489</v>
       </c>
       <c r="U61">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V61">
         <v>0.22</v>
       </c>
       <c r="W61">
-        <v>0.04118400000000001</v>
+        <v>0.040404</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6547,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>7.997427242995639</v>
+        <v>8.151817730312157</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6558,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.08004551218389155</v>
+        <v>0.07955371475779059</v>
       </c>
       <c r="C62">
-        <v>6247.545189226139</v>
+        <v>6283.441521588278</v>
       </c>
       <c r="D62">
-        <v>13168.84518922614</v>
+        <v>13204.74152158828</v>
       </c>
       <c r="E62">
         <v>5124.199999999999</v>
@@ -6371,37 +6591,37 @@
         <v>3618.2</v>
       </c>
       <c r="M62">
-        <v>460.08864</v>
+        <v>451.37484</v>
       </c>
       <c r="N62">
-        <v>3158.11136</v>
+        <v>3166.82516</v>
       </c>
       <c r="O62">
-        <v>694.7844992</v>
+        <v>696.7015352</v>
       </c>
       <c r="P62">
-        <v>2463.3268608</v>
+        <v>2470.1236248</v>
       </c>
       <c r="Q62">
-        <v>3409.1268608</v>
+        <v>3415.9236248</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1383377804597289</v>
+        <v>0.1382782868944765</v>
       </c>
       <c r="T62">
         <v>2.135757203105692</v>
       </c>
       <c r="U62">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V62">
         <v>0.22</v>
       </c>
       <c r="W62">
-        <v>0.04118400000000001</v>
+        <v>0.040404</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6629,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>7.864136788945713</v>
+        <v>8.015954101473621</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6640,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.079905535079278</v>
+        <v>0.07940599796923398</v>
       </c>
       <c r="C63">
-        <v>6113.076655340403</v>
+        <v>6149.630828366589</v>
       </c>
       <c r="D63">
-        <v>13179.6066553404</v>
+        <v>13216.16082836659</v>
       </c>
       <c r="E63">
         <v>5269.43</v>
@@ -6453,37 +6673,37 @@
         <v>3618.2</v>
       </c>
       <c r="M63">
-        <v>467.7567840000001</v>
+        <v>458.8977540000001</v>
       </c>
       <c r="N63">
-        <v>3150.443216</v>
+        <v>3159.302246</v>
       </c>
       <c r="O63">
-        <v>693.0975075199999</v>
+        <v>695.0464941199999</v>
       </c>
       <c r="P63">
-        <v>2457.34570848</v>
+        <v>2464.25575188</v>
       </c>
       <c r="Q63">
-        <v>3403.145708479999</v>
+        <v>3410.05575188</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1404699873827641</v>
+        <v>0.1404091229980358</v>
       </c>
       <c r="T63">
         <v>2.184968198568957</v>
       </c>
       <c r="U63">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V63">
         <v>0.22</v>
       </c>
       <c r="W63">
-        <v>0.04118400000000001</v>
+        <v>0.040404</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6711,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>7.735216513717092</v>
+        <v>7.884545017842905</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6722,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.07976555797466445</v>
+        <v>0.07925828118067736</v>
       </c>
       <c r="C64">
-        <v>5978.625724193083</v>
+        <v>6015.839902806933</v>
       </c>
       <c r="D64">
-        <v>13190.38572419308</v>
+        <v>13227.59990280693</v>
       </c>
       <c r="E64">
         <v>5414.66</v>
@@ -6535,37 +6755,37 @@
         <v>3618.2</v>
       </c>
       <c r="M64">
-        <v>475.4249280000001</v>
+        <v>466.4206680000001</v>
       </c>
       <c r="N64">
-        <v>3142.775072</v>
+        <v>3151.779332</v>
       </c>
       <c r="O64">
-        <v>691.41051584</v>
+        <v>693.3914530399999</v>
       </c>
       <c r="P64">
-        <v>2451.36455616</v>
+        <v>2458.38787896</v>
       </c>
       <c r="Q64">
-        <v>3397.16455616</v>
+        <v>3404.18787896</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1427144157228012</v>
+        <v>0.1426521083702036</v>
       </c>
       <c r="T64">
         <v>2.236769246425025</v>
       </c>
       <c r="U64">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V64">
         <v>0.22</v>
       </c>
       <c r="W64">
-        <v>0.04118400000000001</v>
+        <v>0.040404</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6793,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>7.610454957044237</v>
+        <v>7.757374936909954</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6804,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.07962558087005089</v>
+        <v>0.07911056439212075</v>
       </c>
       <c r="C65">
-        <v>5844.192439009244</v>
+        <v>5882.068796282694</v>
       </c>
       <c r="D65">
-        <v>13201.18243900924</v>
+        <v>13239.05879628269</v>
       </c>
       <c r="E65">
         <v>5559.889999999999</v>
@@ -6617,37 +6837,37 @@
         <v>3618.2</v>
       </c>
       <c r="M65">
-        <v>483.0930720000001</v>
+        <v>473.943582</v>
       </c>
       <c r="N65">
-        <v>3135.106928</v>
+        <v>3144.256418</v>
       </c>
       <c r="O65">
-        <v>689.7235241599999</v>
+        <v>691.7364119599999</v>
       </c>
       <c r="P65">
-        <v>2445.38340384</v>
+        <v>2452.52000604</v>
       </c>
       <c r="Q65">
-        <v>3391.18340384</v>
+        <v>3398.32000604</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1450801645136511</v>
+        <v>0.1450163361949209</v>
       </c>
       <c r="T65">
         <v>2.291370350921962</v>
       </c>
       <c r="U65">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V65">
         <v>0.22</v>
       </c>
       <c r="W65">
-        <v>0.04118400000000001</v>
+        <v>0.040404</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6875,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>7.489654084710201</v>
+        <v>7.634242001403449</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +6886,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.07948560376543735</v>
+        <v>0.07896284760356415</v>
       </c>
       <c r="C66">
-        <v>5709.776843155585</v>
+        <v>5748.317560345426</v>
       </c>
       <c r="D66">
-        <v>13211.99684315558</v>
+        <v>13250.53756034542</v>
       </c>
       <c r="E66">
         <v>5705.119999999999</v>
@@ -6699,37 +6919,37 @@
         <v>3618.2</v>
       </c>
       <c r="M66">
-        <v>490.761216</v>
+        <v>481.466496</v>
       </c>
       <c r="N66">
-        <v>3127.438784</v>
+        <v>3136.733504</v>
       </c>
       <c r="O66">
-        <v>688.03653248</v>
+        <v>690.08137088</v>
       </c>
       <c r="P66">
-        <v>2439.40225152</v>
+        <v>2446.65213312</v>
       </c>
       <c r="Q66">
-        <v>3385.20225152</v>
+        <v>3392.452133119999</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1475773437928815</v>
+        <v>0.1475119100099004</v>
       </c>
       <c r="T66">
         <v>2.349004850113173</v>
       </c>
       <c r="U66">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V66">
         <v>0.22</v>
       </c>
       <c r="W66">
-        <v>0.04118400000000001</v>
+        <v>0.040404</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6957,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>7.372628239636605</v>
+        <v>7.514956970131521</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +6968,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.0793456266608238</v>
+        <v>0.07881513081500753</v>
       </c>
       <c r="C67">
-        <v>5575.378980141031</v>
+        <v>5614.58624672563</v>
       </c>
       <c r="D67">
-        <v>13222.82898014103</v>
+        <v>13262.03624672563</v>
       </c>
       <c r="E67">
         <v>5850.35</v>
@@ -6781,37 +7001,37 @@
         <v>3618.2</v>
       </c>
       <c r="M67">
-        <v>498.4293600000001</v>
+        <v>488.9894100000001</v>
       </c>
       <c r="N67">
-        <v>3119.77064</v>
+        <v>3129.21059</v>
       </c>
       <c r="O67">
-        <v>686.3495408</v>
+        <v>688.4263298</v>
       </c>
       <c r="P67">
-        <v>2433.4210992</v>
+        <v>2440.7842602</v>
       </c>
       <c r="Q67">
-        <v>3379.2210992</v>
+        <v>3386.584260199999</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1502172190309251</v>
+        <v>0.1501500880428787</v>
       </c>
       <c r="T67">
         <v>2.409932749258167</v>
       </c>
       <c r="U67">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V67">
         <v>0.22</v>
       </c>
       <c r="W67">
-        <v>0.04118400000000001</v>
+        <v>0.040404</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +7039,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>7.259203189796041</v>
+        <v>7.399342247514111</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +7050,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.07920564955621026</v>
+        <v>0.07866741402645092</v>
       </c>
       <c r="C68">
-        <v>5440.998893617305</v>
+        <v>5480.874907333531</v>
       </c>
       <c r="D68">
-        <v>13233.67889361731</v>
+        <v>13273.55490733353</v>
       </c>
       <c r="E68">
         <v>5995.58</v>
@@ -6863,37 +7083,37 @@
         <v>3618.2</v>
       </c>
       <c r="M68">
-        <v>506.0975040000001</v>
+        <v>496.5123240000001</v>
       </c>
       <c r="N68">
-        <v>3112.102496</v>
+        <v>3121.687676</v>
       </c>
       <c r="O68">
-        <v>684.6625491199999</v>
+        <v>686.7712887199999</v>
       </c>
       <c r="P68">
-        <v>2427.43994688</v>
+        <v>2434.91638728</v>
       </c>
       <c r="Q68">
-        <v>3373.239946879999</v>
+        <v>3380.716387279999</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1530123810476772</v>
+        <v>0.1529434530189733</v>
       </c>
       <c r="T68">
         <v>2.474444642470515</v>
       </c>
       <c r="U68">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V68">
         <v>0.22</v>
       </c>
       <c r="W68">
-        <v>0.04118400000000001</v>
+        <v>0.040404</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +7121,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>7.149215262677918</v>
+        <v>7.287231001339655</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +7132,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.07906567245159671</v>
+        <v>0.0785196972378943</v>
       </c>
       <c r="C69">
-        <v>5306.636627379528</v>
+        <v>5347.183594259854</v>
       </c>
       <c r="D69">
-        <v>13244.54662737953</v>
+        <v>13285.09359425985</v>
       </c>
       <c r="E69">
         <v>6140.809999999999</v>
@@ -6945,37 +7165,37 @@
         <v>3618.2</v>
       </c>
       <c r="M69">
-        <v>513.7656480000001</v>
+        <v>504.035238</v>
       </c>
       <c r="N69">
-        <v>3104.434352</v>
+        <v>3114.164762</v>
       </c>
       <c r="O69">
-        <v>682.97555744</v>
+        <v>685.11624764</v>
       </c>
       <c r="P69">
-        <v>2421.45879456</v>
+        <v>2429.04851436</v>
       </c>
       <c r="Q69">
-        <v>3367.25879456</v>
+        <v>3374.84851436</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1559769468230203</v>
+        <v>0.155906112842104</v>
       </c>
       <c r="T69">
         <v>2.542866347392701</v>
       </c>
       <c r="U69">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V69">
         <v>0.22</v>
       </c>
       <c r="W69">
-        <v>0.04118400000000001</v>
+        <v>0.040404</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +7203,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>7.042510557264817</v>
+        <v>7.178466359528616</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +7214,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.07892569534698315</v>
+        <v>0.07837198044933769</v>
       </c>
       <c r="C70">
-        <v>5172.292225366791</v>
+        <v>5213.512359776605</v>
       </c>
       <c r="D70">
-        <v>13255.43222536679</v>
+        <v>13296.65235977661</v>
       </c>
       <c r="E70">
         <v>6286.040000000001</v>
@@ -7027,37 +7247,37 @@
         <v>3618.2</v>
       </c>
       <c r="M70">
-        <v>521.4337920000002</v>
+        <v>511.5581520000001</v>
       </c>
       <c r="N70">
-        <v>3096.766208</v>
+        <v>3106.641848</v>
       </c>
       <c r="O70">
-        <v>681.2885657599999</v>
+        <v>683.4612065599999</v>
       </c>
       <c r="P70">
-        <v>2415.47764224</v>
+        <v>2423.18064144</v>
       </c>
       <c r="Q70">
-        <v>3361.277642239999</v>
+        <v>3368.98064144</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1591267979593224</v>
+        <v>0.1590539389041803</v>
       </c>
       <c r="T70">
         <v>2.615564408872524</v>
       </c>
       <c r="U70">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V70">
         <v>0.22</v>
       </c>
       <c r="W70">
-        <v>0.04118400000000001</v>
+        <v>0.040404</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7285,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>6.938944225540332</v>
+        <v>7.072900677770841</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7296,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.0787857182423696</v>
+        <v>0.07822426366078108</v>
       </c>
       <c r="C71">
-        <v>5037.965731662765</v>
+        <v>5079.861256337872</v>
       </c>
       <c r="D71">
-        <v>13266.33573166277</v>
+        <v>13308.23125633787</v>
       </c>
       <c r="E71">
         <v>6431.27</v>
@@ -7109,37 +7329,37 @@
         <v>3618.2</v>
       </c>
       <c r="M71">
-        <v>529.1019360000001</v>
+        <v>519.0810660000001</v>
       </c>
       <c r="N71">
-        <v>3089.098064</v>
+        <v>3099.118934</v>
       </c>
       <c r="O71">
-        <v>679.60157408</v>
+        <v>681.8061654799999</v>
       </c>
       <c r="P71">
-        <v>2409.49648992</v>
+        <v>2417.31276852</v>
       </c>
       <c r="Q71">
-        <v>3355.29648992</v>
+        <v>3363.11276852</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1624798652979665</v>
+        <v>0.1624048505186487</v>
       </c>
       <c r="T71">
         <v>2.692952667867175</v>
       </c>
       <c r="U71">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V71">
         <v>0.22</v>
       </c>
       <c r="W71">
-        <v>0.04118400000000001</v>
+        <v>0.040404</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7367,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>6.838379816474531</v>
+        <v>6.970394870846627</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7378,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07984694113775605</v>
+        <v>0.07807654687222446</v>
       </c>
       <c r="C72">
-        <v>4810.516592521237</v>
+        <v>4946.230336580616</v>
       </c>
       <c r="D72">
-        <v>13184.11659252124</v>
+        <v>13319.83033658062</v>
       </c>
       <c r="E72">
         <v>6576.5</v>
@@ -7191,45 +7411,45 @@
         <v>3618.2</v>
       </c>
       <c r="M72">
-        <v>559.1355000000001</v>
+        <v>526.6039800000001</v>
       </c>
       <c r="N72">
-        <v>3059.064499999999</v>
+        <v>3091.59602</v>
       </c>
       <c r="O72">
-        <v>672.9941899999999</v>
+        <v>680.1511244</v>
       </c>
       <c r="P72">
-        <v>2386.07031</v>
+        <v>2411.4448956</v>
       </c>
       <c r="Q72">
-        <v>3331.870309999999</v>
+        <v>3357.2448956</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1660564704591868</v>
+        <v>0.1659791562407482</v>
       </c>
       <c r="T72">
         <v>2.775500144128135</v>
       </c>
       <c r="U72">
-        <v>0.05500000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V72">
         <v>0.22</v>
       </c>
       <c r="W72">
-        <v>0.04290000000000001</v>
+        <v>0.040404</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y72">
-        <v>6.471061129189613</v>
+        <v>6.870817801263104</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7460,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.07972412403314251</v>
+        <v>0.07792883008366785</v>
       </c>
       <c r="C73">
-        <v>4674.749766666369</v>
+        <v>4812.619653325461</v>
       </c>
       <c r="D73">
-        <v>13193.57976666637</v>
+        <v>13331.44965332546</v>
       </c>
       <c r="E73">
         <v>6721.73</v>
@@ -7273,45 +7493,45 @@
         <v>3618.2</v>
       </c>
       <c r="M73">
-        <v>567.1231500000001</v>
+        <v>534.1268940000001</v>
       </c>
       <c r="N73">
-        <v>3051.076849999999</v>
+        <v>3084.073106</v>
       </c>
       <c r="O73">
-        <v>671.2369069999999</v>
+        <v>678.4960833199999</v>
       </c>
       <c r="P73">
-        <v>2379.839942999999</v>
+        <v>2405.57702268</v>
       </c>
       <c r="Q73">
-        <v>3325.639942999999</v>
+        <v>3351.37702268</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1698797380453189</v>
+        <v>0.1697999658057512</v>
       </c>
       <c r="T73">
         <v>2.863740549786402</v>
       </c>
       <c r="U73">
-        <v>0.05500000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V73">
         <v>0.22</v>
       </c>
       <c r="W73">
-        <v>0.04290000000000001</v>
+        <v>0.040404</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y73">
-        <v>6.379919423144689</v>
+        <v>6.774045719555172</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7542,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.07960130692852896</v>
+        <v>0.07873583329511125</v>
       </c>
       <c r="C74">
-        <v>4538.99653534975</v>
+        <v>4604.157222647918</v>
       </c>
       <c r="D74">
-        <v>13203.05653534975</v>
+        <v>13268.21722264792</v>
       </c>
       <c r="E74">
         <v>6866.959999999999</v>
@@ -7355,37 +7575,37 @@
         <v>3618.2</v>
       </c>
       <c r="M74">
-        <v>575.1108</v>
+        <v>559.42596</v>
       </c>
       <c r="N74">
-        <v>3043.0892</v>
+        <v>3058.77404</v>
       </c>
       <c r="O74">
-        <v>669.4796239999999</v>
+        <v>672.9302888</v>
       </c>
       <c r="P74">
-        <v>2373.609576</v>
+        <v>2385.8437512</v>
       </c>
       <c r="Q74">
-        <v>3319.409576</v>
+        <v>3331.6437512</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1739760961733177</v>
+        <v>0.173893690339683</v>
       </c>
       <c r="T74">
         <v>2.958283841563118</v>
       </c>
       <c r="U74">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V74">
         <v>0.22</v>
       </c>
       <c r="W74">
-        <v>0.04290000000000001</v>
+        <v>0.04173</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7613,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>6.29130943115657</v>
+        <v>6.467701284366567</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7624,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.07947848982391539</v>
+        <v>0.07860137650655463</v>
       </c>
       <c r="C75">
-        <v>4403.256927886754</v>
+        <v>4469.420855980166</v>
       </c>
       <c r="D75">
-        <v>13212.54692788675</v>
+        <v>13278.71085598017</v>
       </c>
       <c r="E75">
         <v>7012.189999999999</v>
@@ -7437,37 +7657,37 @@
         <v>3618.2</v>
       </c>
       <c r="M75">
-        <v>583.0984500000001</v>
+        <v>567.1957650000001</v>
       </c>
       <c r="N75">
-        <v>3035.10155</v>
+        <v>3051.004235</v>
       </c>
       <c r="O75">
-        <v>667.722341</v>
+        <v>671.2209316999999</v>
       </c>
       <c r="P75">
-        <v>2367.379209</v>
+        <v>2379.7833033</v>
       </c>
       <c r="Q75">
-        <v>3313.179209</v>
+        <v>3325.5833033</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1783758882367237</v>
+        <v>0.1782906537279801</v>
       </c>
       <c r="T75">
         <v>3.059830340138109</v>
       </c>
       <c r="U75">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V75">
         <v>0.22</v>
       </c>
       <c r="W75">
-        <v>0.04290000000000001</v>
+        <v>0.04173</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7695,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>6.205127110181822</v>
+        <v>6.379102636635518</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7706,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.07935567271930186</v>
+        <v>0.07846691971799802</v>
       </c>
       <c r="C76">
-        <v>4267.530973677094</v>
+        <v>4334.70110096369</v>
       </c>
       <c r="D76">
-        <v>13222.05097367709</v>
+        <v>13289.22110096369</v>
       </c>
       <c r="E76">
         <v>7157.42</v>
@@ -7519,37 +7739,37 @@
         <v>3618.2</v>
       </c>
       <c r="M76">
-        <v>591.0861000000001</v>
+        <v>574.9655700000001</v>
       </c>
       <c r="N76">
-        <v>3027.1139</v>
+        <v>3043.23443</v>
       </c>
       <c r="O76">
-        <v>665.965058</v>
+        <v>669.5115745999999</v>
       </c>
       <c r="P76">
-        <v>2361.148842</v>
+        <v>2373.722855399999</v>
       </c>
       <c r="Q76">
-        <v>3306.948842</v>
+        <v>3319.5228554</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1831141258434686</v>
+        <v>0.1830258450692231</v>
       </c>
       <c r="T76">
         <v>3.169188107834253</v>
       </c>
       <c r="U76">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V76">
         <v>0.22</v>
       </c>
       <c r="W76">
-        <v>0.04290000000000001</v>
+        <v>0.04173</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7777,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>6.12127404112531</v>
+        <v>6.292898546951253</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7788,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.07923285561468831</v>
+        <v>0.0783324629294414</v>
       </c>
       <c r="C77">
-        <v>4131.818702205148</v>
+        <v>4199.997997074655</v>
       </c>
       <c r="D77">
-        <v>13231.56870220515</v>
+        <v>13299.74799707466</v>
       </c>
       <c r="E77">
         <v>7302.65</v>
@@ -7601,37 +7821,37 @@
         <v>3618.2</v>
       </c>
       <c r="M77">
-        <v>599.0737500000001</v>
+        <v>582.7353750000001</v>
       </c>
       <c r="N77">
-        <v>3019.12625</v>
+        <v>3035.464625</v>
       </c>
       <c r="O77">
-        <v>664.207775</v>
+        <v>667.8022174999999</v>
       </c>
       <c r="P77">
-        <v>2354.918475</v>
+        <v>2367.6624075</v>
       </c>
       <c r="Q77">
-        <v>3300.718475</v>
+        <v>3313.4624075</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1882314224587532</v>
+        <v>0.1881398517177656</v>
       </c>
       <c r="T77">
         <v>3.287294496946088</v>
       </c>
       <c r="U77">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V77">
         <v>0.22</v>
       </c>
       <c r="W77">
-        <v>0.04290000000000001</v>
+        <v>0.04173</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7859,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>6.039657053910306</v>
+        <v>6.208993232991904</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +7870,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.07911003851007475</v>
+        <v>0.07819800614088479</v>
       </c>
       <c r="C78">
-        <v>3996.120143040245</v>
+        <v>4065.31158391439</v>
       </c>
       <c r="D78">
-        <v>13241.10014304024</v>
+        <v>13310.29158391439</v>
       </c>
       <c r="E78">
         <v>7447.879999999999</v>
@@ -7683,37 +7903,37 @@
         <v>3618.2</v>
       </c>
       <c r="M78">
-        <v>607.0614</v>
+        <v>590.50518</v>
       </c>
       <c r="N78">
-        <v>3011.1386</v>
+        <v>3027.69482</v>
       </c>
       <c r="O78">
-        <v>662.4504919999999</v>
+        <v>666.0928603999999</v>
       </c>
       <c r="P78">
-        <v>2348.688108</v>
+        <v>2361.6019596</v>
       </c>
       <c r="Q78">
-        <v>3294.488108</v>
+        <v>3307.4019596</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1937751604586448</v>
+        <v>0.19368002558702</v>
       </c>
       <c r="T78">
         <v>3.415243085150577</v>
       </c>
       <c r="U78">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V78">
         <v>0.22</v>
       </c>
       <c r="W78">
-        <v>0.04290000000000001</v>
+        <v>0.04173</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7941,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>5.960187882148329</v>
+        <v>6.127295953610432</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +7952,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.0789872214054612</v>
+        <v>0.07806354935232818</v>
       </c>
       <c r="C79">
-        <v>3860.435325836976</v>
+        <v>3930.64190120992</v>
       </c>
       <c r="D79">
-        <v>13250.64532583698</v>
+        <v>13320.85190120992</v>
       </c>
       <c r="E79">
         <v>7593.110000000001</v>
@@ -7765,37 +7985,37 @@
         <v>3618.2</v>
       </c>
       <c r="M79">
-        <v>615.0490500000001</v>
+        <v>598.2749850000001</v>
       </c>
       <c r="N79">
-        <v>3003.15095</v>
+        <v>3019.925015</v>
       </c>
       <c r="O79">
-        <v>660.6932089999999</v>
+        <v>664.3835032999999</v>
       </c>
       <c r="P79">
-        <v>2342.457741</v>
+        <v>2355.5415117</v>
       </c>
       <c r="Q79">
-        <v>3288.257740999999</v>
+        <v>3301.3415117</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.19980096263244</v>
+        <v>0.1997019537057747</v>
       </c>
       <c r="T79">
         <v>3.55431763754676</v>
       </c>
       <c r="U79">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V79">
         <v>0.22</v>
       </c>
       <c r="W79">
-        <v>0.04290000000000001</v>
+        <v>0.04173</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +8023,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>5.882782844717831</v>
+        <v>6.04772068148562</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +8034,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.07886440430084765</v>
+        <v>0.07792909256377158</v>
       </c>
       <c r="C80">
-        <v>3724.764280335507</v>
+        <v>3795.988988814433</v>
       </c>
       <c r="D80">
-        <v>13260.20428033551</v>
+        <v>13331.42898881443</v>
       </c>
       <c r="E80">
         <v>7738.34</v>
@@ -7847,37 +8067,37 @@
         <v>3618.2</v>
       </c>
       <c r="M80">
-        <v>623.0367000000001</v>
+        <v>606.0447900000001</v>
       </c>
       <c r="N80">
-        <v>2995.1633</v>
+        <v>3012.15521</v>
       </c>
       <c r="O80">
-        <v>658.935926</v>
+        <v>662.6741462</v>
       </c>
       <c r="P80">
-        <v>2336.227374</v>
+        <v>2349.4810638</v>
       </c>
       <c r="Q80">
-        <v>3282.027373999999</v>
+        <v>3295.2810638</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.206374565003853</v>
+        <v>0.2062713298353253</v>
       </c>
       <c r="T80">
         <v>3.706035331069869</v>
       </c>
       <c r="U80">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V80">
         <v>0.22</v>
       </c>
       <c r="W80">
-        <v>0.04290000000000001</v>
+        <v>0.04173</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +8105,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>5.807362551836833</v>
+        <v>5.970185800953753</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +8116,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.0787415871962341</v>
+        <v>0.07779463577521496</v>
       </c>
       <c r="C81">
-        <v>3589.107036361882</v>
+        <v>3661.352886707806</v>
       </c>
       <c r="D81">
-        <v>13269.77703636188</v>
+        <v>13342.02288670781</v>
       </c>
       <c r="E81">
         <v>7883.57</v>
@@ -7929,37 +8149,37 @@
         <v>3618.2</v>
       </c>
       <c r="M81">
-        <v>631.0243500000001</v>
+        <v>613.8145950000001</v>
       </c>
       <c r="N81">
-        <v>2987.17565</v>
+        <v>3004.385405</v>
       </c>
       <c r="O81">
-        <v>657.178643</v>
+        <v>660.9647891</v>
       </c>
       <c r="P81">
-        <v>2329.997007</v>
+        <v>2343.4206159</v>
       </c>
       <c r="Q81">
-        <v>3275.797007</v>
+        <v>3289.2206159</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2135742247439719</v>
+        <v>0.213466360834357</v>
       </c>
       <c r="T81">
         <v>3.872202328738036</v>
       </c>
       <c r="U81">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V81">
         <v>0.22</v>
       </c>
       <c r="W81">
-        <v>0.04290000000000001</v>
+        <v>0.04173</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +8187,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>5.733851633459151</v>
+        <v>5.894613828789782</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +8198,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.07861877009162055</v>
+        <v>0.07766017898665833</v>
       </c>
       <c r="C82">
-        <v>3453.463623828326</v>
+        <v>3526.73363499709</v>
       </c>
       <c r="D82">
-        <v>13279.36362382833</v>
+        <v>13352.63363499709</v>
       </c>
       <c r="E82">
         <v>8028.800000000001</v>
@@ -8011,37 +8231,37 @@
         <v>3618.2</v>
       </c>
       <c r="M82">
-        <v>639.0120000000002</v>
+        <v>621.5844000000002</v>
       </c>
       <c r="N82">
-        <v>2979.188</v>
+        <v>2996.6156</v>
       </c>
       <c r="O82">
-        <v>655.4213599999999</v>
+        <v>659.2554319999999</v>
       </c>
       <c r="P82">
-        <v>2323.76664</v>
+        <v>2337.360168</v>
       </c>
       <c r="Q82">
-        <v>3269.56664</v>
+        <v>3283.160167999999</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2214938504581028</v>
+        <v>0.2213808949332917</v>
       </c>
       <c r="T82">
         <v>4.05498602617302</v>
       </c>
       <c r="U82">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V82">
         <v>0.22</v>
       </c>
       <c r="W82">
-        <v>0.04290000000000001</v>
+        <v>0.04173</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8269,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>5.662178488040912</v>
+        <v>5.820931155929909</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8280,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07944365298700701</v>
+        <v>0.07752572219810173</v>
       </c>
       <c r="C83">
-        <v>3244.111343909261</v>
+        <v>3392.131273917024</v>
       </c>
       <c r="D83">
-        <v>13215.24134390926</v>
+        <v>13363.26127391703</v>
       </c>
       <c r="E83">
         <v>8174.030000000001</v>
@@ -8093,45 +8313,45 @@
         <v>3618.2</v>
       </c>
       <c r="M83">
-        <v>664.6450950000002</v>
+        <v>629.3542050000001</v>
       </c>
       <c r="N83">
-        <v>2953.554905</v>
+        <v>2988.845795</v>
       </c>
       <c r="O83">
-        <v>649.7820790999999</v>
+        <v>657.5460748999999</v>
       </c>
       <c r="P83">
-        <v>2303.7728259</v>
+        <v>2331.2997201</v>
       </c>
       <c r="Q83">
-        <v>3249.5728259</v>
+        <v>3277.0997201</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2302471209842474</v>
+        <v>0.230128537884746</v>
       </c>
       <c r="T83">
         <v>4.257010112811686</v>
       </c>
       <c r="U83">
-        <v>0.05650000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V83">
         <v>0.22</v>
       </c>
       <c r="W83">
-        <v>0.04407000000000001</v>
+        <v>0.04173</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y83">
-        <v>5.443807570715614</v>
+        <v>5.749067808325837</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8362,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07933253588239345</v>
+        <v>0.07739126540954511</v>
       </c>
       <c r="C84">
-        <v>3107.482919146334</v>
+        <v>3257.545843830556</v>
       </c>
       <c r="D84">
-        <v>13223.84291914633</v>
+        <v>13373.90584383056</v>
       </c>
       <c r="E84">
         <v>8319.26</v>
@@ -8175,45 +8395,45 @@
         <v>3618.2</v>
       </c>
       <c r="M84">
-        <v>672.8505900000001</v>
+        <v>637.1240100000001</v>
       </c>
       <c r="N84">
-        <v>2945.34941</v>
+        <v>2981.07599</v>
       </c>
       <c r="O84">
-        <v>647.9768702</v>
+        <v>655.8367178</v>
       </c>
       <c r="P84">
-        <v>2297.3725398</v>
+        <v>2325.2392722</v>
       </c>
       <c r="Q84">
-        <v>3243.1725398</v>
+        <v>3271.0392722</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2399729771244081</v>
+        <v>0.2398481411641396</v>
       </c>
       <c r="T84">
         <v>4.481481320187982</v>
       </c>
       <c r="U84">
-        <v>0.05650000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V84">
         <v>0.22</v>
       </c>
       <c r="W84">
-        <v>0.04407000000000001</v>
+        <v>0.04173</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y84">
-        <v>5.377419673511766</v>
+        <v>5.678957225297473</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8444,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.0792214187777799</v>
+        <v>0.07725680862098849</v>
       </c>
       <c r="C85">
-        <v>2970.865698913529</v>
+        <v>3122.977385229322</v>
       </c>
       <c r="D85">
-        <v>13232.45569891353</v>
+        <v>13384.56738522932</v>
       </c>
       <c r="E85">
         <v>8464.49</v>
@@ -8257,45 +8477,45 @@
         <v>3618.2</v>
       </c>
       <c r="M85">
-        <v>681.0560850000002</v>
+        <v>644.8938150000001</v>
       </c>
       <c r="N85">
-        <v>2937.143915</v>
+        <v>2973.306184999999</v>
       </c>
       <c r="O85">
-        <v>646.1716613</v>
+        <v>654.1273606999999</v>
       </c>
       <c r="P85">
-        <v>2290.9722537</v>
+        <v>2319.1788243</v>
       </c>
       <c r="Q85">
-        <v>3236.7722537</v>
+        <v>3264.978824299999</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2508430516339994</v>
+        <v>0.2507112271822854</v>
       </c>
       <c r="T85">
         <v>4.732360904902666</v>
       </c>
       <c r="U85">
-        <v>0.05650000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V85">
         <v>0.22</v>
       </c>
       <c r="W85">
-        <v>0.04407000000000001</v>
+        <v>0.04173</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y85">
-        <v>5.312631484674275</v>
+        <v>5.610536053908346</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8526,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.07911030167316635</v>
+        <v>0.0776465118324319</v>
       </c>
       <c r="C86">
-        <v>2834.259705117878</v>
+        <v>2946.8931327296</v>
       </c>
       <c r="D86">
-        <v>13241.07970511788</v>
+        <v>13353.7131327296</v>
       </c>
       <c r="E86">
         <v>8609.719999999999</v>
@@ -8339,37 +8559,37 @@
         <v>3618.2</v>
       </c>
       <c r="M86">
-        <v>689.2615800000001</v>
+        <v>662.423076</v>
       </c>
       <c r="N86">
-        <v>2928.938419999999</v>
+        <v>2955.776924</v>
       </c>
       <c r="O86">
-        <v>644.3664523999998</v>
+        <v>650.2709232799999</v>
       </c>
       <c r="P86">
-        <v>2284.5719676</v>
+        <v>2305.50600072</v>
       </c>
       <c r="Q86">
-        <v>3230.3719676</v>
+        <v>3251.30600072</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2630718854572897</v>
+        <v>0.2629321989526993</v>
       </c>
       <c r="T86">
         <v>5.014600437706682</v>
       </c>
       <c r="U86">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V86">
         <v>0.22</v>
       </c>
       <c r="W86">
-        <v>0.04407000000000001</v>
+        <v>0.04235400000000001</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8597,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>5.249385871761485</v>
+        <v>5.462068172274844</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8608,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.0789991845685528</v>
+        <v>0.07751829504387531</v>
       </c>
       <c r="C87">
-        <v>2697.664959723563</v>
+        <v>2811.798818896388</v>
       </c>
       <c r="D87">
-        <v>13249.71495972356</v>
+        <v>13363.84881889639</v>
       </c>
       <c r="E87">
         <v>8754.949999999999</v>
@@ -8421,37 +8641,37 @@
         <v>3618.2</v>
       </c>
       <c r="M87">
-        <v>697.467075</v>
+        <v>670.309065</v>
       </c>
       <c r="N87">
-        <v>2920.732925</v>
+        <v>2947.890935</v>
       </c>
       <c r="O87">
-        <v>642.5612434999999</v>
+        <v>648.5360057</v>
       </c>
       <c r="P87">
-        <v>2278.1716815</v>
+        <v>2299.3549293</v>
       </c>
       <c r="Q87">
-        <v>3223.9716815</v>
+        <v>3245.1549293</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2769312304570186</v>
+        <v>0.2767826336258352</v>
       </c>
       <c r="T87">
         <v>5.334471908217903</v>
       </c>
       <c r="U87">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V87">
         <v>0.22</v>
       </c>
       <c r="W87">
-        <v>0.04407000000000001</v>
+        <v>0.04235400000000001</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8679,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>5.187628390917234</v>
+        <v>5.397808546718669</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8690,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.07888806746393925</v>
+        <v>0.07739007825531868</v>
       </c>
       <c r="C88">
-        <v>2561.081484752087</v>
+        <v>2676.719903052879</v>
       </c>
       <c r="D88">
-        <v>13258.36148475209</v>
+        <v>13373.99990305288</v>
       </c>
       <c r="E88">
         <v>8900.18</v>
@@ -8503,37 +8723,37 @@
         <v>3618.2</v>
       </c>
       <c r="M88">
-        <v>705.6725700000002</v>
+        <v>678.1950540000001</v>
       </c>
       <c r="N88">
-        <v>2912.52743</v>
+        <v>2940.004946</v>
       </c>
       <c r="O88">
-        <v>640.7560345999999</v>
+        <v>646.8010881199999</v>
       </c>
       <c r="P88">
-        <v>2271.7713954</v>
+        <v>2293.20385788</v>
       </c>
       <c r="Q88">
-        <v>3217.571395399999</v>
+        <v>3239.003857879999</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2927704818852803</v>
+        <v>0.2926117018237048</v>
       </c>
       <c r="T88">
         <v>5.700039303087871</v>
       </c>
       <c r="U88">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V88">
         <v>0.22</v>
       </c>
       <c r="W88">
-        <v>0.04407000000000001</v>
+        <v>0.04235400000000001</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8761,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>5.12730713055773</v>
+        <v>5.335043331059148</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8772,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.07877695035932569</v>
+        <v>0.07726186146676207</v>
       </c>
       <c r="C89">
-        <v>2424.509302282489</v>
+        <v>2541.656420314357</v>
       </c>
       <c r="D89">
-        <v>13267.01930228249</v>
+        <v>13384.16642031436</v>
       </c>
       <c r="E89">
         <v>9045.41</v>
@@ -8585,37 +8805,37 @@
         <v>3618.2</v>
       </c>
       <c r="M89">
-        <v>713.8780650000001</v>
+        <v>686.0810430000001</v>
       </c>
       <c r="N89">
-        <v>2904.321935</v>
+        <v>2932.118957</v>
       </c>
       <c r="O89">
-        <v>638.9508257</v>
+        <v>645.0661705399999</v>
       </c>
       <c r="P89">
-        <v>2265.3711093</v>
+        <v>2287.05278646</v>
       </c>
       <c r="Q89">
-        <v>3211.1711093</v>
+        <v>3232.85278646</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3110465412255823</v>
+        <v>0.3108760112827851</v>
       </c>
       <c r="T89">
         <v>6.12184783563014</v>
       </c>
       <c r="U89">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V89">
         <v>0.22</v>
       </c>
       <c r="W89">
-        <v>0.04407000000000001</v>
+        <v>0.04235400000000001</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8843,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>5.068372565838676</v>
+        <v>5.273720993920538</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +8854,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.07866583325471216</v>
+        <v>0.07713364467820547</v>
       </c>
       <c r="C90">
-        <v>2287.948434451504</v>
+        <v>2406.608405902962</v>
       </c>
       <c r="D90">
-        <v>13275.6884344515</v>
+        <v>13394.34840590296</v>
       </c>
       <c r="E90">
         <v>9190.639999999999</v>
@@ -8667,37 +8887,37 @@
         <v>3618.2</v>
       </c>
       <c r="M90">
-        <v>722.0835600000001</v>
+        <v>693.9670320000001</v>
       </c>
       <c r="N90">
-        <v>2896.11644</v>
+        <v>2924.232968</v>
       </c>
       <c r="O90">
-        <v>637.1456168</v>
+        <v>643.3312529599999</v>
       </c>
       <c r="P90">
-        <v>2258.9708232</v>
+        <v>2280.90171504</v>
       </c>
       <c r="Q90">
-        <v>3204.7708232</v>
+        <v>3226.70171504</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3323686104559346</v>
+        <v>0.3321843723183788</v>
       </c>
       <c r="T90">
         <v>6.61395779026279</v>
       </c>
       <c r="U90">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V90">
         <v>0.22</v>
       </c>
       <c r="W90">
-        <v>0.04407000000000001</v>
+        <v>0.04235400000000001</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8925,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>5.010777423045055</v>
+        <v>5.21379234626235</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +8936,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.0785547161500986</v>
+        <v>0.07700542788964884</v>
       </c>
       <c r="C91">
-        <v>2151.398903453781</v>
+        <v>2271.575895148091</v>
       </c>
       <c r="D91">
-        <v>13284.36890345378</v>
+        <v>13404.54589514809</v>
       </c>
       <c r="E91">
         <v>9335.869999999999</v>
@@ -8749,37 +8969,37 @@
         <v>3618.2</v>
       </c>
       <c r="M91">
-        <v>730.2890550000001</v>
+        <v>701.853021</v>
       </c>
       <c r="N91">
-        <v>2887.910945</v>
+        <v>2916.346979</v>
       </c>
       <c r="O91">
-        <v>635.3404078999999</v>
+        <v>641.59633538</v>
       </c>
       <c r="P91">
-        <v>2252.570537099999</v>
+        <v>2274.75064362</v>
       </c>
       <c r="Q91">
-        <v>3198.3705371</v>
+        <v>3220.55064362</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3575674195463509</v>
+        <v>0.3573669808149895</v>
       </c>
       <c r="T91">
         <v>7.195542282101373</v>
       </c>
       <c r="U91">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V91">
         <v>0.22</v>
       </c>
       <c r="W91">
-        <v>0.04407000000000001</v>
+        <v>0.04235400000000001</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +9007,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>4.9544765531232</v>
+        <v>5.155210409787493</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +9018,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.07844359904548505</v>
+        <v>0.07687721110109223</v>
       </c>
       <c r="C92">
-        <v>2014.860731542036</v>
+        <v>2136.558923486817</v>
       </c>
       <c r="D92">
-        <v>13293.06073154204</v>
+        <v>13414.75892348682</v>
       </c>
       <c r="E92">
         <v>9481.1</v>
@@ -8831,37 +9051,37 @@
         <v>3618.2</v>
       </c>
       <c r="M92">
-        <v>738.4945500000001</v>
+        <v>709.7390100000001</v>
       </c>
       <c r="N92">
-        <v>2879.705449999999</v>
+        <v>2908.46099</v>
       </c>
       <c r="O92">
-        <v>633.5351989999999</v>
+        <v>639.8614177999999</v>
       </c>
       <c r="P92">
-        <v>2246.170251</v>
+        <v>2268.5995722</v>
       </c>
       <c r="Q92">
-        <v>3191.970251</v>
+        <v>3214.3995722</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.3878059904548505</v>
+        <v>0.3875861110109223</v>
       </c>
       <c r="T92">
         <v>7.893443672307675</v>
       </c>
       <c r="U92">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V92">
         <v>0.22</v>
       </c>
       <c r="W92">
-        <v>0.04407000000000001</v>
+        <v>0.04235400000000001</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +9089,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>4.899426813644054</v>
+        <v>5.097930294123186</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +9100,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.0783324819408715</v>
+        <v>0.07674899431253562</v>
       </c>
       <c r="C93">
-        <v>1878.333941027277</v>
+        <v>2001.557526464294</v>
       </c>
       <c r="D93">
-        <v>13301.76394102728</v>
+        <v>13424.98752646429</v>
       </c>
       <c r="E93">
         <v>9626.33</v>
@@ -8913,37 +9133,37 @@
         <v>3618.2</v>
       </c>
       <c r="M93">
-        <v>746.7000450000002</v>
+        <v>717.6249990000001</v>
       </c>
       <c r="N93">
-        <v>2871.499955</v>
+        <v>2900.575001</v>
       </c>
       <c r="O93">
-        <v>631.7299901</v>
+        <v>638.1265002199999</v>
       </c>
       <c r="P93">
-        <v>2239.7699649</v>
+        <v>2262.44850078</v>
       </c>
       <c r="Q93">
-        <v>3185.5699649</v>
+        <v>3208.24850078</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4247642437874612</v>
+        <v>0.4245206034726181</v>
       </c>
       <c r="T93">
         <v>8.746434260337599</v>
       </c>
       <c r="U93">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V93">
         <v>0.22</v>
       </c>
       <c r="W93">
-        <v>0.04407000000000001</v>
+        <v>0.04235400000000001</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +9171,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>4.845586958549064</v>
+        <v>5.041909082099854</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +9182,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.07822136483625795</v>
+        <v>0.076620777523979</v>
       </c>
       <c r="C94">
-        <v>1741.818554278971</v>
+        <v>1866.571739734167</v>
       </c>
       <c r="D94">
-        <v>13310.47855427897</v>
+        <v>13435.23173973417</v>
       </c>
       <c r="E94">
         <v>9771.559999999999</v>
@@ -8995,37 +9215,37 @@
         <v>3618.2</v>
       </c>
       <c r="M94">
-        <v>754.9055400000001</v>
+        <v>725.5109880000001</v>
       </c>
       <c r="N94">
-        <v>2863.29446</v>
+        <v>2892.689012</v>
       </c>
       <c r="O94">
-        <v>629.9247811999999</v>
+        <v>636.3915826399999</v>
       </c>
       <c r="P94">
-        <v>2233.3696788</v>
+        <v>2256.29742936</v>
       </c>
       <c r="Q94">
-        <v>3179.1696788</v>
+        <v>3202.09742936</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.4709620604532246</v>
+        <v>0.4706887190497377</v>
       </c>
       <c r="T94">
         <v>9.812672495375006</v>
       </c>
       <c r="U94">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V94">
         <v>0.22</v>
       </c>
       <c r="W94">
-        <v>0.04407000000000001</v>
+        <v>0.04235400000000001</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9253,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>4.792917535086574</v>
+        <v>4.987105722511814</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9264,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.07811024773164438</v>
+        <v>0.07649256073542239</v>
       </c>
       <c r="C95">
-        <v>1605.314593725254</v>
+        <v>1731.601599058989</v>
       </c>
       <c r="D95">
-        <v>13319.20459372526</v>
+        <v>13445.49159905899</v>
       </c>
       <c r="E95">
         <v>9916.790000000001</v>
@@ -9077,37 +9297,37 @@
         <v>3618.2</v>
       </c>
       <c r="M95">
-        <v>763.1110350000001</v>
+        <v>733.3969770000002</v>
       </c>
       <c r="N95">
-        <v>2855.088965</v>
+        <v>2884.803022999999</v>
       </c>
       <c r="O95">
-        <v>628.1195723</v>
+        <v>634.6566650599999</v>
       </c>
       <c r="P95">
-        <v>2226.9693927</v>
+        <v>2250.14635794</v>
       </c>
       <c r="Q95">
-        <v>3172.7693927</v>
+        <v>3195.94635794</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.5303592533092059</v>
+        <v>0.5300477247917487</v>
       </c>
       <c r="T95">
         <v>11.18355022613738</v>
       </c>
       <c r="U95">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V95">
         <v>0.22</v>
       </c>
       <c r="W95">
-        <v>0.04407000000000001</v>
+        <v>0.04235400000000001</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9335,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>4.741380787397471</v>
+        <v>4.933480929796631</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9346,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.07799913062703084</v>
+        <v>0.07636434394686578</v>
       </c>
       <c r="C96">
-        <v>1468.822081853101</v>
+        <v>1596.647140310644</v>
       </c>
       <c r="D96">
-        <v>13327.9420818531</v>
+        <v>13455.76714031065</v>
       </c>
       <c r="E96">
         <v>10062.02</v>
@@ -9159,37 +9379,37 @@
         <v>3618.2</v>
       </c>
       <c r="M96">
-        <v>771.3165300000002</v>
+        <v>741.2829660000001</v>
       </c>
       <c r="N96">
-        <v>2846.88347</v>
+        <v>2876.917034</v>
       </c>
       <c r="O96">
-        <v>626.3143633999999</v>
+        <v>632.9217474799999</v>
       </c>
       <c r="P96">
-        <v>2220.5691066</v>
+        <v>2243.99528652</v>
       </c>
       <c r="Q96">
-        <v>3166.3691066</v>
+        <v>3189.79528652</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.6095555104505146</v>
+        <v>0.6091930657810968</v>
       </c>
       <c r="T96">
         <v>13.01138720048722</v>
       </c>
       <c r="U96">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V96">
         <v>0.22</v>
       </c>
       <c r="W96">
-        <v>0.04407000000000001</v>
+        <v>0.04235400000000001</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9417,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>4.690940566254945</v>
+        <v>4.880997090117944</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9428,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.07788801352241731</v>
+        <v>0.07623612715830917</v>
       </c>
       <c r="C97">
-        <v>1332.341041208547</v>
+        <v>1461.708399470752</v>
       </c>
       <c r="D97">
-        <v>13336.69104120855</v>
+        <v>13466.05839947075</v>
       </c>
       <c r="E97">
         <v>10207.25</v>
@@ -9241,37 +9461,37 @@
         <v>3618.2</v>
       </c>
       <c r="M97">
-        <v>779.5220250000001</v>
+        <v>749.1689550000001</v>
       </c>
       <c r="N97">
-        <v>2838.677975</v>
+        <v>2869.031045</v>
       </c>
       <c r="O97">
-        <v>624.5091544999999</v>
+        <v>631.1868298999999</v>
       </c>
       <c r="P97">
-        <v>2214.1688205</v>
+        <v>2237.8442151</v>
       </c>
       <c r="Q97">
-        <v>3159.968820499999</v>
+        <v>3183.6442151</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.7204302704483468</v>
+        <v>0.7199965431661842</v>
       </c>
       <c r="T97">
         <v>15.570358964577</v>
       </c>
       <c r="U97">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V97">
         <v>0.22</v>
       </c>
       <c r="W97">
-        <v>0.04407000000000001</v>
+        <v>0.04235400000000001</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9499,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>4.641562244504893</v>
+        <v>4.829618173379862</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9510,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.07777689641780375</v>
+        <v>0.07610791036975256</v>
       </c>
       <c r="C98">
-        <v>1195.871494396852</v>
+        <v>1326.785412631092</v>
       </c>
       <c r="D98">
-        <v>13345.45149439685</v>
+        <v>13476.36541263109</v>
       </c>
       <c r="E98">
         <v>10352.48</v>
@@ -9323,37 +9543,37 @@
         <v>3618.2</v>
       </c>
       <c r="M98">
-        <v>787.7275200000001</v>
+        <v>757.0549440000001</v>
       </c>
       <c r="N98">
-        <v>2830.472479999999</v>
+        <v>2861.145056</v>
       </c>
       <c r="O98">
-        <v>622.7039455999999</v>
+        <v>629.45191232</v>
       </c>
       <c r="P98">
-        <v>2207.7685344</v>
+        <v>2231.69314368</v>
       </c>
       <c r="Q98">
-        <v>3153.568534399999</v>
+        <v>3177.49314368</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.8867424104450931</v>
+        <v>0.8862017592438132</v>
       </c>
       <c r="T98">
         <v>19.40881661071162</v>
       </c>
       <c r="U98">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V98">
         <v>0.22</v>
       </c>
       <c r="W98">
-        <v>0.04407000000000001</v>
+        <v>0.04235400000000001</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9581,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>4.5932126377913</v>
+        <v>4.779309650740488</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9592,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.07766577931319021</v>
+        <v>0.07597969358119597</v>
       </c>
       <c r="C99">
-        <v>1059.41346408272</v>
+        <v>1191.87821599404</v>
       </c>
       <c r="D99">
-        <v>13354.22346408272</v>
+        <v>13486.68821599404</v>
       </c>
       <c r="E99">
         <v>10497.71</v>
@@ -9405,37 +9625,37 @@
         <v>3618.2</v>
       </c>
       <c r="M99">
-        <v>795.9330150000001</v>
+        <v>764.9409330000001</v>
       </c>
       <c r="N99">
-        <v>2822.266985</v>
+        <v>2853.259067</v>
       </c>
       <c r="O99">
-        <v>620.8987367</v>
+        <v>627.71699474</v>
       </c>
       <c r="P99">
-        <v>2201.3682483</v>
+        <v>2225.54207226</v>
       </c>
       <c r="Q99">
-        <v>3147.1682483</v>
+        <v>3171.34207226</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.163929310439672</v>
+        <v>1.163210452706531</v>
       </c>
       <c r="T99">
         <v>25.80624602093604</v>
       </c>
       <c r="U99">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V99">
         <v>0.22</v>
       </c>
       <c r="W99">
-        <v>0.04407000000000001</v>
+        <v>0.04235400000000001</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9663,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>4.545859930185205</v>
+        <v>4.7300384172277</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9674,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.07755466220857665</v>
+        <v>0.07585147679263934</v>
       </c>
       <c r="C100">
-        <v>922.9669729904817</v>
+        <v>1056.986845872965</v>
       </c>
       <c r="D100">
-        <v>13363.00697299048</v>
+        <v>13497.02684587296</v>
       </c>
       <c r="E100">
         <v>10642.94</v>
@@ -9487,37 +9707,37 @@
         <v>3618.2</v>
       </c>
       <c r="M100">
-        <v>804.1385100000001</v>
+        <v>772.8269220000001</v>
       </c>
       <c r="N100">
-        <v>2814.06149</v>
+        <v>2845.373078</v>
       </c>
       <c r="O100">
-        <v>619.0935277999999</v>
+        <v>625.9820771599999</v>
       </c>
       <c r="P100">
-        <v>2194.967962199999</v>
+        <v>2219.39100084</v>
       </c>
       <c r="Q100">
-        <v>3140.7679622</v>
+        <v>3165.19100084</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.718303110428831</v>
+        <v>1.717227839631965</v>
       </c>
       <c r="T100">
         <v>38.60110484138487</v>
       </c>
       <c r="U100">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V100">
         <v>0.22</v>
       </c>
       <c r="W100">
-        <v>0.04407000000000001</v>
+        <v>0.04235400000000001</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,7 +9745,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>4.499473604366989</v>
+        <v>4.681772719092722</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9756,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.0774435451039631</v>
+        <v>0.07572326000408272</v>
       </c>
       <c r="C101">
-        <v>786.532043904288</v>
+        <v>922.1113386926809</v>
       </c>
       <c r="D101">
-        <v>13371.80204390429</v>
+        <v>13507.38133869268</v>
       </c>
       <c r="E101">
         <v>10788.17</v>
@@ -9569,37 +9789,37 @@
         <v>3618.2</v>
       </c>
       <c r="M101">
-        <v>812.3440050000002</v>
+        <v>780.7129110000002</v>
       </c>
       <c r="N101">
-        <v>2805.855995</v>
+        <v>2837.487089</v>
       </c>
       <c r="O101">
-        <v>617.2883189</v>
+        <v>624.2471595799999</v>
       </c>
       <c r="P101">
-        <v>2188.5676761</v>
+        <v>2213.23992942</v>
       </c>
       <c r="Q101">
-        <v>3134.3676761</v>
+        <v>3159.03992942</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.381424510396307</v>
+        <v>3.379280000408269</v>
       </c>
       <c r="T101">
         <v>76.98568130273139</v>
       </c>
       <c r="U101">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V101">
         <v>0.22</v>
       </c>
       <c r="W101">
-        <v>0.04407000000000001</v>
+        <v>0.04235400000000001</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9607,7 +9827,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>4.454024376040049</v>
+        <v>4.634482085566534</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/norway/norway_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_metals_mining.xlsx
@@ -1498,7 +1498,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1635,22 +1635,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08841672207118731</v>
+        <v>0.0882573052826307</v>
       </c>
       <c r="C2">
-        <v>14346.41554537598</v>
+        <v>14212.32470188606</v>
       </c>
       <c r="D2">
-        <v>12553.91554537598</v>
+        <v>12565.05470188606</v>
       </c>
       <c r="E2">
-        <v>-3589.6</v>
+        <v>-3444.37</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>145.23</v>
       </c>
       <c r="G2">
         <v>1792.5</v>
@@ -1671,28 +1671,28 @@
         <v>3618.2</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>7.305069</v>
       </c>
       <c r="N2">
-        <v>3618.2</v>
+        <v>3610.894931</v>
       </c>
       <c r="O2">
-        <v>796.004</v>
+        <v>794.39688482</v>
       </c>
       <c r="P2">
-        <v>2822.196</v>
+        <v>2816.49804618</v>
       </c>
       <c r="Q2">
-        <v>3767.996</v>
+        <v>3762.29804618</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08841672207118731</v>
+        <v>0.08875249018447545</v>
       </c>
       <c r="T2">
-        <v>0.9842199092652959</v>
+        <v>0.991974369156477</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>495.2999075025848</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0882573052826307</v>
+        <v>0.08809788849407407</v>
       </c>
       <c r="C3">
-        <v>14212.32470188606</v>
+        <v>14078.25364361815</v>
       </c>
       <c r="D3">
-        <v>12565.05470188606</v>
+        <v>12576.21364361815</v>
       </c>
       <c r="E3">
-        <v>-3444.37</v>
+        <v>-3299.14</v>
       </c>
       <c r="F3">
-        <v>145.23</v>
+        <v>290.46</v>
       </c>
       <c r="G3">
         <v>1792.5</v>
@@ -1753,28 +1753,28 @@
         <v>3618.2</v>
       </c>
       <c r="M3">
-        <v>7.305069</v>
+        <v>14.610138</v>
       </c>
       <c r="N3">
-        <v>3610.894931</v>
+        <v>3603.589862</v>
       </c>
       <c r="O3">
-        <v>794.39688482</v>
+        <v>792.7897696399999</v>
       </c>
       <c r="P3">
-        <v>2816.49804618</v>
+        <v>2810.80009236</v>
       </c>
       <c r="Q3">
-        <v>3762.29804618</v>
+        <v>3756.60009236</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08875249018447545</v>
+        <v>0.08909511070823886</v>
       </c>
       <c r="T3">
-        <v>0.991974369156477</v>
+        <v>0.9998870833311516</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>495.2999075025848</v>
+        <v>247.6499537512924</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1799,22 +1799,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08809788849407407</v>
+        <v>0.08793847170551748</v>
       </c>
       <c r="C4">
-        <v>14078.25364361815</v>
+        <v>13944.20242333249</v>
       </c>
       <c r="D4">
-        <v>12576.21364361815</v>
+        <v>12587.39242333249</v>
       </c>
       <c r="E4">
-        <v>-3299.14</v>
+        <v>-3153.91</v>
       </c>
       <c r="F4">
-        <v>290.46</v>
+        <v>435.69</v>
       </c>
       <c r="G4">
         <v>1792.5</v>
@@ -1835,28 +1835,28 @@
         <v>3618.2</v>
       </c>
       <c r="M4">
-        <v>14.610138</v>
+        <v>21.915207</v>
       </c>
       <c r="N4">
-        <v>3603.589862</v>
+        <v>3596.284793</v>
       </c>
       <c r="O4">
-        <v>792.7897696399999</v>
+        <v>791.18265446</v>
       </c>
       <c r="P4">
-        <v>2810.80009236</v>
+        <v>2805.10213854</v>
       </c>
       <c r="Q4">
-        <v>3756.60009236</v>
+        <v>3750.90213854</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08909511070823886</v>
+        <v>0.08944479557269844</v>
       </c>
       <c r="T4">
-        <v>0.9998870833311516</v>
+        <v>1.007962946251696</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>247.6499537512924</v>
+        <v>165.0999691675283</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1881,22 +1881,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08793847170551748</v>
+        <v>0.08777905491696086</v>
       </c>
       <c r="C5">
-        <v>13944.20242333249</v>
+        <v>13810.17109397705</v>
       </c>
       <c r="D5">
-        <v>12587.39242333249</v>
+        <v>12598.59109397705</v>
       </c>
       <c r="E5">
-        <v>-3153.91</v>
+        <v>-3008.68</v>
       </c>
       <c r="F5">
-        <v>435.69</v>
+        <v>580.92</v>
       </c>
       <c r="G5">
         <v>1792.5</v>
@@ -1917,28 +1917,28 @@
         <v>3618.2</v>
       </c>
       <c r="M5">
-        <v>21.915207</v>
+        <v>29.220276</v>
       </c>
       <c r="N5">
-        <v>3596.284793</v>
+        <v>3588.979724</v>
       </c>
       <c r="O5">
-        <v>791.18265446</v>
+        <v>789.5755392799999</v>
       </c>
       <c r="P5">
-        <v>2805.10213854</v>
+        <v>2799.40418472</v>
       </c>
       <c r="Q5">
-        <v>3750.90213854</v>
+        <v>3745.20418472</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08944479557269844</v>
+        <v>0.0898017655385009</v>
       </c>
       <c r="T5">
-        <v>1.007962946251696</v>
+        <v>1.016207056316418</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>165.0999691675283</v>
+        <v>123.8249768756462</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1963,22 +1963,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08777905491696086</v>
+        <v>0.08761963812840425</v>
       </c>
       <c r="C6">
-        <v>13810.17109397705</v>
+        <v>13676.15970868842</v>
       </c>
       <c r="D6">
-        <v>12598.59109397705</v>
+        <v>12609.80970868842</v>
       </c>
       <c r="E6">
-        <v>-3008.68</v>
+        <v>-2863.45</v>
       </c>
       <c r="F6">
-        <v>580.92</v>
+        <v>726.1500000000001</v>
       </c>
       <c r="G6">
         <v>1792.5</v>
@@ -1999,28 +1999,28 @@
         <v>3618.2</v>
       </c>
       <c r="M6">
-        <v>29.220276</v>
+        <v>36.52534500000001</v>
       </c>
       <c r="N6">
-        <v>3588.979724</v>
+        <v>3581.674655</v>
       </c>
       <c r="O6">
-        <v>789.5755392799999</v>
+        <v>787.9684241</v>
       </c>
       <c r="P6">
-        <v>2799.40418472</v>
+        <v>2793.7062309</v>
       </c>
       <c r="Q6">
-        <v>3745.20418472</v>
+        <v>3739.5062309</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0898017655385009</v>
+        <v>0.09016625066147817</v>
       </c>
       <c r="T6">
-        <v>1.016207056316418</v>
+        <v>1.024624726593029</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>123.8249768756462</v>
+        <v>99.05998150051694</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2045,22 +2045,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08761963812840425</v>
+        <v>0.08746022133984764</v>
       </c>
       <c r="C7">
-        <v>13676.15970868842</v>
+        <v>13542.16832079262</v>
       </c>
       <c r="D7">
-        <v>12609.80970868842</v>
+        <v>12621.04832079262</v>
       </c>
       <c r="E7">
-        <v>-2863.45</v>
+        <v>-2718.22</v>
       </c>
       <c r="F7">
-        <v>726.1500000000001</v>
+        <v>871.3800000000001</v>
       </c>
       <c r="G7">
         <v>1792.5</v>
@@ -2081,28 +2081,28 @@
         <v>3618.2</v>
       </c>
       <c r="M7">
-        <v>36.52534500000001</v>
+        <v>43.83041400000001</v>
       </c>
       <c r="N7">
-        <v>3581.674655</v>
+        <v>3574.369586</v>
       </c>
       <c r="O7">
-        <v>787.9684241</v>
+        <v>786.3613089199999</v>
       </c>
       <c r="P7">
-        <v>2793.7062309</v>
+        <v>2788.00827708</v>
       </c>
       <c r="Q7">
-        <v>3739.5062309</v>
+        <v>3733.80827708</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09016625066147817</v>
+        <v>0.09053849078707196</v>
       </c>
       <c r="T7">
-        <v>1.024624726593029</v>
+        <v>1.033221496237228</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2119,7 +2119,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>99.05998150051694</v>
+        <v>82.54998458376411</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2127,22 +2127,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08746022133984764</v>
+        <v>0.08730080455129104</v>
       </c>
       <c r="C8">
-        <v>13542.16832079262</v>
+        <v>13408.19698380593</v>
       </c>
       <c r="D8">
-        <v>12621.04832079262</v>
+        <v>12632.30698380593</v>
       </c>
       <c r="E8">
-        <v>-2718.22</v>
+        <v>-2572.99</v>
       </c>
       <c r="F8">
-        <v>871.38</v>
+        <v>1016.61</v>
       </c>
       <c r="G8">
         <v>1792.5</v>
@@ -2163,28 +2163,28 @@
         <v>3618.2</v>
       </c>
       <c r="M8">
-        <v>43.830414</v>
+        <v>51.135483</v>
       </c>
       <c r="N8">
-        <v>3574.369586</v>
+        <v>3567.064517</v>
       </c>
       <c r="O8">
-        <v>786.3613089199999</v>
+        <v>784.75419374</v>
       </c>
       <c r="P8">
-        <v>2788.00827708</v>
+        <v>2782.31032326</v>
       </c>
       <c r="Q8">
-        <v>3733.80827708</v>
+        <v>3728.11032326</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09053849078707196</v>
+        <v>0.09091873607665701</v>
       </c>
       <c r="T8">
-        <v>1.033221496237228</v>
+        <v>1.042003142647968</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>82.54998458376413</v>
+        <v>70.75712964322641</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2209,22 +2209,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08730080455129102</v>
+        <v>0.08714138776273442</v>
       </c>
       <c r="C9">
-        <v>13408.19698380593</v>
+        <v>13274.24575143578</v>
       </c>
       <c r="D9">
-        <v>12632.30698380593</v>
+        <v>12643.58575143578</v>
       </c>
       <c r="E9">
-        <v>-2572.99</v>
+        <v>-2427.76</v>
       </c>
       <c r="F9">
-        <v>1016.61</v>
+        <v>1161.84</v>
       </c>
       <c r="G9">
         <v>1792.5</v>
@@ -2245,28 +2245,28 @@
         <v>3618.2</v>
       </c>
       <c r="M9">
-        <v>51.13548300000001</v>
+        <v>58.440552</v>
       </c>
       <c r="N9">
-        <v>3567.064517</v>
+        <v>3559.759448</v>
       </c>
       <c r="O9">
-        <v>784.75419374</v>
+        <v>783.14707856</v>
       </c>
       <c r="P9">
-        <v>2782.31032326</v>
+        <v>2776.61236944</v>
       </c>
       <c r="Q9">
-        <v>3728.11032326</v>
+        <v>3722.41236944</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09091873607665701</v>
+        <v>0.09130724756818959</v>
       </c>
       <c r="T9">
-        <v>1.042003142647968</v>
+        <v>1.050975694415464</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>70.75712964322639</v>
+        <v>61.9124884378231</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2291,22 +2291,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08714138776273442</v>
+        <v>0.08698197097417781</v>
       </c>
       <c r="C10">
-        <v>13274.24575143578</v>
+        <v>13140.31467758158</v>
       </c>
       <c r="D10">
-        <v>12643.58575143578</v>
+        <v>12654.88467758158</v>
       </c>
       <c r="E10">
-        <v>-2427.76</v>
+        <v>-2282.53</v>
       </c>
       <c r="F10">
-        <v>1161.84</v>
+        <v>1307.07</v>
       </c>
       <c r="G10">
         <v>1792.5</v>
@@ -2327,28 +2327,28 @@
         <v>3618.2</v>
       </c>
       <c r="M10">
-        <v>58.440552</v>
+        <v>65.745621</v>
       </c>
       <c r="N10">
-        <v>3559.759448</v>
+        <v>3552.454379</v>
       </c>
       <c r="O10">
-        <v>783.14707856</v>
+        <v>781.5399633799999</v>
       </c>
       <c r="P10">
-        <v>2776.61236944</v>
+        <v>2770.91441562</v>
       </c>
       <c r="Q10">
-        <v>3722.41236944</v>
+        <v>3716.71441562</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09130724756818959</v>
+        <v>0.09170429777382176</v>
       </c>
       <c r="T10">
-        <v>1.050975694415464</v>
+        <v>1.060145445122904</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2365,7 +2365,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>61.9124884378231</v>
+        <v>55.03332305584276</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2373,22 +2373,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08698197097417781</v>
+        <v>0.08682255418562121</v>
       </c>
       <c r="C11">
-        <v>13140.31467758158</v>
+        <v>13006.40381633556</v>
       </c>
       <c r="D11">
-        <v>12654.88467758158</v>
+        <v>12666.20381633556</v>
       </c>
       <c r="E11">
-        <v>-2282.53</v>
+        <v>-2137.3</v>
       </c>
       <c r="F11">
-        <v>1307.07</v>
+        <v>1452.3</v>
       </c>
       <c r="G11">
         <v>1792.5</v>
@@ -2409,28 +2409,28 @@
         <v>3618.2</v>
       </c>
       <c r="M11">
-        <v>65.745621</v>
+        <v>73.05069</v>
       </c>
       <c r="N11">
-        <v>3552.454379</v>
+        <v>3545.14931</v>
       </c>
       <c r="O11">
-        <v>781.5399633799999</v>
+        <v>779.9328482</v>
       </c>
       <c r="P11">
-        <v>2770.91441562</v>
+        <v>2765.2164618</v>
       </c>
       <c r="Q11">
-        <v>3716.71441562</v>
+        <v>3711.0164618</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09170429777382176</v>
+        <v>0.09211017131735688</v>
       </c>
       <c r="T11">
-        <v>1.060145445122904</v>
+        <v>1.069518968068288</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>55.03332305584276</v>
+        <v>49.52999075025848</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2455,22 +2455,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08682255418562121</v>
+        <v>0.08666313739706458</v>
       </c>
       <c r="C12">
-        <v>13006.40381633555</v>
+        <v>12872.51322198367</v>
       </c>
       <c r="D12">
-        <v>12666.20381633556</v>
+        <v>12677.54322198367</v>
       </c>
       <c r="E12">
-        <v>-2137.3</v>
+        <v>-1992.07</v>
       </c>
       <c r="F12">
-        <v>1452.3</v>
+        <v>1597.53</v>
       </c>
       <c r="G12">
         <v>1792.5</v>
@@ -2491,28 +2491,28 @@
         <v>3618.2</v>
       </c>
       <c r="M12">
-        <v>73.05069000000002</v>
+        <v>80.35575900000001</v>
       </c>
       <c r="N12">
-        <v>3545.14931</v>
+        <v>3537.844241</v>
       </c>
       <c r="O12">
-        <v>779.9328482</v>
+        <v>778.3257330199999</v>
       </c>
       <c r="P12">
-        <v>2765.2164618</v>
+        <v>2759.51850798</v>
       </c>
       <c r="Q12">
-        <v>3711.0164618</v>
+        <v>3705.31850798</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09211017131735688</v>
+        <v>0.0925251656146793</v>
       </c>
       <c r="T12">
-        <v>1.069518968068288</v>
+        <v>1.079103131978737</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>49.52999075025847</v>
+        <v>45.0272643184168</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2537,22 +2537,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08666313739706458</v>
+        <v>0.08650372060850796</v>
       </c>
       <c r="C13">
-        <v>12872.51322198367</v>
+        <v>12738.64294900644</v>
       </c>
       <c r="D13">
-        <v>12677.54322198367</v>
+        <v>12688.90294900644</v>
       </c>
       <c r="E13">
-        <v>-1992.07</v>
+        <v>-1846.84</v>
       </c>
       <c r="F13">
-        <v>1597.53</v>
+        <v>1742.76</v>
       </c>
       <c r="G13">
         <v>1792.5</v>
@@ -2573,28 +2573,28 @@
         <v>3618.2</v>
       </c>
       <c r="M13">
-        <v>80.35575900000001</v>
+        <v>87.66082800000001</v>
       </c>
       <c r="N13">
-        <v>3537.844241</v>
+        <v>3530.539172</v>
       </c>
       <c r="O13">
-        <v>778.3257330199999</v>
+        <v>776.71861784</v>
       </c>
       <c r="P13">
-        <v>2759.51850798</v>
+        <v>2753.82055416</v>
       </c>
       <c r="Q13">
-        <v>3705.31850798</v>
+        <v>3699.62055416</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0925251656146793</v>
+        <v>0.09294959160057722</v>
       </c>
       <c r="T13">
-        <v>1.079103131978737</v>
+        <v>1.088905117796241</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>45.0272643184168</v>
+        <v>41.27499229188206</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2619,22 +2619,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08650372060850796</v>
+        <v>0.08634430381995135</v>
       </c>
       <c r="C14">
-        <v>12738.64294900644</v>
+        <v>12604.79305207983</v>
       </c>
       <c r="D14">
-        <v>12688.90294900644</v>
+        <v>12700.28305207983</v>
       </c>
       <c r="E14">
-        <v>-1846.84</v>
+        <v>-1701.61</v>
       </c>
       <c r="F14">
-        <v>1742.76</v>
+        <v>1887.99</v>
       </c>
       <c r="G14">
         <v>1792.5</v>
@@ -2655,28 +2655,28 @@
         <v>3618.2</v>
       </c>
       <c r="M14">
-        <v>87.66082800000001</v>
+        <v>94.96589700000001</v>
       </c>
       <c r="N14">
-        <v>3530.539172</v>
+        <v>3523.234103</v>
       </c>
       <c r="O14">
-        <v>776.71861784</v>
+        <v>775.1115026599999</v>
       </c>
       <c r="P14">
-        <v>2753.82055416</v>
+        <v>2748.12260034</v>
       </c>
       <c r="Q14">
-        <v>3699.62055416</v>
+        <v>3693.92260034</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09294959160057722</v>
+        <v>0.09338377450569121</v>
       </c>
       <c r="T14">
-        <v>1.088905117796241</v>
+        <v>1.098932436621044</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2693,7 +2693,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>41.27499229188206</v>
+        <v>38.09999288481421</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2701,22 +2701,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08634430381995135</v>
+        <v>0.08618488703139474</v>
       </c>
       <c r="C15">
-        <v>12604.79305207983</v>
+        <v>12470.96358607613</v>
       </c>
       <c r="D15">
-        <v>12700.28305207983</v>
+        <v>12711.68358607613</v>
       </c>
       <c r="E15">
-        <v>-1701.61</v>
+        <v>-1556.38</v>
       </c>
       <c r="F15">
-        <v>1887.99</v>
+        <v>2033.22</v>
       </c>
       <c r="G15">
         <v>1792.5</v>
@@ -2737,28 +2737,28 @@
         <v>3618.2</v>
       </c>
       <c r="M15">
-        <v>94.96589700000001</v>
+        <v>102.270966</v>
       </c>
       <c r="N15">
-        <v>3523.234103</v>
+        <v>3515.929034</v>
       </c>
       <c r="O15">
-        <v>775.1115026599999</v>
+        <v>773.50438748</v>
       </c>
       <c r="P15">
-        <v>2748.12260034</v>
+        <v>2742.42464652</v>
       </c>
       <c r="Q15">
-        <v>3693.92260034</v>
+        <v>3688.22464652</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09338377450569121</v>
+        <v>0.09382805468766831</v>
       </c>
       <c r="T15">
-        <v>1.098932436621044</v>
+        <v>1.109192948906889</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>38.09999288481421</v>
+        <v>35.3785648216132</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08618488703139474</v>
+        <v>0.08602547024283813</v>
       </c>
       <c r="C16">
-        <v>12470.96358607613</v>
+        <v>12337.15460606482</v>
       </c>
       <c r="D16">
-        <v>12711.68358607613</v>
+        <v>12723.10460606482</v>
       </c>
       <c r="E16">
-        <v>-1556.38</v>
+        <v>-1411.15</v>
       </c>
       <c r="F16">
-        <v>2033.22</v>
+        <v>2178.45</v>
       </c>
       <c r="G16">
         <v>1792.5</v>
@@ -2819,28 +2819,28 @@
         <v>3618.2</v>
       </c>
       <c r="M16">
-        <v>102.270966</v>
+        <v>109.576035</v>
       </c>
       <c r="N16">
-        <v>3515.929034</v>
+        <v>3508.623965</v>
       </c>
       <c r="O16">
-        <v>773.50438748</v>
+        <v>771.8972722999999</v>
       </c>
       <c r="P16">
-        <v>2742.42464652</v>
+        <v>2736.7266927</v>
       </c>
       <c r="Q16">
-        <v>3688.22464652</v>
+        <v>3682.5266927</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09382805468766831</v>
+        <v>0.09428278852098604</v>
       </c>
       <c r="T16">
-        <v>1.109192948906889</v>
+        <v>1.119694885011225</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2857,7 +2857,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>35.3785648216132</v>
+        <v>33.01999383350565</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2865,22 +2865,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08602547024283813</v>
+        <v>0.08586605345428151</v>
       </c>
       <c r="C17">
-        <v>12337.15460606483</v>
+        <v>12203.3661673135</v>
       </c>
       <c r="D17">
-        <v>12723.10460606482</v>
+        <v>12734.5461673135</v>
       </c>
       <c r="E17">
-        <v>-1411.15</v>
+        <v>-1265.92</v>
       </c>
       <c r="F17">
-        <v>2178.45</v>
+        <v>2323.68</v>
       </c>
       <c r="G17">
         <v>1792.5</v>
@@ -2901,28 +2901,28 @@
         <v>3618.2</v>
       </c>
       <c r="M17">
-        <v>109.576035</v>
+        <v>116.881104</v>
       </c>
       <c r="N17">
-        <v>3508.623965</v>
+        <v>3501.318896</v>
       </c>
       <c r="O17">
-        <v>771.8972722999999</v>
+        <v>770.29015712</v>
       </c>
       <c r="P17">
-        <v>2736.7266927</v>
+        <v>2731.02873888</v>
       </c>
       <c r="Q17">
-        <v>3682.5266927</v>
+        <v>3676.82873888</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09428278852098604</v>
+        <v>0.09474834935033515</v>
       </c>
       <c r="T17">
-        <v>1.119694885011225</v>
+        <v>1.130446867213283</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2939,7 +2939,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>33.01999383350565</v>
+        <v>30.95624421891155</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2947,22 +2947,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08586605345428151</v>
+        <v>0.08570663666572489</v>
       </c>
       <c r="C18">
-        <v>12203.3661673135</v>
+        <v>12069.59832528871</v>
       </c>
       <c r="D18">
-        <v>12734.5461673135</v>
+        <v>12746.00832528871</v>
       </c>
       <c r="E18">
-        <v>-1265.92</v>
+        <v>-1120.69</v>
       </c>
       <c r="F18">
-        <v>2323.68</v>
+        <v>2468.91</v>
       </c>
       <c r="G18">
         <v>1792.5</v>
@@ -2983,28 +2983,28 @@
         <v>3618.2</v>
       </c>
       <c r="M18">
-        <v>116.881104</v>
+        <v>124.186173</v>
       </c>
       <c r="N18">
-        <v>3501.318896</v>
+        <v>3494.013827</v>
       </c>
       <c r="O18">
-        <v>770.29015712</v>
+        <v>768.68304194</v>
       </c>
       <c r="P18">
-        <v>2731.02873888</v>
+        <v>2725.33078506</v>
       </c>
       <c r="Q18">
-        <v>3676.82873888</v>
+        <v>3671.13078506</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09474834935033515</v>
+        <v>0.09522512851292157</v>
       </c>
       <c r="T18">
-        <v>1.130446867213283</v>
+        <v>1.141457933323824</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>30.95624421891155</v>
+        <v>29.13528867662263</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3029,22 +3029,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08570663666572489</v>
+        <v>0.0855472198771683</v>
       </c>
       <c r="C19">
-        <v>12069.59832528871</v>
+        <v>11935.85113565691</v>
       </c>
       <c r="D19">
-        <v>12746.00832528871</v>
+        <v>12757.49113565691</v>
       </c>
       <c r="E19">
-        <v>-1120.69</v>
+        <v>-975.4599999999996</v>
       </c>
       <c r="F19">
-        <v>2468.91</v>
+        <v>2614.14</v>
       </c>
       <c r="G19">
         <v>1792.5</v>
@@ -3065,28 +3065,28 @@
         <v>3618.2</v>
       </c>
       <c r="M19">
-        <v>124.186173</v>
+        <v>131.491242</v>
       </c>
       <c r="N19">
-        <v>3494.013827</v>
+        <v>3486.708758</v>
       </c>
       <c r="O19">
-        <v>768.68304194</v>
+        <v>767.0759267599999</v>
       </c>
       <c r="P19">
-        <v>2725.33078506</v>
+        <v>2719.63283124</v>
       </c>
       <c r="Q19">
-        <v>3671.13078506</v>
+        <v>3665.43283124</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09522512851292157</v>
+        <v>0.09571353643557109</v>
       </c>
       <c r="T19">
-        <v>1.141457933323824</v>
+        <v>1.152737562022427</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>29.13528867662263</v>
+        <v>27.51666152792137</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3111,22 +3111,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0855472198771683</v>
+        <v>0.08538780308861169</v>
       </c>
       <c r="C20">
-        <v>11935.85113565691</v>
+        <v>11802.1246542853</v>
       </c>
       <c r="D20">
-        <v>12757.49113565691</v>
+        <v>12768.9946542853</v>
       </c>
       <c r="E20">
-        <v>-975.46</v>
+        <v>-830.23</v>
       </c>
       <c r="F20">
-        <v>2614.14</v>
+        <v>2759.37</v>
       </c>
       <c r="G20">
         <v>1792.5</v>
@@ -3147,28 +3147,28 @@
         <v>3618.2</v>
       </c>
       <c r="M20">
-        <v>131.491242</v>
+        <v>138.796311</v>
       </c>
       <c r="N20">
-        <v>3486.708758</v>
+        <v>3479.403689</v>
       </c>
       <c r="O20">
-        <v>767.0759267599999</v>
+        <v>765.46881158</v>
       </c>
       <c r="P20">
-        <v>2719.63283124</v>
+        <v>2713.93487742</v>
       </c>
       <c r="Q20">
-        <v>3665.43283124</v>
+        <v>3659.73487742</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09571353643557109</v>
+        <v>0.09621400381310084</v>
       </c>
       <c r="T20">
-        <v>1.152737562022427</v>
+        <v>1.164295700071613</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3185,7 +3185,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>27.51666152792138</v>
+        <v>26.06841618434657</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3193,22 +3193,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08538780308861169</v>
+        <v>0.08522838630005508</v>
       </c>
       <c r="C21">
-        <v>11802.1246542853</v>
+        <v>11668.41893724281</v>
       </c>
       <c r="D21">
-        <v>12768.9946542853</v>
+        <v>12780.51893724281</v>
       </c>
       <c r="E21">
-        <v>-830.23</v>
+        <v>-684.9999999999995</v>
       </c>
       <c r="F21">
-        <v>2759.37</v>
+        <v>2904.6</v>
       </c>
       <c r="G21">
         <v>1792.5</v>
@@ -3229,28 +3229,28 @@
         <v>3618.2</v>
       </c>
       <c r="M21">
-        <v>138.796311</v>
+        <v>146.10138</v>
       </c>
       <c r="N21">
-        <v>3479.403689</v>
+        <v>3472.09862</v>
       </c>
       <c r="O21">
-        <v>765.46881158</v>
+        <v>763.8616963999999</v>
       </c>
       <c r="P21">
-        <v>2713.93487742</v>
+        <v>2708.2369236</v>
       </c>
       <c r="Q21">
-        <v>3659.73487742</v>
+        <v>3654.0369236</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09621400381310084</v>
+        <v>0.09672698287506884</v>
       </c>
       <c r="T21">
-        <v>1.164295700071613</v>
+        <v>1.176142791572029</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>26.06841618434657</v>
+        <v>24.76499537512924</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3275,22 +3275,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08522838630005508</v>
+        <v>0.08506896951149848</v>
       </c>
       <c r="C22">
-        <v>11668.41893724281</v>
+        <v>11534.73404080092</v>
       </c>
       <c r="D22">
-        <v>12780.51893724281</v>
+        <v>12792.06404080092</v>
       </c>
       <c r="E22">
-        <v>-684.9999999999995</v>
+        <v>-539.7699999999995</v>
       </c>
       <c r="F22">
-        <v>2904.6</v>
+        <v>3049.83</v>
       </c>
       <c r="G22">
         <v>1792.5</v>
@@ -3311,28 +3311,28 @@
         <v>3618.2</v>
       </c>
       <c r="M22">
-        <v>146.10138</v>
+        <v>153.406449</v>
       </c>
       <c r="N22">
-        <v>3472.09862</v>
+        <v>3464.793551</v>
       </c>
       <c r="O22">
-        <v>763.8616963999999</v>
+        <v>762.25458122</v>
       </c>
       <c r="P22">
-        <v>2708.2369236</v>
+        <v>2702.53896978</v>
       </c>
       <c r="Q22">
-        <v>3654.0369236</v>
+        <v>3648.338969779999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09672698287506884</v>
+        <v>0.09725294874873223</v>
       </c>
       <c r="T22">
-        <v>1.176142791572029</v>
+        <v>1.188289809439544</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>24.76499537512924</v>
+        <v>23.58570988107546</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3357,22 +3357,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08506896951149846</v>
+        <v>0.08490955272294184</v>
       </c>
       <c r="C23">
-        <v>11534.73404080092</v>
+        <v>11401.07002143466</v>
       </c>
       <c r="D23">
-        <v>12792.06404080092</v>
+        <v>12803.63002143466</v>
       </c>
       <c r="E23">
-        <v>-539.77</v>
+        <v>-394.54</v>
       </c>
       <c r="F23">
-        <v>3049.83</v>
+        <v>3195.06</v>
       </c>
       <c r="G23">
         <v>1792.5</v>
@@ -3393,28 +3393,28 @@
         <v>3618.2</v>
       </c>
       <c r="M23">
-        <v>153.406449</v>
+        <v>160.711518</v>
       </c>
       <c r="N23">
-        <v>3464.793551</v>
+        <v>3457.488482</v>
       </c>
       <c r="O23">
-        <v>762.25458122</v>
+        <v>760.6474660399999</v>
       </c>
       <c r="P23">
-        <v>2702.53896978</v>
+        <v>2696.84101596</v>
       </c>
       <c r="Q23">
-        <v>3648.338969779999</v>
+        <v>3642.64101596</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09725294874873222</v>
+        <v>0.09779240092684852</v>
       </c>
       <c r="T23">
-        <v>1.188289809439543</v>
+        <v>1.200748289303661</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3431,7 +3431,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>23.58570988107547</v>
+        <v>22.5136321592084</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3439,22 +3439,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08490955272294184</v>
+        <v>0.08475013593438523</v>
       </c>
       <c r="C24">
-        <v>11401.07002143466</v>
+        <v>11267.42693582346</v>
       </c>
       <c r="D24">
-        <v>12803.63002143466</v>
+        <v>12815.21693582346</v>
       </c>
       <c r="E24">
-        <v>-394.54</v>
+        <v>-249.3099999999999</v>
       </c>
       <c r="F24">
-        <v>3195.06</v>
+        <v>3340.29</v>
       </c>
       <c r="G24">
         <v>1792.5</v>
@@ -3475,28 +3475,28 @@
         <v>3618.2</v>
       </c>
       <c r="M24">
-        <v>160.711518</v>
+        <v>168.016587</v>
       </c>
       <c r="N24">
-        <v>3457.488482</v>
+        <v>3450.183413</v>
       </c>
       <c r="O24">
-        <v>760.6474660399999</v>
+        <v>759.04035086</v>
       </c>
       <c r="P24">
-        <v>2696.84101596</v>
+        <v>2691.14306214</v>
       </c>
       <c r="Q24">
-        <v>3642.64101596</v>
+        <v>3636.94306214</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09779240092684852</v>
+        <v>0.09834586484985094</v>
       </c>
       <c r="T24">
-        <v>1.200748289303661</v>
+        <v>1.213530366047366</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>22.5136321592084</v>
+        <v>21.5347785870689</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3521,22 +3521,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08475013593438523</v>
+        <v>0.08459071914582864</v>
       </c>
       <c r="C25">
-        <v>11267.42693582346</v>
+        <v>11133.80484085213</v>
       </c>
       <c r="D25">
-        <v>12815.21693582346</v>
+        <v>12826.82484085213</v>
       </c>
       <c r="E25">
-        <v>-249.3099999999999</v>
+        <v>-104.0799999999995</v>
       </c>
       <c r="F25">
-        <v>3340.29</v>
+        <v>3485.52</v>
       </c>
       <c r="G25">
         <v>1792.5</v>
@@ -3557,28 +3557,28 @@
         <v>3618.2</v>
       </c>
       <c r="M25">
-        <v>168.016587</v>
+        <v>175.321656</v>
       </c>
       <c r="N25">
-        <v>3450.183413</v>
+        <v>3442.878344</v>
       </c>
       <c r="O25">
-        <v>759.04035086</v>
+        <v>757.4332356799999</v>
       </c>
       <c r="P25">
-        <v>2691.14306214</v>
+        <v>2685.44510832</v>
       </c>
       <c r="Q25">
-        <v>3636.94306214</v>
+        <v>3631.245108319999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09834586484985094</v>
+        <v>0.0989138936129324</v>
       </c>
       <c r="T25">
-        <v>1.213530366047366</v>
+        <v>1.226648813231695</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>21.5347785870689</v>
+        <v>20.63749614594103</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3603,22 +3603,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08459071914582864</v>
+        <v>0.08443130235727202</v>
       </c>
       <c r="C26">
-        <v>11133.80484085213</v>
+        <v>11000.20379361178</v>
       </c>
       <c r="D26">
-        <v>12826.82484085213</v>
+        <v>12838.45379361178</v>
       </c>
       <c r="E26">
-        <v>-104.0799999999999</v>
+        <v>41.15000000000009</v>
       </c>
       <c r="F26">
-        <v>3485.52</v>
+        <v>3630.75</v>
       </c>
       <c r="G26">
         <v>1792.5</v>
@@ -3639,28 +3639,28 @@
         <v>3618.2</v>
       </c>
       <c r="M26">
-        <v>175.321656</v>
+        <v>182.626725</v>
       </c>
       <c r="N26">
-        <v>3442.878344</v>
+        <v>3435.573275</v>
       </c>
       <c r="O26">
-        <v>757.4332356799999</v>
+        <v>755.8261205</v>
       </c>
       <c r="P26">
-        <v>2685.44510832</v>
+        <v>2679.7471545</v>
       </c>
       <c r="Q26">
-        <v>3631.245108319999</v>
+        <v>3625.5471545</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.0989138936129324</v>
+        <v>0.09949706980969603</v>
       </c>
       <c r="T26">
-        <v>1.226648813231695</v>
+        <v>1.240117085674273</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>20.63749614594103</v>
+        <v>19.81199630010339</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3685,22 +3685,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08443130235727202</v>
+        <v>0.0842718855687154</v>
       </c>
       <c r="C27">
-        <v>11000.20379361178</v>
+        <v>10866.62385140071</v>
       </c>
       <c r="D27">
-        <v>12838.45379361178</v>
+        <v>12850.10385140071</v>
       </c>
       <c r="E27">
-        <v>41.15000000000009</v>
+        <v>186.3800000000001</v>
       </c>
       <c r="F27">
-        <v>3630.75</v>
+        <v>3775.98</v>
       </c>
       <c r="G27">
         <v>1792.5</v>
@@ -3721,28 +3721,28 @@
         <v>3618.2</v>
       </c>
       <c r="M27">
-        <v>182.626725</v>
+        <v>189.931794</v>
       </c>
       <c r="N27">
-        <v>3435.573275</v>
+        <v>3428.268206</v>
       </c>
       <c r="O27">
-        <v>755.8261205</v>
+        <v>754.21900532</v>
       </c>
       <c r="P27">
-        <v>2679.7471545</v>
+        <v>2674.04920068</v>
       </c>
       <c r="Q27">
-        <v>3625.5471545</v>
+        <v>3619.84920068</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09949706980969603</v>
+        <v>0.1000960075252911</v>
       </c>
       <c r="T27">
-        <v>1.240117085674273</v>
+        <v>1.253949365480164</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>19.81199630010339</v>
+        <v>19.04999644240711</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3767,22 +3767,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0842718855687154</v>
+        <v>0.08411246878015879</v>
       </c>
       <c r="C28">
-        <v>10866.62385140071</v>
+        <v>10733.06507172542</v>
       </c>
       <c r="D28">
-        <v>12850.10385140071</v>
+        <v>12861.77507172542</v>
       </c>
       <c r="E28">
-        <v>186.3800000000001</v>
+        <v>331.6100000000001</v>
       </c>
       <c r="F28">
-        <v>3775.98</v>
+        <v>3921.21</v>
       </c>
       <c r="G28">
         <v>1792.5</v>
@@ -3803,28 +3803,28 @@
         <v>3618.2</v>
       </c>
       <c r="M28">
-        <v>189.931794</v>
+        <v>197.236863</v>
       </c>
       <c r="N28">
-        <v>3428.268206</v>
+        <v>3420.963137</v>
       </c>
       <c r="O28">
-        <v>754.21900532</v>
+        <v>752.6118901399999</v>
       </c>
       <c r="P28">
-        <v>2674.04920068</v>
+        <v>2668.35124686</v>
       </c>
       <c r="Q28">
-        <v>3619.84920068</v>
+        <v>3614.151246859999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1000960075252911</v>
+        <v>0.1007113544933682</v>
       </c>
       <c r="T28">
-        <v>1.253949365480164</v>
+        <v>1.268160611856079</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>19.04999644240711</v>
+        <v>18.34444101861425</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08411246878015879</v>
+        <v>0.08395305199160218</v>
       </c>
       <c r="C29">
-        <v>10733.06507172542</v>
+        <v>10599.52751230151</v>
       </c>
       <c r="D29">
-        <v>12861.77507172542</v>
+        <v>12873.46751230151</v>
       </c>
       <c r="E29">
-        <v>331.6100000000001</v>
+        <v>476.8400000000006</v>
       </c>
       <c r="F29">
-        <v>3921.21</v>
+        <v>4066.440000000001</v>
       </c>
       <c r="G29">
         <v>1792.5</v>
@@ -3885,28 +3885,28 @@
         <v>3618.2</v>
       </c>
       <c r="M29">
-        <v>197.236863</v>
+        <v>204.541932</v>
       </c>
       <c r="N29">
-        <v>3420.963137</v>
+        <v>3413.658068</v>
       </c>
       <c r="O29">
-        <v>752.6118901399999</v>
+        <v>751.00477496</v>
       </c>
       <c r="P29">
-        <v>2668.35124686</v>
+        <v>2662.65329304</v>
       </c>
       <c r="Q29">
-        <v>3614.151246859999</v>
+        <v>3608.45329304</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1007113544933682</v>
+        <v>0.1013437944327808</v>
       </c>
       <c r="T29">
-        <v>1.268160611856079</v>
+        <v>1.282766615075769</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3923,7 +3923,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>18.34444101861425</v>
+        <v>17.6892824108066</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3931,22 +3931,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08395305199160218</v>
+        <v>0.08379363520304556</v>
       </c>
       <c r="C30">
-        <v>10599.52751230151</v>
+        <v>10466.01123105465</v>
       </c>
       <c r="D30">
-        <v>12873.46751230151</v>
+        <v>12885.18123105465</v>
       </c>
       <c r="E30">
-        <v>476.8400000000006</v>
+        <v>622.0700000000002</v>
       </c>
       <c r="F30">
-        <v>4066.440000000001</v>
+        <v>4211.67</v>
       </c>
       <c r="G30">
         <v>1792.5</v>
@@ -3967,28 +3967,28 @@
         <v>3618.2</v>
       </c>
       <c r="M30">
-        <v>204.541932</v>
+        <v>211.847001</v>
       </c>
       <c r="N30">
-        <v>3413.658068</v>
+        <v>3406.352999</v>
       </c>
       <c r="O30">
-        <v>751.00477496</v>
+        <v>749.3976597799999</v>
       </c>
       <c r="P30">
-        <v>2662.65329304</v>
+        <v>2656.95533922</v>
       </c>
       <c r="Q30">
-        <v>3608.45329304</v>
+        <v>3602.75533922</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1013437944327808</v>
+        <v>0.1019940495817543</v>
       </c>
       <c r="T30">
-        <v>1.282766615075769</v>
+        <v>1.297784055005873</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>17.6892824108066</v>
+        <v>17.07930715526154</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4013,22 +4013,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08379363520304556</v>
+        <v>0.08363421841448895</v>
       </c>
       <c r="C31">
-        <v>10466.01123105465</v>
+        <v>10332.51628612151</v>
       </c>
       <c r="D31">
-        <v>12885.18123105465</v>
+        <v>12896.91628612151</v>
       </c>
       <c r="E31">
-        <v>622.0700000000002</v>
+        <v>767.2999999999997</v>
       </c>
       <c r="F31">
-        <v>4211.67</v>
+        <v>4356.9</v>
       </c>
       <c r="G31">
         <v>1792.5</v>
@@ -4049,28 +4049,28 @@
         <v>3618.2</v>
       </c>
       <c r="M31">
-        <v>211.847001</v>
+        <v>219.15207</v>
       </c>
       <c r="N31">
-        <v>3406.352999</v>
+        <v>3399.04793</v>
       </c>
       <c r="O31">
-        <v>749.3976597799999</v>
+        <v>747.7905446</v>
       </c>
       <c r="P31">
-        <v>2656.95533922</v>
+        <v>2651.2573854</v>
       </c>
       <c r="Q31">
-        <v>3602.75533922</v>
+        <v>3597.057385399999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1019940495817543</v>
+        <v>0.1026628834492699</v>
       </c>
       <c r="T31">
-        <v>1.297784055005873</v>
+        <v>1.313230564648266</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>17.07930715526154</v>
+        <v>16.50999691675283</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4095,22 +4095,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08363421841448895</v>
+        <v>0.08347480162593233</v>
       </c>
       <c r="C32">
-        <v>10332.51628612151</v>
+        <v>10199.04273585077</v>
       </c>
       <c r="D32">
-        <v>12896.91628612151</v>
+        <v>12908.67273585077</v>
       </c>
       <c r="E32">
-        <v>767.2999999999997</v>
+        <v>912.5300000000002</v>
       </c>
       <c r="F32">
-        <v>4356.9</v>
+        <v>4502.13</v>
       </c>
       <c r="G32">
         <v>1792.5</v>
@@ -4131,28 +4131,28 @@
         <v>3618.2</v>
       </c>
       <c r="M32">
-        <v>219.15207</v>
+        <v>226.457139</v>
       </c>
       <c r="N32">
-        <v>3399.04793</v>
+        <v>3391.742861</v>
       </c>
       <c r="O32">
-        <v>747.7905446</v>
+        <v>746.1834294199999</v>
       </c>
       <c r="P32">
-        <v>2651.2573854</v>
+        <v>2645.55943158</v>
       </c>
       <c r="Q32">
-        <v>3597.057385399999</v>
+        <v>3591.35943158</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1026628834492699</v>
+        <v>0.103351103805699</v>
       </c>
       <c r="T32">
-        <v>1.313230564648266</v>
+        <v>1.32912479920783</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>16.50999691675283</v>
+        <v>15.97741637105112</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4177,22 +4177,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08347480162593233</v>
+        <v>0.08331538483737573</v>
       </c>
       <c r="C33">
-        <v>10199.04273585077</v>
+        <v>10065.59063880405</v>
       </c>
       <c r="D33">
-        <v>12908.67273585077</v>
+        <v>12920.45063880405</v>
       </c>
       <c r="E33">
-        <v>912.5300000000002</v>
+        <v>1057.76</v>
       </c>
       <c r="F33">
-        <v>4502.13</v>
+        <v>4647.36</v>
       </c>
       <c r="G33">
         <v>1792.5</v>
@@ -4213,28 +4213,28 @@
         <v>3618.2</v>
       </c>
       <c r="M33">
-        <v>226.457139</v>
+        <v>233.762208</v>
       </c>
       <c r="N33">
-        <v>3391.742861</v>
+        <v>3384.437792</v>
       </c>
       <c r="O33">
-        <v>746.1834294199999</v>
+        <v>744.57631424</v>
       </c>
       <c r="P33">
-        <v>2645.55943158</v>
+        <v>2639.86147776</v>
       </c>
       <c r="Q33">
-        <v>3591.35943158</v>
+        <v>3585.66147776</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.103351103805699</v>
+        <v>0.1040595659373172</v>
       </c>
       <c r="T33">
-        <v>1.32912479920783</v>
+        <v>1.34548651125444</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4251,7 +4251,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>15.97741637105112</v>
+        <v>15.47812210945578</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4259,22 +4259,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08331538483737573</v>
+        <v>0.08315596804881911</v>
       </c>
       <c r="C34">
-        <v>10065.59063880405</v>
+        <v>9932.16005375689</v>
       </c>
       <c r="D34">
-        <v>12920.45063880405</v>
+        <v>12932.25005375689</v>
       </c>
       <c r="E34">
-        <v>1057.76</v>
+        <v>1202.99</v>
       </c>
       <c r="F34">
-        <v>4647.36</v>
+        <v>4792.59</v>
       </c>
       <c r="G34">
         <v>1792.5</v>
@@ -4295,28 +4295,28 @@
         <v>3618.2</v>
       </c>
       <c r="M34">
-        <v>233.762208</v>
+        <v>241.067277</v>
       </c>
       <c r="N34">
-        <v>3384.437792</v>
+        <v>3377.132723</v>
       </c>
       <c r="O34">
-        <v>744.57631424</v>
+        <v>742.9691990599999</v>
       </c>
       <c r="P34">
-        <v>2639.86147776</v>
+        <v>2634.16352394</v>
       </c>
       <c r="Q34">
-        <v>3585.66147776</v>
+        <v>3579.96352394</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1040595659373172</v>
+        <v>0.1047891761922673</v>
       </c>
       <c r="T34">
-        <v>1.34548651125444</v>
+        <v>1.362336632615874</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4333,7 +4333,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>15.47812210945578</v>
+        <v>15.00908810613893</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4341,22 +4341,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08315596804881911</v>
+        <v>0.08299655126026249</v>
       </c>
       <c r="C35">
-        <v>9932.16005375689</v>
+        <v>9798.751039699731</v>
       </c>
       <c r="D35">
-        <v>12932.25005375689</v>
+        <v>12944.07103969973</v>
       </c>
       <c r="E35">
-        <v>1202.99</v>
+        <v>1348.220000000001</v>
       </c>
       <c r="F35">
-        <v>4792.59</v>
+        <v>4937.820000000001</v>
       </c>
       <c r="G35">
         <v>1792.5</v>
@@ -4377,28 +4377,28 @@
         <v>3618.2</v>
       </c>
       <c r="M35">
-        <v>241.067277</v>
+        <v>248.3723460000001</v>
       </c>
       <c r="N35">
-        <v>3377.132723</v>
+        <v>3369.827654</v>
       </c>
       <c r="O35">
-        <v>742.9691990599999</v>
+        <v>741.3620838799999</v>
       </c>
       <c r="P35">
-        <v>2634.16352394</v>
+        <v>2628.46557012</v>
       </c>
       <c r="Q35">
-        <v>3579.96352394</v>
+        <v>3574.26557012</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1047891761922673</v>
+        <v>0.1055408958488826</v>
       </c>
       <c r="T35">
-        <v>1.362336632615874</v>
+        <v>1.379697363715533</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4415,7 +4415,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>15.00908810613893</v>
+        <v>14.56764433831131</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4423,22 +4423,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08299655126026249</v>
+        <v>0.08283713447170589</v>
       </c>
       <c r="C36">
-        <v>9798.751039699731</v>
+        <v>9665.36365583889</v>
       </c>
       <c r="D36">
-        <v>12944.07103969973</v>
+        <v>12955.91365583889</v>
       </c>
       <c r="E36">
-        <v>1348.220000000001</v>
+        <v>1493.45</v>
       </c>
       <c r="F36">
-        <v>4937.820000000001</v>
+        <v>5083.05</v>
       </c>
       <c r="G36">
         <v>1792.5</v>
@@ -4459,28 +4459,28 @@
         <v>3618.2</v>
       </c>
       <c r="M36">
-        <v>248.3723460000001</v>
+        <v>255.677415</v>
       </c>
       <c r="N36">
-        <v>3369.827654</v>
+        <v>3362.522585</v>
       </c>
       <c r="O36">
-        <v>741.3620838799999</v>
+        <v>739.7549686999999</v>
       </c>
       <c r="P36">
-        <v>2628.46557012</v>
+        <v>2622.7676163</v>
       </c>
       <c r="Q36">
-        <v>3574.26557012</v>
+        <v>3568.5676163</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1055408958488826</v>
+        <v>0.106315745341086</v>
       </c>
       <c r="T36">
-        <v>1.379697363715533</v>
+        <v>1.39759227115672</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4497,7 +4497,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>14.56764433831131</v>
+        <v>14.15142592864528</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4505,22 +4505,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08283713447170589</v>
+        <v>0.08267771768314927</v>
       </c>
       <c r="C37">
-        <v>9665.36365583889</v>
+        <v>9531.997961597572</v>
       </c>
       <c r="D37">
-        <v>12955.91365583889</v>
+        <v>12967.77796159757</v>
       </c>
       <c r="E37">
-        <v>1493.45</v>
+        <v>1638.680000000001</v>
       </c>
       <c r="F37">
-        <v>5083.05</v>
+        <v>5228.280000000001</v>
       </c>
       <c r="G37">
         <v>1792.5</v>
@@ -4541,28 +4541,28 @@
         <v>3618.2</v>
       </c>
       <c r="M37">
-        <v>255.677415</v>
+        <v>262.9824840000001</v>
       </c>
       <c r="N37">
-        <v>3362.522585</v>
+        <v>3355.217516</v>
       </c>
       <c r="O37">
-        <v>739.7549686999999</v>
+        <v>738.1478535199999</v>
       </c>
       <c r="P37">
-        <v>2622.7676163</v>
+        <v>2617.06966248</v>
       </c>
       <c r="Q37">
-        <v>3568.5676163</v>
+        <v>3562.86966248</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.106315745341086</v>
+        <v>0.1071148088799208</v>
       </c>
       <c r="T37">
-        <v>1.39759227115672</v>
+        <v>1.416046394455445</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4579,7 +4579,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>14.15142592864528</v>
+        <v>13.75833076396069</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4587,22 +4587,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08267771768314927</v>
+        <v>0.08251830089459267</v>
       </c>
       <c r="C38">
-        <v>9531.997961597572</v>
+        <v>9398.654016616831</v>
       </c>
       <c r="D38">
-        <v>12967.77796159757</v>
+        <v>12979.66401661683</v>
       </c>
       <c r="E38">
-        <v>1638.68</v>
+        <v>1783.91</v>
       </c>
       <c r="F38">
-        <v>5228.28</v>
+        <v>5373.51</v>
       </c>
       <c r="G38">
         <v>1792.5</v>
@@ -4623,28 +4623,28 @@
         <v>3618.2</v>
       </c>
       <c r="M38">
-        <v>262.982484</v>
+        <v>270.2875530000001</v>
       </c>
       <c r="N38">
-        <v>3355.217516</v>
+        <v>3347.912447</v>
       </c>
       <c r="O38">
-        <v>738.1478535199999</v>
+        <v>736.54073834</v>
       </c>
       <c r="P38">
-        <v>2617.06966248</v>
+        <v>2611.37170866</v>
       </c>
       <c r="Q38">
-        <v>3562.86966248</v>
+        <v>3557.17170866</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1071148088799207</v>
+        <v>0.1079392395152265</v>
       </c>
       <c r="T38">
-        <v>1.416046394455444</v>
+        <v>1.435086362938255</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4661,7 +4661,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>13.75833076396069</v>
+        <v>13.38648398655634</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4669,22 +4669,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08251830089459267</v>
+        <v>0.08235888410603605</v>
       </c>
       <c r="C39">
-        <v>9398.654016616831</v>
+        <v>9265.331880756597</v>
       </c>
       <c r="D39">
-        <v>12979.66401661683</v>
+        <v>12991.5718807566</v>
       </c>
       <c r="E39">
-        <v>1783.91</v>
+        <v>1929.14</v>
       </c>
       <c r="F39">
-        <v>5373.51</v>
+        <v>5518.74</v>
       </c>
       <c r="G39">
         <v>1792.5</v>
@@ -4705,28 +4705,28 @@
         <v>3618.2</v>
       </c>
       <c r="M39">
-        <v>270.2875530000001</v>
+        <v>277.592622</v>
       </c>
       <c r="N39">
-        <v>3347.912447</v>
+        <v>3340.607378</v>
       </c>
       <c r="O39">
-        <v>736.54073834</v>
+        <v>734.9336231599999</v>
       </c>
       <c r="P39">
-        <v>2611.37170866</v>
+        <v>2605.67375484</v>
       </c>
       <c r="Q39">
-        <v>3557.17170866</v>
+        <v>3551.47375484</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1079392395152265</v>
+        <v>0.1087902646871549</v>
       </c>
       <c r="T39">
-        <v>1.435086362938255</v>
+        <v>1.45474052395277</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4743,7 +4743,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>13.38648398655634</v>
+        <v>13.03420809217328</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4751,22 +4751,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08235888410603605</v>
+        <v>0.08219946731747943</v>
       </c>
       <c r="C40">
-        <v>9265.331880756597</v>
+        <v>9132.031614096664</v>
       </c>
       <c r="D40">
-        <v>12991.5718807566</v>
+        <v>13003.50161409666</v>
       </c>
       <c r="E40">
-        <v>1929.14</v>
+        <v>2074.37</v>
       </c>
       <c r="F40">
-        <v>5518.74</v>
+        <v>5663.97</v>
       </c>
       <c r="G40">
         <v>1792.5</v>
@@ -4787,28 +4787,28 @@
         <v>3618.2</v>
       </c>
       <c r="M40">
-        <v>277.592622</v>
+        <v>284.8976910000001</v>
       </c>
       <c r="N40">
-        <v>3340.607378</v>
+        <v>3333.302309</v>
       </c>
       <c r="O40">
-        <v>734.9336231599999</v>
+        <v>733.32650798</v>
       </c>
       <c r="P40">
-        <v>2605.67375484</v>
+        <v>2599.97580102</v>
       </c>
       <c r="Q40">
-        <v>3551.47375484</v>
+        <v>3545.77580102</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1087902646871549</v>
+        <v>0.1096691923237368</v>
       </c>
       <c r="T40">
-        <v>1.45474052395277</v>
+        <v>1.475039083689071</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4825,7 +4825,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>13.03420809217328</v>
+        <v>12.6999976282714</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4833,22 +4833,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08219946731747943</v>
+        <v>0.08204005052892283</v>
       </c>
       <c r="C41">
-        <v>9132.031614096664</v>
+        <v>8998.753276937703</v>
       </c>
       <c r="D41">
-        <v>13003.50161409666</v>
+        <v>13015.4532769377</v>
       </c>
       <c r="E41">
-        <v>2074.37</v>
+        <v>2219.600000000001</v>
       </c>
       <c r="F41">
-        <v>5663.97</v>
+        <v>5809.200000000001</v>
       </c>
       <c r="G41">
         <v>1792.5</v>
@@ -4869,28 +4869,28 @@
         <v>3618.2</v>
       </c>
       <c r="M41">
-        <v>284.8976910000001</v>
+        <v>292.2027600000001</v>
       </c>
       <c r="N41">
-        <v>3333.302309</v>
+        <v>3325.99724</v>
       </c>
       <c r="O41">
-        <v>733.32650798</v>
+        <v>731.7193927999999</v>
       </c>
       <c r="P41">
-        <v>2599.97580102</v>
+        <v>2594.2778472</v>
       </c>
       <c r="Q41">
-        <v>3545.77580102</v>
+        <v>3540.0778472</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1096691923237368</v>
+        <v>0.1105774175482047</v>
       </c>
       <c r="T41">
-        <v>1.475039083689071</v>
+        <v>1.49601426208325</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4907,7 +4907,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>12.6999976282714</v>
+        <v>12.38249768756462</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08204005052892283</v>
+        <v>0.08188063374036622</v>
       </c>
       <c r="C42">
-        <v>8998.753276937703</v>
+        <v>8865.496929802288</v>
       </c>
       <c r="D42">
-        <v>13015.4532769377</v>
+        <v>13027.42692980229</v>
       </c>
       <c r="E42">
-        <v>2219.600000000001</v>
+        <v>2364.83</v>
       </c>
       <c r="F42">
-        <v>5809.200000000001</v>
+        <v>5954.43</v>
       </c>
       <c r="G42">
         <v>1792.5</v>
@@ -4951,28 +4951,28 @@
         <v>3618.2</v>
       </c>
       <c r="M42">
-        <v>292.2027600000001</v>
+        <v>299.507829</v>
       </c>
       <c r="N42">
-        <v>3325.99724</v>
+        <v>3318.692171</v>
       </c>
       <c r="O42">
-        <v>731.7193927999999</v>
+        <v>730.11227762</v>
       </c>
       <c r="P42">
-        <v>2594.2778472</v>
+        <v>2588.57989338</v>
       </c>
       <c r="Q42">
-        <v>3540.0778472</v>
+        <v>3534.37989338</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1105774175482047</v>
+        <v>0.1115164300684173</v>
       </c>
       <c r="T42">
-        <v>1.49601426208325</v>
+        <v>1.517700463473841</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4989,7 +4989,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>12.38249768756462</v>
+        <v>12.08048554884353</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4997,22 +4997,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08188063374036622</v>
+        <v>0.08172121695180962</v>
       </c>
       <c r="C43">
-        <v>8865.496929802288</v>
+        <v>8732.262633435908</v>
       </c>
       <c r="D43">
-        <v>13027.42692980229</v>
+        <v>13039.42263343591</v>
       </c>
       <c r="E43">
-        <v>2364.83</v>
+        <v>2510.060000000001</v>
       </c>
       <c r="F43">
-        <v>5954.43</v>
+        <v>6099.660000000001</v>
       </c>
       <c r="G43">
         <v>1792.5</v>
@@ -5033,28 +5033,28 @@
         <v>3618.2</v>
       </c>
       <c r="M43">
-        <v>299.507829</v>
+        <v>306.8128980000001</v>
       </c>
       <c r="N43">
-        <v>3318.692171</v>
+        <v>3311.387102</v>
       </c>
       <c r="O43">
-        <v>730.11227762</v>
+        <v>728.5051624399999</v>
       </c>
       <c r="P43">
-        <v>2588.57989338</v>
+        <v>2582.88193956</v>
       </c>
       <c r="Q43">
-        <v>3534.37989338</v>
+        <v>3528.68193956</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1115164300684173</v>
+        <v>0.1124878223307062</v>
       </c>
       <c r="T43">
-        <v>1.517700463473841</v>
+        <v>1.540134464912384</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>12.08048554884353</v>
+        <v>11.79285494053773</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5079,22 +5079,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08172121695180962</v>
+        <v>0.081561800163253</v>
       </c>
       <c r="C44">
-        <v>8732.26263343591</v>
+        <v>8599.050448808004</v>
       </c>
       <c r="D44">
-        <v>13039.42263343591</v>
+        <v>13051.440448808</v>
       </c>
       <c r="E44">
-        <v>2510.06</v>
+        <v>2655.29</v>
       </c>
       <c r="F44">
-        <v>6099.66</v>
+        <v>6244.89</v>
       </c>
       <c r="G44">
         <v>1792.5</v>
@@ -5115,28 +5115,28 @@
         <v>3618.2</v>
       </c>
       <c r="M44">
-        <v>306.812898</v>
+        <v>314.117967</v>
       </c>
       <c r="N44">
-        <v>3311.387102</v>
+        <v>3304.082033</v>
       </c>
       <c r="O44">
-        <v>728.5051624399999</v>
+        <v>726.8980472599999</v>
       </c>
       <c r="P44">
-        <v>2582.88193956</v>
+        <v>2577.18398574</v>
       </c>
       <c r="Q44">
-        <v>3528.68193956</v>
+        <v>3522.98398574</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1124878223307062</v>
+        <v>0.1134932985320228</v>
       </c>
       <c r="T44">
-        <v>1.540134464912384</v>
+        <v>1.563355624296138</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>11.79285494053773</v>
+        <v>11.51860250006011</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5161,22 +5161,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.081561800163253</v>
+        <v>0.08140238337469638</v>
       </c>
       <c r="C45">
-        <v>8599.050448808004</v>
+        <v>8465.860437112973</v>
       </c>
       <c r="D45">
-        <v>13051.440448808</v>
+        <v>13063.48043711297</v>
       </c>
       <c r="E45">
-        <v>2655.29</v>
+        <v>2800.52</v>
       </c>
       <c r="F45">
-        <v>6244.89</v>
+        <v>6390.12</v>
       </c>
       <c r="G45">
         <v>1792.5</v>
@@ -5197,28 +5197,28 @@
         <v>3618.2</v>
       </c>
       <c r="M45">
-        <v>314.117967</v>
+        <v>321.423036</v>
       </c>
       <c r="N45">
-        <v>3304.082033</v>
+        <v>3296.776964</v>
       </c>
       <c r="O45">
-        <v>726.8980472599999</v>
+        <v>725.2909320799999</v>
       </c>
       <c r="P45">
-        <v>2577.18398574</v>
+        <v>2571.48603192</v>
       </c>
       <c r="Q45">
-        <v>3522.98398574</v>
+        <v>3517.28603192</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1134932985320228</v>
+        <v>0.1145346845976721</v>
       </c>
       <c r="T45">
-        <v>1.563355624296138</v>
+        <v>1.587406110800742</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5235,7 +5235,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>11.51860250006011</v>
+        <v>11.2568160796042</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5243,22 +5243,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08140238337469638</v>
+        <v>0.08124296658613978</v>
       </c>
       <c r="C46">
-        <v>8465.860437112973</v>
+        <v>8332.692659771254</v>
       </c>
       <c r="D46">
-        <v>13063.48043711297</v>
+        <v>13075.54265977125</v>
       </c>
       <c r="E46">
-        <v>2800.52</v>
+        <v>2945.75</v>
       </c>
       <c r="F46">
-        <v>6390.12</v>
+        <v>6535.35</v>
       </c>
       <c r="G46">
         <v>1792.5</v>
@@ -5279,28 +5279,28 @@
         <v>3618.2</v>
       </c>
       <c r="M46">
-        <v>321.423036</v>
+        <v>328.728105</v>
       </c>
       <c r="N46">
-        <v>3296.776964</v>
+        <v>3289.471895</v>
       </c>
       <c r="O46">
-        <v>725.2909320799999</v>
+        <v>723.6838168999999</v>
       </c>
       <c r="P46">
-        <v>2571.48603192</v>
+        <v>2565.7880781</v>
       </c>
       <c r="Q46">
-        <v>3517.28603192</v>
+        <v>3511.5880781</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1145346845976721</v>
+        <v>0.1156139392475269</v>
       </c>
       <c r="T46">
-        <v>1.587406110800742</v>
+        <v>1.612331160450966</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>11.2568160796042</v>
+        <v>11.00666461116855</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5325,22 +5325,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08124296658613978</v>
+        <v>0.08108354979758316</v>
       </c>
       <c r="C47">
-        <v>8332.692659771254</v>
+        <v>8199.54717843033</v>
       </c>
       <c r="D47">
-        <v>13075.54265977125</v>
+        <v>13087.62717843033</v>
       </c>
       <c r="E47">
-        <v>2945.75</v>
+        <v>3090.98</v>
       </c>
       <c r="F47">
-        <v>6535.35</v>
+        <v>6680.58</v>
       </c>
       <c r="G47">
         <v>1792.5</v>
@@ -5361,28 +5361,28 @@
         <v>3618.2</v>
       </c>
       <c r="M47">
-        <v>328.728105</v>
+        <v>336.033174</v>
       </c>
       <c r="N47">
-        <v>3289.471895</v>
+        <v>3282.166826</v>
       </c>
       <c r="O47">
-        <v>723.6838168999999</v>
+        <v>722.07670172</v>
       </c>
       <c r="P47">
-        <v>2565.7880781</v>
+        <v>2560.09012428</v>
       </c>
       <c r="Q47">
-        <v>3511.5880781</v>
+        <v>3505.890124279999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1156139392475269</v>
+        <v>0.1167331662918207</v>
       </c>
       <c r="T47">
-        <v>1.612331160450966</v>
+        <v>1.638179360088237</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5399,7 +5399,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>11.00666461116855</v>
+        <v>10.76738929353445</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5407,22 +5407,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08108354979758316</v>
+        <v>0.08092413300902655</v>
       </c>
       <c r="C48">
-        <v>8199.54717843033</v>
+        <v>8066.424054965803</v>
       </c>
       <c r="D48">
-        <v>13087.62717843033</v>
+        <v>13099.7340549658</v>
       </c>
       <c r="E48">
-        <v>3090.98</v>
+        <v>3236.21</v>
       </c>
       <c r="F48">
-        <v>6680.58</v>
+        <v>6825.81</v>
       </c>
       <c r="G48">
         <v>1792.5</v>
@@ -5443,28 +5443,28 @@
         <v>3618.2</v>
       </c>
       <c r="M48">
-        <v>336.033174</v>
+        <v>343.338243</v>
       </c>
       <c r="N48">
-        <v>3282.166826</v>
+        <v>3274.861757</v>
       </c>
       <c r="O48">
-        <v>722.07670172</v>
+        <v>720.4695865399999</v>
       </c>
       <c r="P48">
-        <v>2560.09012428</v>
+        <v>2554.39217046</v>
       </c>
       <c r="Q48">
-        <v>3505.890124279999</v>
+        <v>3500.19217046</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1167331662918207</v>
+        <v>0.117894628318918</v>
       </c>
       <c r="T48">
-        <v>1.638179360088237</v>
+        <v>1.665002963485404</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>10.76738929353445</v>
+        <v>10.53829590431031</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5489,22 +5489,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08092413300902655</v>
+        <v>0.08076471622046993</v>
       </c>
       <c r="C49">
-        <v>8066.424054965803</v>
+        <v>7933.323351482442</v>
       </c>
       <c r="D49">
-        <v>13099.7340549658</v>
+        <v>13111.86335148244</v>
       </c>
       <c r="E49">
-        <v>3236.21</v>
+        <v>3381.440000000001</v>
       </c>
       <c r="F49">
-        <v>6825.81</v>
+        <v>6971.040000000001</v>
       </c>
       <c r="G49">
         <v>1792.5</v>
@@ -5525,28 +5525,28 @@
         <v>3618.2</v>
       </c>
       <c r="M49">
-        <v>343.338243</v>
+        <v>350.6433120000001</v>
       </c>
       <c r="N49">
-        <v>3274.861757</v>
+        <v>3267.556688</v>
       </c>
       <c r="O49">
-        <v>720.4695865399999</v>
+        <v>718.86247136</v>
       </c>
       <c r="P49">
-        <v>2554.39217046</v>
+        <v>2548.694216639999</v>
       </c>
       <c r="Q49">
-        <v>3500.19217046</v>
+        <v>3494.49421664</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.117894628318918</v>
+        <v>0.1191007619624422</v>
       </c>
       <c r="T49">
-        <v>1.665002963485404</v>
+        <v>1.692858243936309</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5563,7 +5563,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>10.53829590431031</v>
+        <v>10.31874807297051</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5571,22 +5571,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08076471622046993</v>
+        <v>0.08060529943191332</v>
       </c>
       <c r="C50">
-        <v>7933.323351482443</v>
+        <v>7800.245130315247</v>
       </c>
       <c r="D50">
-        <v>13111.86335148244</v>
+        <v>13124.01513031525</v>
       </c>
       <c r="E50">
-        <v>3381.44</v>
+        <v>3526.67</v>
       </c>
       <c r="F50">
-        <v>6971.04</v>
+        <v>7116.27</v>
       </c>
       <c r="G50">
         <v>1792.5</v>
@@ -5607,28 +5607,28 @@
         <v>3618.2</v>
       </c>
       <c r="M50">
-        <v>350.643312</v>
+        <v>357.948381</v>
       </c>
       <c r="N50">
-        <v>3267.556688</v>
+        <v>3260.251619</v>
       </c>
       <c r="O50">
-        <v>718.86247136</v>
+        <v>717.2553561799999</v>
       </c>
       <c r="P50">
-        <v>2548.694216639999</v>
+        <v>2542.99626282</v>
       </c>
       <c r="Q50">
-        <v>3494.49421664</v>
+        <v>3488.796262819999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1191007619624422</v>
+        <v>0.1203541949645359</v>
       </c>
       <c r="T50">
-        <v>1.692858243936309</v>
+        <v>1.721805888326465</v>
       </c>
       <c r="U50">
         <v>0.0503</v>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>10.31874807297052</v>
+        <v>10.10816137760377</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5653,22 +5653,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08060529943191332</v>
+        <v>0.0804458826433567</v>
       </c>
       <c r="C51">
-        <v>7800.245130315247</v>
+        <v>7667.189454030502</v>
       </c>
       <c r="D51">
-        <v>13124.01513031525</v>
+        <v>13136.1894540305</v>
       </c>
       <c r="E51">
-        <v>3526.67</v>
+        <v>3671.9</v>
       </c>
       <c r="F51">
-        <v>7116.27</v>
+        <v>7261.5</v>
       </c>
       <c r="G51">
         <v>1792.5</v>
@@ -5689,28 +5689,28 @@
         <v>3618.2</v>
       </c>
       <c r="M51">
-        <v>357.948381</v>
+        <v>365.25345</v>
       </c>
       <c r="N51">
-        <v>3260.251619</v>
+        <v>3252.94655</v>
       </c>
       <c r="O51">
-        <v>717.2553561799999</v>
+        <v>715.648241</v>
       </c>
       <c r="P51">
-        <v>2542.99626282</v>
+        <v>2537.298309</v>
       </c>
       <c r="Q51">
-        <v>3488.796262819999</v>
+        <v>3483.098309</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1203541949645359</v>
+        <v>0.1216577652867134</v>
       </c>
       <c r="T51">
-        <v>1.721805888326465</v>
+        <v>1.751911438492227</v>
       </c>
       <c r="U51">
         <v>0.0503</v>
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>10.10816137760377</v>
+        <v>9.905998150051696</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5735,22 +5735,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.0804458826433567</v>
+        <v>0.08028646585480011</v>
       </c>
       <c r="C52">
-        <v>7667.189454030502</v>
+        <v>7534.156385426876</v>
       </c>
       <c r="D52">
-        <v>13136.1894540305</v>
+        <v>13148.38638542688</v>
       </c>
       <c r="E52">
-        <v>3671.9</v>
+        <v>3817.130000000001</v>
       </c>
       <c r="F52">
-        <v>7261.5</v>
+        <v>7406.73</v>
       </c>
       <c r="G52">
         <v>1792.5</v>
@@ -5771,28 +5771,28 @@
         <v>3618.2</v>
       </c>
       <c r="M52">
-        <v>365.25345</v>
+        <v>372.558519</v>
       </c>
       <c r="N52">
-        <v>3252.94655</v>
+        <v>3245.641481</v>
       </c>
       <c r="O52">
-        <v>715.648241</v>
+        <v>714.0411258199999</v>
       </c>
       <c r="P52">
-        <v>2537.298309</v>
+        <v>2531.600355179999</v>
       </c>
       <c r="Q52">
-        <v>3483.098309</v>
+        <v>3477.40035518</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1216577652867134</v>
+        <v>0.1230145425608165</v>
       </c>
       <c r="T52">
-        <v>1.751911438492227</v>
+        <v>1.783245786623938</v>
       </c>
       <c r="U52">
         <v>0.0503</v>
@@ -5809,7 +5809,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>9.905998150051696</v>
+        <v>9.711762892207544</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5817,22 +5817,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08028646585480011</v>
+        <v>0.08012704906624349</v>
       </c>
       <c r="C53">
-        <v>7534.156385426876</v>
+        <v>7401.145987536486</v>
       </c>
       <c r="D53">
-        <v>13148.38638542688</v>
+        <v>13160.60598753649</v>
       </c>
       <c r="E53">
-        <v>3817.130000000001</v>
+        <v>3962.36</v>
       </c>
       <c r="F53">
-        <v>7406.73</v>
+        <v>7551.96</v>
       </c>
       <c r="G53">
         <v>1792.5</v>
@@ -5853,28 +5853,28 @@
         <v>3618.2</v>
       </c>
       <c r="M53">
-        <v>372.558519</v>
+        <v>379.863588</v>
       </c>
       <c r="N53">
-        <v>3245.641481</v>
+        <v>3238.336412</v>
       </c>
       <c r="O53">
-        <v>714.0411258199999</v>
+        <v>712.4340106399999</v>
       </c>
       <c r="P53">
-        <v>2531.600355179999</v>
+        <v>2525.90240136</v>
       </c>
       <c r="Q53">
-        <v>3477.40035518</v>
+        <v>3471.702401359999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1230145425608165</v>
+        <v>0.1244278522213406</v>
       </c>
       <c r="T53">
-        <v>1.783245786623938</v>
+        <v>1.815885732594471</v>
       </c>
       <c r="U53">
         <v>0.0503</v>
@@ -5891,7 +5891,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>9.711762892207544</v>
+        <v>9.524998221203553</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5899,22 +5899,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08012704906624349</v>
+        <v>0.07996763227768688</v>
       </c>
       <c r="C54">
-        <v>7401.145987536486</v>
+        <v>7268.158323625985</v>
       </c>
       <c r="D54">
-        <v>13160.60598753649</v>
+        <v>13172.84832362599</v>
       </c>
       <c r="E54">
-        <v>3962.36</v>
+        <v>4107.59</v>
       </c>
       <c r="F54">
-        <v>7551.96</v>
+        <v>7697.190000000001</v>
       </c>
       <c r="G54">
         <v>1792.5</v>
@@ -5935,28 +5935,28 @@
         <v>3618.2</v>
       </c>
       <c r="M54">
-        <v>379.863588</v>
+        <v>387.1686570000001</v>
       </c>
       <c r="N54">
-        <v>3238.336412</v>
+        <v>3231.031343</v>
       </c>
       <c r="O54">
-        <v>712.4340106399999</v>
+        <v>710.8268954599999</v>
       </c>
       <c r="P54">
-        <v>2525.90240136</v>
+        <v>2520.20444754</v>
       </c>
       <c r="Q54">
-        <v>3471.702401359999</v>
+        <v>3466.00444754</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1244278522213406</v>
+        <v>0.1259013027184827</v>
       </c>
       <c r="T54">
-        <v>1.815885732594471</v>
+        <v>1.84991461243609</v>
       </c>
       <c r="U54">
         <v>0.0503</v>
@@ -5973,7 +5973,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>9.524998221203553</v>
+        <v>9.345281273633674</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07996763227768688</v>
+        <v>0.07980821548913027</v>
       </c>
       <c r="C55">
-        <v>7268.158323625985</v>
+        <v>7135.193457197649</v>
       </c>
       <c r="D55">
-        <v>13172.84832362599</v>
+        <v>13185.11345719765</v>
       </c>
       <c r="E55">
-        <v>4107.59</v>
+        <v>4252.82</v>
       </c>
       <c r="F55">
-        <v>7697.190000000001</v>
+        <v>7842.42</v>
       </c>
       <c r="G55">
         <v>1792.5</v>
@@ -6017,28 +6017,28 @@
         <v>3618.2</v>
       </c>
       <c r="M55">
-        <v>387.1686570000001</v>
+        <v>394.4737260000001</v>
       </c>
       <c r="N55">
-        <v>3231.031343</v>
+        <v>3223.726274</v>
       </c>
       <c r="O55">
-        <v>710.8268954599999</v>
+        <v>709.2197802799999</v>
       </c>
       <c r="P55">
-        <v>2520.20444754</v>
+        <v>2514.50649372</v>
       </c>
       <c r="Q55">
-        <v>3466.00444754</v>
+        <v>3460.30649372</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1259013027184827</v>
+        <v>0.127438816280718</v>
       </c>
       <c r="T55">
-        <v>1.84991461243609</v>
+        <v>1.885423008792563</v>
       </c>
       <c r="U55">
         <v>0.0503</v>
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>9.345281273633674</v>
+        <v>9.172220509307126</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6063,22 +6063,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07980821548913027</v>
+        <v>0.07964879870057365</v>
       </c>
       <c r="C56">
-        <v>7135.193457197649</v>
+        <v>7002.251451990483</v>
       </c>
       <c r="D56">
-        <v>13185.11345719765</v>
+        <v>13197.40145199048</v>
       </c>
       <c r="E56">
-        <v>4252.82</v>
+        <v>4398.050000000001</v>
       </c>
       <c r="F56">
-        <v>7842.42</v>
+        <v>7987.650000000001</v>
       </c>
       <c r="G56">
         <v>1792.5</v>
@@ -6099,28 +6099,28 @@
         <v>3618.2</v>
       </c>
       <c r="M56">
-        <v>394.4737260000001</v>
+        <v>401.7787950000001</v>
       </c>
       <c r="N56">
-        <v>3223.726274</v>
+        <v>3216.421205</v>
       </c>
       <c r="O56">
-        <v>709.2197802799999</v>
+        <v>707.6126651</v>
       </c>
       <c r="P56">
-        <v>2514.50649372</v>
+        <v>2508.8085399</v>
       </c>
       <c r="Q56">
-        <v>3460.30649372</v>
+        <v>3454.608539899999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.127438816280718</v>
+        <v>0.1290446637790525</v>
       </c>
       <c r="T56">
-        <v>1.885423008792563</v>
+        <v>1.922509556098212</v>
       </c>
       <c r="U56">
         <v>0.0503</v>
@@ -6137,7 +6137,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>9.172220509307126</v>
+        <v>9.00545286368336</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6145,22 +6145,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07964879870057365</v>
+        <v>0.07948938191201704</v>
       </c>
       <c r="C57">
-        <v>7002.251451990483</v>
+        <v>6869.332371981327</v>
       </c>
       <c r="D57">
-        <v>13197.40145199048</v>
+        <v>13209.71237198133</v>
       </c>
       <c r="E57">
-        <v>4398.050000000001</v>
+        <v>4543.280000000001</v>
       </c>
       <c r="F57">
-        <v>7987.650000000001</v>
+        <v>8132.880000000001</v>
       </c>
       <c r="G57">
         <v>1792.5</v>
@@ -6181,28 +6181,28 @@
         <v>3618.2</v>
       </c>
       <c r="M57">
-        <v>401.7787950000001</v>
+        <v>409.0838640000001</v>
       </c>
       <c r="N57">
-        <v>3216.421205</v>
+        <v>3209.116136</v>
       </c>
       <c r="O57">
-        <v>707.6126651</v>
+        <v>706.0055499199999</v>
       </c>
       <c r="P57">
-        <v>2508.8085399</v>
+        <v>2503.11058608</v>
       </c>
       <c r="Q57">
-        <v>3454.608539899999</v>
+        <v>3448.91058608</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1290446637790525</v>
+        <v>0.1307235043454933</v>
       </c>
       <c r="T57">
-        <v>1.922509556098212</v>
+        <v>1.961281855554117</v>
       </c>
       <c r="U57">
         <v>0.0503</v>
@@ -6219,7 +6219,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>9.00545286368336</v>
+        <v>8.844641205403299</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6227,22 +6227,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07948938191201704</v>
+        <v>0.07999686512346042</v>
       </c>
       <c r="C58">
-        <v>6869.332371981327</v>
+        <v>6684.991696148094</v>
       </c>
       <c r="D58">
-        <v>13209.71237198133</v>
+        <v>13170.60169614809</v>
       </c>
       <c r="E58">
-        <v>4543.280000000001</v>
+        <v>4688.51</v>
       </c>
       <c r="F58">
-        <v>8132.880000000001</v>
+        <v>8278.110000000001</v>
       </c>
       <c r="G58">
         <v>1792.5</v>
@@ -6263,45 +6263,45 @@
         <v>3618.2</v>
       </c>
       <c r="M58">
-        <v>409.0838640000001</v>
+        <v>428.8060980000001</v>
       </c>
       <c r="N58">
-        <v>3209.116136</v>
+        <v>3189.393902</v>
       </c>
       <c r="O58">
-        <v>706.0055499199999</v>
+        <v>701.66665844</v>
       </c>
       <c r="P58">
-        <v>2503.11058608</v>
+        <v>2487.72724356</v>
       </c>
       <c r="Q58">
-        <v>3448.91058608</v>
+        <v>3433.52724356</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1307235043454933</v>
+        <v>0.1324804305196754</v>
       </c>
       <c r="T58">
-        <v>1.961281855554117</v>
+        <v>2.001857517775414</v>
       </c>
       <c r="U58">
-        <v>0.0503</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V58">
         <v>0.22</v>
       </c>
       <c r="W58">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y58">
-        <v>8.844641205403299</v>
+        <v>8.437846422603812</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6309,22 +6309,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07999686512346042</v>
+        <v>0.07984914833490381</v>
       </c>
       <c r="C59">
-        <v>6684.991696148094</v>
+        <v>6551.122006410442</v>
       </c>
       <c r="D59">
-        <v>13170.60169614809</v>
+        <v>13181.96200641044</v>
       </c>
       <c r="E59">
-        <v>4688.51</v>
+        <v>4833.74</v>
       </c>
       <c r="F59">
-        <v>8278.110000000001</v>
+        <v>8423.34</v>
       </c>
       <c r="G59">
         <v>1792.5</v>
@@ -6345,28 +6345,28 @@
         <v>3618.2</v>
       </c>
       <c r="M59">
-        <v>428.8060980000001</v>
+        <v>436.329012</v>
       </c>
       <c r="N59">
-        <v>3189.393902</v>
+        <v>3181.870988</v>
       </c>
       <c r="O59">
-        <v>701.66665844</v>
+        <v>700.0116173599999</v>
       </c>
       <c r="P59">
-        <v>2487.72724356</v>
+        <v>2481.85937064</v>
       </c>
       <c r="Q59">
-        <v>3433.52724356</v>
+        <v>3427.65937064</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1324804305196754</v>
+        <v>0.1343210198450091</v>
       </c>
       <c r="T59">
-        <v>2.001857517775414</v>
+        <v>2.044365354388201</v>
       </c>
       <c r="U59">
         <v>0.05180000000000001</v>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>8.437846422603812</v>
+        <v>8.292366311869262</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6391,22 +6391,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07984914833490381</v>
+        <v>0.07970143154634721</v>
       </c>
       <c r="C60">
-        <v>6551.122006410442</v>
+        <v>6417.271931276011</v>
       </c>
       <c r="D60">
-        <v>13181.96200641044</v>
+        <v>13193.34193127601</v>
       </c>
       <c r="E60">
-        <v>4833.74</v>
+        <v>4978.969999999999</v>
       </c>
       <c r="F60">
-        <v>8423.34</v>
+        <v>8568.57</v>
       </c>
       <c r="G60">
         <v>1792.5</v>
@@ -6427,28 +6427,28 @@
         <v>3618.2</v>
       </c>
       <c r="M60">
-        <v>436.329012</v>
+        <v>443.851926</v>
       </c>
       <c r="N60">
-        <v>3181.870988</v>
+        <v>3174.348074</v>
       </c>
       <c r="O60">
-        <v>700.0116173599999</v>
+        <v>698.3565762799999</v>
       </c>
       <c r="P60">
-        <v>2481.85937064</v>
+        <v>2475.99149772</v>
       </c>
       <c r="Q60">
-        <v>3427.65937064</v>
+        <v>3421.79149772</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.134321019845009</v>
+        <v>0.136251394015481</v>
       </c>
       <c r="T60">
-        <v>2.0443653543882</v>
+        <v>2.088946744006489</v>
       </c>
       <c r="U60">
         <v>0.05180000000000001</v>
@@ -6465,7 +6465,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>8.292366311869262</v>
+        <v>8.151817730312157</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6473,22 +6473,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07970143154634721</v>
+        <v>0.07955371475779059</v>
       </c>
       <c r="C61">
-        <v>6417.271931276011</v>
+        <v>6283.441521588278</v>
       </c>
       <c r="D61">
-        <v>13193.34193127601</v>
+        <v>13204.74152158828</v>
       </c>
       <c r="E61">
-        <v>4978.969999999999</v>
+        <v>5124.199999999999</v>
       </c>
       <c r="F61">
-        <v>8568.57</v>
+        <v>8713.799999999999</v>
       </c>
       <c r="G61">
         <v>1792.5</v>
@@ -6509,28 +6509,28 @@
         <v>3618.2</v>
       </c>
       <c r="M61">
-        <v>443.851926</v>
+        <v>451.37484</v>
       </c>
       <c r="N61">
-        <v>3174.348074</v>
+        <v>3166.82516</v>
       </c>
       <c r="O61">
-        <v>698.3565762799999</v>
+        <v>696.7015352</v>
       </c>
       <c r="P61">
-        <v>2475.99149772</v>
+        <v>2470.1236248</v>
       </c>
       <c r="Q61">
-        <v>3421.79149772</v>
+        <v>3415.9236248</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.136251394015481</v>
+        <v>0.1382782868944765</v>
       </c>
       <c r="T61">
-        <v>2.088946744006489</v>
+        <v>2.135757203105692</v>
       </c>
       <c r="U61">
         <v>0.05180000000000001</v>
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>8.151817730312157</v>
+        <v>8.015954101473621</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6555,22 +6555,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07955371475779059</v>
+        <v>0.07940599796923398</v>
       </c>
       <c r="C62">
-        <v>6283.441521588278</v>
+        <v>6149.630828366589</v>
       </c>
       <c r="D62">
-        <v>13204.74152158828</v>
+        <v>13216.16082836659</v>
       </c>
       <c r="E62">
-        <v>5124.199999999999</v>
+        <v>5269.43</v>
       </c>
       <c r="F62">
-        <v>8713.799999999999</v>
+        <v>8859.030000000001</v>
       </c>
       <c r="G62">
         <v>1792.5</v>
@@ -6591,28 +6591,28 @@
         <v>3618.2</v>
       </c>
       <c r="M62">
-        <v>451.37484</v>
+        <v>458.8977540000001</v>
       </c>
       <c r="N62">
-        <v>3166.82516</v>
+        <v>3159.302246</v>
       </c>
       <c r="O62">
-        <v>696.7015352</v>
+        <v>695.0464941199999</v>
       </c>
       <c r="P62">
-        <v>2470.1236248</v>
+        <v>2464.25575188</v>
       </c>
       <c r="Q62">
-        <v>3415.9236248</v>
+        <v>3410.05575188</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1382782868944765</v>
+        <v>0.1404091229980358</v>
       </c>
       <c r="T62">
-        <v>2.135757203105692</v>
+        <v>2.184968198568957</v>
       </c>
       <c r="U62">
         <v>0.05180000000000001</v>
@@ -6629,7 +6629,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>8.015954101473621</v>
+        <v>7.884545017842905</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6637,22 +6637,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07940599796923398</v>
+        <v>0.07925828118067736</v>
       </c>
       <c r="C63">
-        <v>6149.630828366589</v>
+        <v>6015.839902806933</v>
       </c>
       <c r="D63">
-        <v>13216.16082836659</v>
+        <v>13227.59990280693</v>
       </c>
       <c r="E63">
-        <v>5269.43</v>
+        <v>5414.66</v>
       </c>
       <c r="F63">
-        <v>8859.030000000001</v>
+        <v>9004.26</v>
       </c>
       <c r="G63">
         <v>1792.5</v>
@@ -6673,28 +6673,28 @@
         <v>3618.2</v>
       </c>
       <c r="M63">
-        <v>458.8977540000001</v>
+        <v>466.4206680000001</v>
       </c>
       <c r="N63">
-        <v>3159.302246</v>
+        <v>3151.779332</v>
       </c>
       <c r="O63">
-        <v>695.0464941199999</v>
+        <v>693.3914530399999</v>
       </c>
       <c r="P63">
-        <v>2464.25575188</v>
+        <v>2458.38787896</v>
       </c>
       <c r="Q63">
-        <v>3410.05575188</v>
+        <v>3404.18787896</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1404091229980358</v>
+        <v>0.1426521083702036</v>
       </c>
       <c r="T63">
-        <v>2.184968198568957</v>
+        <v>2.236769246425025</v>
       </c>
       <c r="U63">
         <v>0.05180000000000001</v>
@@ -6711,7 +6711,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>7.884545017842905</v>
+        <v>7.757374936909954</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6719,22 +6719,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07925828118067736</v>
+        <v>0.07911056439212075</v>
       </c>
       <c r="C64">
-        <v>6015.839902806933</v>
+        <v>5882.068796282694</v>
       </c>
       <c r="D64">
-        <v>13227.59990280693</v>
+        <v>13239.05879628269</v>
       </c>
       <c r="E64">
-        <v>5414.66</v>
+        <v>5559.889999999999</v>
       </c>
       <c r="F64">
-        <v>9004.26</v>
+        <v>9149.49</v>
       </c>
       <c r="G64">
         <v>1792.5</v>
@@ -6755,28 +6755,28 @@
         <v>3618.2</v>
       </c>
       <c r="M64">
-        <v>466.4206680000001</v>
+        <v>473.943582</v>
       </c>
       <c r="N64">
-        <v>3151.779332</v>
+        <v>3144.256418</v>
       </c>
       <c r="O64">
-        <v>693.3914530399999</v>
+        <v>691.7364119599999</v>
       </c>
       <c r="P64">
-        <v>2458.38787896</v>
+        <v>2452.52000604</v>
       </c>
       <c r="Q64">
-        <v>3404.18787896</v>
+        <v>3398.32000604</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1426521083702036</v>
+        <v>0.1450163361949209</v>
       </c>
       <c r="T64">
-        <v>2.236769246425025</v>
+        <v>2.291370350921962</v>
       </c>
       <c r="U64">
         <v>0.05180000000000001</v>
@@ -6793,7 +6793,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>7.757374936909954</v>
+        <v>7.634242001403449</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6801,22 +6801,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07911056439212075</v>
+        <v>0.07896284760356415</v>
       </c>
       <c r="C65">
-        <v>5882.068796282694</v>
+        <v>5748.317560345426</v>
       </c>
       <c r="D65">
-        <v>13239.05879628269</v>
+        <v>13250.53756034542</v>
       </c>
       <c r="E65">
-        <v>5559.889999999999</v>
+        <v>5705.119999999999</v>
       </c>
       <c r="F65">
-        <v>9149.49</v>
+        <v>9294.719999999999</v>
       </c>
       <c r="G65">
         <v>1792.5</v>
@@ -6837,28 +6837,28 @@
         <v>3618.2</v>
       </c>
       <c r="M65">
-        <v>473.943582</v>
+        <v>481.466496</v>
       </c>
       <c r="N65">
-        <v>3144.256418</v>
+        <v>3136.733504</v>
       </c>
       <c r="O65">
-        <v>691.7364119599999</v>
+        <v>690.08137088</v>
       </c>
       <c r="P65">
-        <v>2452.52000604</v>
+        <v>2446.65213312</v>
       </c>
       <c r="Q65">
-        <v>3398.32000604</v>
+        <v>3392.452133119999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1450163361949209</v>
+        <v>0.1475119100099004</v>
       </c>
       <c r="T65">
-        <v>2.291370350921962</v>
+        <v>2.349004850113173</v>
       </c>
       <c r="U65">
         <v>0.05180000000000001</v>
@@ -6875,7 +6875,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>7.634242001403449</v>
+        <v>7.514956970131521</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6883,22 +6883,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07896284760356415</v>
+        <v>0.07881513081500753</v>
       </c>
       <c r="C66">
-        <v>5748.317560345426</v>
+        <v>5614.58624672563</v>
       </c>
       <c r="D66">
-        <v>13250.53756034542</v>
+        <v>13262.03624672563</v>
       </c>
       <c r="E66">
-        <v>5705.119999999999</v>
+        <v>5850.35</v>
       </c>
       <c r="F66">
-        <v>9294.719999999999</v>
+        <v>9439.950000000001</v>
       </c>
       <c r="G66">
         <v>1792.5</v>
@@ -6919,28 +6919,28 @@
         <v>3618.2</v>
       </c>
       <c r="M66">
-        <v>481.466496</v>
+        <v>488.9894100000001</v>
       </c>
       <c r="N66">
-        <v>3136.733504</v>
+        <v>3129.21059</v>
       </c>
       <c r="O66">
-        <v>690.08137088</v>
+        <v>688.4263298</v>
       </c>
       <c r="P66">
-        <v>2446.65213312</v>
+        <v>2440.7842602</v>
       </c>
       <c r="Q66">
-        <v>3392.452133119999</v>
+        <v>3386.584260199999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1475119100099004</v>
+        <v>0.1501500880428787</v>
       </c>
       <c r="T66">
-        <v>2.349004850113173</v>
+        <v>2.409932749258167</v>
       </c>
       <c r="U66">
         <v>0.05180000000000001</v>
@@ -6957,7 +6957,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>7.514956970131521</v>
+        <v>7.399342247514111</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6965,22 +6965,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07881513081500753</v>
+        <v>0.07866741402645092</v>
       </c>
       <c r="C67">
-        <v>5614.58624672563</v>
+        <v>5480.874907333531</v>
       </c>
       <c r="D67">
-        <v>13262.03624672563</v>
+        <v>13273.55490733353</v>
       </c>
       <c r="E67">
-        <v>5850.35</v>
+        <v>5995.58</v>
       </c>
       <c r="F67">
-        <v>9439.950000000001</v>
+        <v>9585.18</v>
       </c>
       <c r="G67">
         <v>1792.5</v>
@@ -7001,28 +7001,28 @@
         <v>3618.2</v>
       </c>
       <c r="M67">
-        <v>488.9894100000001</v>
+        <v>496.5123240000001</v>
       </c>
       <c r="N67">
-        <v>3129.21059</v>
+        <v>3121.687676</v>
       </c>
       <c r="O67">
-        <v>688.4263298</v>
+        <v>686.7712887199999</v>
       </c>
       <c r="P67">
-        <v>2440.7842602</v>
+        <v>2434.91638728</v>
       </c>
       <c r="Q67">
-        <v>3386.584260199999</v>
+        <v>3380.716387279999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1501500880428787</v>
+        <v>0.1529434530189733</v>
       </c>
       <c r="T67">
-        <v>2.409932749258167</v>
+        <v>2.474444642470515</v>
       </c>
       <c r="U67">
         <v>0.05180000000000001</v>
@@ -7039,7 +7039,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>7.399342247514111</v>
+        <v>7.287231001339655</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7047,22 +7047,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07866741402645092</v>
+        <v>0.0785196972378943</v>
       </c>
       <c r="C68">
-        <v>5480.874907333531</v>
+        <v>5347.183594259854</v>
       </c>
       <c r="D68">
-        <v>13273.55490733353</v>
+        <v>13285.09359425985</v>
       </c>
       <c r="E68">
-        <v>5995.58</v>
+        <v>6140.809999999999</v>
       </c>
       <c r="F68">
-        <v>9585.18</v>
+        <v>9730.41</v>
       </c>
       <c r="G68">
         <v>1792.5</v>
@@ -7083,28 +7083,28 @@
         <v>3618.2</v>
       </c>
       <c r="M68">
-        <v>496.5123240000001</v>
+        <v>504.035238</v>
       </c>
       <c r="N68">
-        <v>3121.687676</v>
+        <v>3114.164762</v>
       </c>
       <c r="O68">
-        <v>686.7712887199999</v>
+        <v>685.11624764</v>
       </c>
       <c r="P68">
-        <v>2434.91638728</v>
+        <v>2429.04851436</v>
       </c>
       <c r="Q68">
-        <v>3380.716387279999</v>
+        <v>3374.84851436</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1529434530189733</v>
+        <v>0.155906112842104</v>
       </c>
       <c r="T68">
-        <v>2.474444642470515</v>
+        <v>2.542866347392701</v>
       </c>
       <c r="U68">
         <v>0.05180000000000001</v>
@@ -7121,7 +7121,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>7.287231001339655</v>
+        <v>7.178466359528616</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7129,22 +7129,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.0785196972378943</v>
+        <v>0.07837198044933769</v>
       </c>
       <c r="C69">
-        <v>5347.183594259854</v>
+        <v>5213.512359776605</v>
       </c>
       <c r="D69">
-        <v>13285.09359425985</v>
+        <v>13296.65235977661</v>
       </c>
       <c r="E69">
-        <v>6140.809999999999</v>
+        <v>6286.040000000001</v>
       </c>
       <c r="F69">
-        <v>9730.41</v>
+        <v>9875.640000000001</v>
       </c>
       <c r="G69">
         <v>1792.5</v>
@@ -7165,28 +7165,28 @@
         <v>3618.2</v>
       </c>
       <c r="M69">
-        <v>504.035238</v>
+        <v>511.5581520000001</v>
       </c>
       <c r="N69">
-        <v>3114.164762</v>
+        <v>3106.641848</v>
       </c>
       <c r="O69">
-        <v>685.11624764</v>
+        <v>683.4612065599999</v>
       </c>
       <c r="P69">
-        <v>2429.04851436</v>
+        <v>2423.18064144</v>
       </c>
       <c r="Q69">
-        <v>3374.84851436</v>
+        <v>3368.98064144</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.155906112842104</v>
+        <v>0.1590539389041803</v>
       </c>
       <c r="T69">
-        <v>2.542866347392701</v>
+        <v>2.615564408872524</v>
       </c>
       <c r="U69">
         <v>0.05180000000000001</v>
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>7.178466359528616</v>
+        <v>7.072900677770841</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7211,22 +7211,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07837198044933769</v>
+        <v>0.07822426366078108</v>
       </c>
       <c r="C70">
-        <v>5213.512359776605</v>
+        <v>5079.861256337872</v>
       </c>
       <c r="D70">
-        <v>13296.65235977661</v>
+        <v>13308.23125633787</v>
       </c>
       <c r="E70">
-        <v>6286.040000000001</v>
+        <v>6431.27</v>
       </c>
       <c r="F70">
-        <v>9875.640000000001</v>
+        <v>10020.87</v>
       </c>
       <c r="G70">
         <v>1792.5</v>
@@ -7247,28 +7247,28 @@
         <v>3618.2</v>
       </c>
       <c r="M70">
-        <v>511.5581520000001</v>
+        <v>519.0810660000001</v>
       </c>
       <c r="N70">
-        <v>3106.641848</v>
+        <v>3099.118934</v>
       </c>
       <c r="O70">
-        <v>683.4612065599999</v>
+        <v>681.8061654799999</v>
       </c>
       <c r="P70">
-        <v>2423.18064144</v>
+        <v>2417.31276852</v>
       </c>
       <c r="Q70">
-        <v>3368.98064144</v>
+        <v>3363.11276852</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1590539389041803</v>
+        <v>0.1624048505186487</v>
       </c>
       <c r="T70">
-        <v>2.615564408872524</v>
+        <v>2.692952667867175</v>
       </c>
       <c r="U70">
         <v>0.05180000000000001</v>
@@ -7285,7 +7285,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>7.072900677770841</v>
+        <v>6.970394870846627</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7293,22 +7293,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07822426366078108</v>
+        <v>0.07807654687222446</v>
       </c>
       <c r="C71">
-        <v>5079.861256337872</v>
+        <v>4946.230336580616</v>
       </c>
       <c r="D71">
-        <v>13308.23125633787</v>
+        <v>13319.83033658062</v>
       </c>
       <c r="E71">
-        <v>6431.27</v>
+        <v>6576.5</v>
       </c>
       <c r="F71">
-        <v>10020.87</v>
+        <v>10166.1</v>
       </c>
       <c r="G71">
         <v>1792.5</v>
@@ -7329,28 +7329,28 @@
         <v>3618.2</v>
       </c>
       <c r="M71">
-        <v>519.0810660000001</v>
+        <v>526.6039800000001</v>
       </c>
       <c r="N71">
-        <v>3099.118934</v>
+        <v>3091.59602</v>
       </c>
       <c r="O71">
-        <v>681.8061654799999</v>
+        <v>680.1511244</v>
       </c>
       <c r="P71">
-        <v>2417.31276852</v>
+        <v>2411.4448956</v>
       </c>
       <c r="Q71">
-        <v>3363.11276852</v>
+        <v>3357.2448956</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1624048505186487</v>
+        <v>0.1659791562407482</v>
       </c>
       <c r="T71">
-        <v>2.692952667867175</v>
+        <v>2.775500144128135</v>
       </c>
       <c r="U71">
         <v>0.05180000000000001</v>
@@ -7367,7 +7367,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>6.970394870846627</v>
+        <v>6.870817801263104</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7375,22 +7375,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07807654687222446</v>
+        <v>0.07792883008366785</v>
       </c>
       <c r="C72">
-        <v>4946.230336580616</v>
+        <v>4812.619653325459</v>
       </c>
       <c r="D72">
-        <v>13319.83033658062</v>
+        <v>13331.44965332546</v>
       </c>
       <c r="E72">
-        <v>6576.5</v>
+        <v>6721.730000000001</v>
       </c>
       <c r="F72">
-        <v>10166.1</v>
+        <v>10311.33</v>
       </c>
       <c r="G72">
         <v>1792.5</v>
@@ -7411,28 +7411,28 @@
         <v>3618.2</v>
       </c>
       <c r="M72">
-        <v>526.6039800000001</v>
+        <v>534.1268940000001</v>
       </c>
       <c r="N72">
-        <v>3091.59602</v>
+        <v>3084.073106</v>
       </c>
       <c r="O72">
-        <v>680.1511244</v>
+        <v>678.4960833199999</v>
       </c>
       <c r="P72">
-        <v>2411.4448956</v>
+        <v>2405.57702268</v>
       </c>
       <c r="Q72">
-        <v>3357.2448956</v>
+        <v>3351.37702268</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1659791562407482</v>
+        <v>0.1697999658057513</v>
       </c>
       <c r="T72">
-        <v>2.775500144128135</v>
+        <v>2.863740549786403</v>
       </c>
       <c r="U72">
         <v>0.05180000000000001</v>
@@ -7449,7 +7449,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>6.870817801263104</v>
+        <v>6.774045719555172</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7457,22 +7457,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07792883008366785</v>
+        <v>0.07873583329511125</v>
       </c>
       <c r="C73">
-        <v>4812.619653325461</v>
+        <v>4604.157222647918</v>
       </c>
       <c r="D73">
-        <v>13331.44965332546</v>
+        <v>13268.21722264792</v>
       </c>
       <c r="E73">
-        <v>6721.73</v>
+        <v>6866.959999999999</v>
       </c>
       <c r="F73">
-        <v>10311.33</v>
+        <v>10456.56</v>
       </c>
       <c r="G73">
         <v>1792.5</v>
@@ -7493,45 +7493,45 @@
         <v>3618.2</v>
       </c>
       <c r="M73">
-        <v>534.1268940000001</v>
+        <v>559.42596</v>
       </c>
       <c r="N73">
-        <v>3084.073106</v>
+        <v>3058.77404</v>
       </c>
       <c r="O73">
-        <v>678.4960833199999</v>
+        <v>672.9302888</v>
       </c>
       <c r="P73">
-        <v>2405.57702268</v>
+        <v>2385.8437512</v>
       </c>
       <c r="Q73">
-        <v>3351.37702268</v>
+        <v>3331.6437512</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1697999658057512</v>
+        <v>0.173893690339683</v>
       </c>
       <c r="T73">
-        <v>2.863740549786402</v>
+        <v>2.958283841563118</v>
       </c>
       <c r="U73">
-        <v>0.05180000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V73">
         <v>0.22</v>
       </c>
       <c r="W73">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y73">
-        <v>6.774045719555172</v>
+        <v>6.467701284366567</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7539,22 +7539,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07873583329511125</v>
+        <v>0.07860137650655463</v>
       </c>
       <c r="C74">
-        <v>4604.157222647918</v>
+        <v>4469.420855980166</v>
       </c>
       <c r="D74">
-        <v>13268.21722264792</v>
+        <v>13278.71085598017</v>
       </c>
       <c r="E74">
-        <v>6866.959999999999</v>
+        <v>7012.189999999999</v>
       </c>
       <c r="F74">
-        <v>10456.56</v>
+        <v>10601.79</v>
       </c>
       <c r="G74">
         <v>1792.5</v>
@@ -7575,28 +7575,28 @@
         <v>3618.2</v>
       </c>
       <c r="M74">
-        <v>559.42596</v>
+        <v>567.1957650000001</v>
       </c>
       <c r="N74">
-        <v>3058.77404</v>
+        <v>3051.004235</v>
       </c>
       <c r="O74">
-        <v>672.9302888</v>
+        <v>671.2209316999999</v>
       </c>
       <c r="P74">
-        <v>2385.8437512</v>
+        <v>2379.7833033</v>
       </c>
       <c r="Q74">
-        <v>3331.6437512</v>
+        <v>3325.5833033</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.173893690339683</v>
+        <v>0.1782906537279801</v>
       </c>
       <c r="T74">
-        <v>2.958283841563118</v>
+        <v>3.059830340138109</v>
       </c>
       <c r="U74">
         <v>0.05350000000000001</v>
@@ -7613,7 +7613,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>6.467701284366567</v>
+        <v>6.379102636635518</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7621,22 +7621,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07860137650655463</v>
+        <v>0.07846691971799802</v>
       </c>
       <c r="C75">
-        <v>4469.420855980166</v>
+        <v>4334.70110096369</v>
       </c>
       <c r="D75">
-        <v>13278.71085598017</v>
+        <v>13289.22110096369</v>
       </c>
       <c r="E75">
-        <v>7012.189999999999</v>
+        <v>7157.42</v>
       </c>
       <c r="F75">
-        <v>10601.79</v>
+        <v>10747.02</v>
       </c>
       <c r="G75">
         <v>1792.5</v>
@@ -7657,28 +7657,28 @@
         <v>3618.2</v>
       </c>
       <c r="M75">
-        <v>567.1957650000001</v>
+        <v>574.9655700000001</v>
       </c>
       <c r="N75">
-        <v>3051.004235</v>
+        <v>3043.23443</v>
       </c>
       <c r="O75">
-        <v>671.2209316999999</v>
+        <v>669.5115745999999</v>
       </c>
       <c r="P75">
-        <v>2379.7833033</v>
+        <v>2373.722855399999</v>
       </c>
       <c r="Q75">
-        <v>3325.5833033</v>
+        <v>3319.5228554</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1782906537279801</v>
+        <v>0.1830258450692231</v>
       </c>
       <c r="T75">
-        <v>3.059830340138109</v>
+        <v>3.169188107834253</v>
       </c>
       <c r="U75">
         <v>0.05350000000000001</v>
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>6.379102636635518</v>
+        <v>6.292898546951253</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7703,22 +7703,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07846691971799802</v>
+        <v>0.0783324629294414</v>
       </c>
       <c r="C76">
-        <v>4334.70110096369</v>
+        <v>4199.997997074655</v>
       </c>
       <c r="D76">
-        <v>13289.22110096369</v>
+        <v>13299.74799707466</v>
       </c>
       <c r="E76">
-        <v>7157.42</v>
+        <v>7302.65</v>
       </c>
       <c r="F76">
-        <v>10747.02</v>
+        <v>10892.25</v>
       </c>
       <c r="G76">
         <v>1792.5</v>
@@ -7739,28 +7739,28 @@
         <v>3618.2</v>
       </c>
       <c r="M76">
-        <v>574.9655700000001</v>
+        <v>582.7353750000001</v>
       </c>
       <c r="N76">
-        <v>3043.23443</v>
+        <v>3035.464625</v>
       </c>
       <c r="O76">
-        <v>669.5115745999999</v>
+        <v>667.8022174999999</v>
       </c>
       <c r="P76">
-        <v>2373.722855399999</v>
+        <v>2367.6624075</v>
       </c>
       <c r="Q76">
-        <v>3319.5228554</v>
+        <v>3313.4624075</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1830258450692231</v>
+        <v>0.1881398517177656</v>
       </c>
       <c r="T76">
-        <v>3.169188107834253</v>
+        <v>3.287294496946088</v>
       </c>
       <c r="U76">
         <v>0.05350000000000001</v>
@@ -7777,7 +7777,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>6.292898546951253</v>
+        <v>6.208993232991904</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7785,22 +7785,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.0783324629294414</v>
+        <v>0.07819800614088479</v>
       </c>
       <c r="C77">
-        <v>4199.997997074655</v>
+        <v>4065.31158391439</v>
       </c>
       <c r="D77">
-        <v>13299.74799707466</v>
+        <v>13310.29158391439</v>
       </c>
       <c r="E77">
-        <v>7302.65</v>
+        <v>7447.879999999999</v>
       </c>
       <c r="F77">
-        <v>10892.25</v>
+        <v>11037.48</v>
       </c>
       <c r="G77">
         <v>1792.5</v>
@@ -7821,28 +7821,28 @@
         <v>3618.2</v>
       </c>
       <c r="M77">
-        <v>582.7353750000001</v>
+        <v>590.50518</v>
       </c>
       <c r="N77">
-        <v>3035.464625</v>
+        <v>3027.69482</v>
       </c>
       <c r="O77">
-        <v>667.8022174999999</v>
+        <v>666.0928603999999</v>
       </c>
       <c r="P77">
-        <v>2367.6624075</v>
+        <v>2361.6019596</v>
       </c>
       <c r="Q77">
-        <v>3313.4624075</v>
+        <v>3307.4019596</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1881398517177656</v>
+        <v>0.19368002558702</v>
       </c>
       <c r="T77">
-        <v>3.287294496946088</v>
+        <v>3.415243085150577</v>
       </c>
       <c r="U77">
         <v>0.05350000000000001</v>
@@ -7859,7 +7859,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>6.208993232991904</v>
+        <v>6.127295953610432</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7867,22 +7867,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07819800614088479</v>
+        <v>0.07806354935232818</v>
       </c>
       <c r="C78">
-        <v>4065.31158391439</v>
+        <v>3930.64190120992</v>
       </c>
       <c r="D78">
-        <v>13310.29158391439</v>
+        <v>13320.85190120992</v>
       </c>
       <c r="E78">
-        <v>7447.879999999999</v>
+        <v>7593.110000000001</v>
       </c>
       <c r="F78">
-        <v>11037.48</v>
+        <v>11182.71</v>
       </c>
       <c r="G78">
         <v>1792.5</v>
@@ -7903,28 +7903,28 @@
         <v>3618.2</v>
       </c>
       <c r="M78">
-        <v>590.50518</v>
+        <v>598.2749850000001</v>
       </c>
       <c r="N78">
-        <v>3027.69482</v>
+        <v>3019.925015</v>
       </c>
       <c r="O78">
-        <v>666.0928603999999</v>
+        <v>664.3835032999999</v>
       </c>
       <c r="P78">
-        <v>2361.6019596</v>
+        <v>2355.5415117</v>
       </c>
       <c r="Q78">
-        <v>3307.4019596</v>
+        <v>3301.3415117</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.19368002558702</v>
+        <v>0.1997019537057747</v>
       </c>
       <c r="T78">
-        <v>3.415243085150577</v>
+        <v>3.55431763754676</v>
       </c>
       <c r="U78">
         <v>0.05350000000000001</v>
@@ -7941,7 +7941,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>6.127295953610432</v>
+        <v>6.04772068148562</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7949,22 +7949,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07806354935232818</v>
+        <v>0.07792909256377158</v>
       </c>
       <c r="C79">
-        <v>3930.64190120992</v>
+        <v>3795.988988814433</v>
       </c>
       <c r="D79">
-        <v>13320.85190120992</v>
+        <v>13331.42898881443</v>
       </c>
       <c r="E79">
-        <v>7593.110000000001</v>
+        <v>7738.34</v>
       </c>
       <c r="F79">
-        <v>11182.71</v>
+        <v>11327.94</v>
       </c>
       <c r="G79">
         <v>1792.5</v>
@@ -7985,28 +7985,28 @@
         <v>3618.2</v>
       </c>
       <c r="M79">
-        <v>598.2749850000001</v>
+        <v>606.0447900000001</v>
       </c>
       <c r="N79">
-        <v>3019.925015</v>
+        <v>3012.15521</v>
       </c>
       <c r="O79">
-        <v>664.3835032999999</v>
+        <v>662.6741462</v>
       </c>
       <c r="P79">
-        <v>2355.5415117</v>
+        <v>2349.4810638</v>
       </c>
       <c r="Q79">
-        <v>3301.3415117</v>
+        <v>3295.2810638</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1997019537057747</v>
+        <v>0.2062713298353253</v>
       </c>
       <c r="T79">
-        <v>3.55431763754676</v>
+        <v>3.706035331069869</v>
       </c>
       <c r="U79">
         <v>0.05350000000000001</v>
@@ -8023,7 +8023,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>6.04772068148562</v>
+        <v>5.970185800953753</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8031,22 +8031,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07792909256377158</v>
+        <v>0.07779463577521496</v>
       </c>
       <c r="C80">
-        <v>3795.988988814433</v>
+        <v>3661.352886707806</v>
       </c>
       <c r="D80">
-        <v>13331.42898881443</v>
+        <v>13342.02288670781</v>
       </c>
       <c r="E80">
-        <v>7738.34</v>
+        <v>7883.57</v>
       </c>
       <c r="F80">
-        <v>11327.94</v>
+        <v>11473.17</v>
       </c>
       <c r="G80">
         <v>1792.5</v>
@@ -8067,28 +8067,28 @@
         <v>3618.2</v>
       </c>
       <c r="M80">
-        <v>606.0447900000001</v>
+        <v>613.8145950000001</v>
       </c>
       <c r="N80">
-        <v>3012.15521</v>
+        <v>3004.385405</v>
       </c>
       <c r="O80">
-        <v>662.6741462</v>
+        <v>660.9647891</v>
       </c>
       <c r="P80">
-        <v>2349.4810638</v>
+        <v>2343.4206159</v>
       </c>
       <c r="Q80">
-        <v>3295.2810638</v>
+        <v>3289.2206159</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2062713298353253</v>
+        <v>0.213466360834357</v>
       </c>
       <c r="T80">
-        <v>3.706035331069869</v>
+        <v>3.872202328738036</v>
       </c>
       <c r="U80">
         <v>0.05350000000000001</v>
@@ -8105,7 +8105,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>5.970185800953753</v>
+        <v>5.894613828789782</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8113,22 +8113,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07779463577521496</v>
+        <v>0.07766017898665833</v>
       </c>
       <c r="C81">
-        <v>3661.352886707806</v>
+        <v>3526.73363499709</v>
       </c>
       <c r="D81">
-        <v>13342.02288670781</v>
+        <v>13352.63363499709</v>
       </c>
       <c r="E81">
-        <v>7883.57</v>
+        <v>8028.800000000001</v>
       </c>
       <c r="F81">
-        <v>11473.17</v>
+        <v>11618.4</v>
       </c>
       <c r="G81">
         <v>1792.5</v>
@@ -8149,28 +8149,28 @@
         <v>3618.2</v>
       </c>
       <c r="M81">
-        <v>613.8145950000001</v>
+        <v>621.5844000000002</v>
       </c>
       <c r="N81">
-        <v>3004.385405</v>
+        <v>2996.6156</v>
       </c>
       <c r="O81">
-        <v>660.9647891</v>
+        <v>659.2554319999999</v>
       </c>
       <c r="P81">
-        <v>2343.4206159</v>
+        <v>2337.360168</v>
       </c>
       <c r="Q81">
-        <v>3289.2206159</v>
+        <v>3283.160167999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.213466360834357</v>
+        <v>0.2213808949332917</v>
       </c>
       <c r="T81">
-        <v>3.872202328738036</v>
+        <v>4.05498602617302</v>
       </c>
       <c r="U81">
         <v>0.05350000000000001</v>
@@ -8187,7 +8187,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>5.894613828789782</v>
+        <v>5.820931155929909</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8195,22 +8195,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.07766017898665833</v>
+        <v>0.07752572219810173</v>
       </c>
       <c r="C82">
-        <v>3526.73363499709</v>
+        <v>3392.131273917024</v>
       </c>
       <c r="D82">
-        <v>13352.63363499709</v>
+        <v>13363.26127391703</v>
       </c>
       <c r="E82">
-        <v>8028.800000000001</v>
+        <v>8174.030000000001</v>
       </c>
       <c r="F82">
-        <v>11618.4</v>
+        <v>11763.63</v>
       </c>
       <c r="G82">
         <v>1792.5</v>
@@ -8231,28 +8231,28 @@
         <v>3618.2</v>
       </c>
       <c r="M82">
-        <v>621.5844000000002</v>
+        <v>629.3542050000001</v>
       </c>
       <c r="N82">
-        <v>2996.6156</v>
+        <v>2988.845795</v>
       </c>
       <c r="O82">
-        <v>659.2554319999999</v>
+        <v>657.5460748999999</v>
       </c>
       <c r="P82">
-        <v>2337.360168</v>
+        <v>2331.2997201</v>
       </c>
       <c r="Q82">
-        <v>3283.160167999999</v>
+        <v>3277.0997201</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2213808949332917</v>
+        <v>0.230128537884746</v>
       </c>
       <c r="T82">
-        <v>4.05498602617302</v>
+        <v>4.257010112811686</v>
       </c>
       <c r="U82">
         <v>0.05350000000000001</v>
@@ -8269,7 +8269,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>5.820931155929909</v>
+        <v>5.749067808325837</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8277,22 +8277,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07752572219810173</v>
+        <v>0.07739126540954511</v>
       </c>
       <c r="C83">
-        <v>3392.131273917024</v>
+        <v>3257.545843830556</v>
       </c>
       <c r="D83">
-        <v>13363.26127391703</v>
+        <v>13373.90584383056</v>
       </c>
       <c r="E83">
-        <v>8174.030000000001</v>
+        <v>8319.26</v>
       </c>
       <c r="F83">
-        <v>11763.63</v>
+        <v>11908.86</v>
       </c>
       <c r="G83">
         <v>1792.5</v>
@@ -8313,28 +8313,28 @@
         <v>3618.2</v>
       </c>
       <c r="M83">
-        <v>629.3542050000001</v>
+        <v>637.1240100000001</v>
       </c>
       <c r="N83">
-        <v>2988.845795</v>
+        <v>2981.07599</v>
       </c>
       <c r="O83">
-        <v>657.5460748999999</v>
+        <v>655.8367178</v>
       </c>
       <c r="P83">
-        <v>2331.2997201</v>
+        <v>2325.2392722</v>
       </c>
       <c r="Q83">
-        <v>3277.0997201</v>
+        <v>3271.0392722</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.230128537884746</v>
+        <v>0.2398481411641396</v>
       </c>
       <c r="T83">
-        <v>4.257010112811686</v>
+        <v>4.481481320187982</v>
       </c>
       <c r="U83">
         <v>0.05350000000000001</v>
@@ -8351,7 +8351,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>5.749067808325837</v>
+        <v>5.678957225297473</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8359,22 +8359,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07739126540954511</v>
+        <v>0.07725680862098849</v>
       </c>
       <c r="C84">
-        <v>3257.545843830556</v>
+        <v>3122.977385229322</v>
       </c>
       <c r="D84">
-        <v>13373.90584383056</v>
+        <v>13384.56738522932</v>
       </c>
       <c r="E84">
-        <v>8319.26</v>
+        <v>8464.49</v>
       </c>
       <c r="F84">
-        <v>11908.86</v>
+        <v>12054.09</v>
       </c>
       <c r="G84">
         <v>1792.5</v>
@@ -8395,28 +8395,28 @@
         <v>3618.2</v>
       </c>
       <c r="M84">
-        <v>637.1240100000001</v>
+        <v>644.8938150000001</v>
       </c>
       <c r="N84">
-        <v>2981.07599</v>
+        <v>2973.306184999999</v>
       </c>
       <c r="O84">
-        <v>655.8367178</v>
+        <v>654.1273606999999</v>
       </c>
       <c r="P84">
-        <v>2325.2392722</v>
+        <v>2319.1788243</v>
       </c>
       <c r="Q84">
-        <v>3271.0392722</v>
+        <v>3264.978824299999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2398481411641396</v>
+        <v>0.2507112271822854</v>
       </c>
       <c r="T84">
-        <v>4.481481320187982</v>
+        <v>4.732360904902666</v>
       </c>
       <c r="U84">
         <v>0.05350000000000001</v>
@@ -8433,7 +8433,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>5.678957225297473</v>
+        <v>5.610536053908346</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8441,22 +8441,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07725680862098849</v>
+        <v>0.0776465118324319</v>
       </c>
       <c r="C85">
-        <v>3122.977385229322</v>
+        <v>2946.893132729598</v>
       </c>
       <c r="D85">
-        <v>13384.56738522932</v>
+        <v>13353.7131327296</v>
       </c>
       <c r="E85">
-        <v>8464.49</v>
+        <v>8609.720000000001</v>
       </c>
       <c r="F85">
-        <v>12054.09</v>
+        <v>12199.32</v>
       </c>
       <c r="G85">
         <v>1792.5</v>
@@ -8477,45 +8477,45 @@
         <v>3618.2</v>
       </c>
       <c r="M85">
-        <v>644.8938150000001</v>
+        <v>662.4230760000002</v>
       </c>
       <c r="N85">
-        <v>2973.306184999999</v>
+        <v>2955.776924</v>
       </c>
       <c r="O85">
-        <v>654.1273606999999</v>
+        <v>650.2709232799999</v>
       </c>
       <c r="P85">
-        <v>2319.1788243</v>
+        <v>2305.50600072</v>
       </c>
       <c r="Q85">
-        <v>3264.978824299999</v>
+        <v>3251.30600072</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2507112271822854</v>
+        <v>0.2629321989526995</v>
       </c>
       <c r="T85">
-        <v>4.732360904902666</v>
+        <v>5.014600437706686</v>
       </c>
       <c r="U85">
-        <v>0.05350000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V85">
         <v>0.22</v>
       </c>
       <c r="W85">
-        <v>0.04173</v>
+        <v>0.04235400000000001</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y85">
-        <v>5.610536053908346</v>
+        <v>5.462068172274843</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8523,22 +8523,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.0776465118324319</v>
+        <v>0.07751829504387531</v>
       </c>
       <c r="C86">
-        <v>2946.8931327296</v>
+        <v>2811.798818896388</v>
       </c>
       <c r="D86">
-        <v>13353.7131327296</v>
+        <v>13363.84881889639</v>
       </c>
       <c r="E86">
-        <v>8609.719999999999</v>
+        <v>8754.949999999999</v>
       </c>
       <c r="F86">
-        <v>12199.32</v>
+        <v>12344.55</v>
       </c>
       <c r="G86">
         <v>1792.5</v>
@@ -8559,28 +8559,28 @@
         <v>3618.2</v>
       </c>
       <c r="M86">
-        <v>662.423076</v>
+        <v>670.309065</v>
       </c>
       <c r="N86">
-        <v>2955.776924</v>
+        <v>2947.890935</v>
       </c>
       <c r="O86">
-        <v>650.2709232799999</v>
+        <v>648.5360057</v>
       </c>
       <c r="P86">
-        <v>2305.50600072</v>
+        <v>2299.3549293</v>
       </c>
       <c r="Q86">
-        <v>3251.30600072</v>
+        <v>3245.1549293</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2629321989526993</v>
+        <v>0.2767826336258352</v>
       </c>
       <c r="T86">
-        <v>5.014600437706682</v>
+        <v>5.334471908217903</v>
       </c>
       <c r="U86">
         <v>0.05430000000000001</v>
@@ -8597,7 +8597,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>5.462068172274844</v>
+        <v>5.397808546718669</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8605,22 +8605,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.07751829504387531</v>
+        <v>0.07739007825531868</v>
       </c>
       <c r="C87">
-        <v>2811.798818896388</v>
+        <v>2676.719903052879</v>
       </c>
       <c r="D87">
-        <v>13363.84881889639</v>
+        <v>13373.99990305288</v>
       </c>
       <c r="E87">
-        <v>8754.949999999999</v>
+        <v>8900.18</v>
       </c>
       <c r="F87">
-        <v>12344.55</v>
+        <v>12489.78</v>
       </c>
       <c r="G87">
         <v>1792.5</v>
@@ -8641,28 +8641,28 @@
         <v>3618.2</v>
       </c>
       <c r="M87">
-        <v>670.309065</v>
+        <v>678.1950540000001</v>
       </c>
       <c r="N87">
-        <v>2947.890935</v>
+        <v>2940.004946</v>
       </c>
       <c r="O87">
-        <v>648.5360057</v>
+        <v>646.8010881199999</v>
       </c>
       <c r="P87">
-        <v>2299.3549293</v>
+        <v>2293.20385788</v>
       </c>
       <c r="Q87">
-        <v>3245.1549293</v>
+        <v>3239.003857879999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2767826336258352</v>
+        <v>0.2926117018237048</v>
       </c>
       <c r="T87">
-        <v>5.334471908217903</v>
+        <v>5.700039303087871</v>
       </c>
       <c r="U87">
         <v>0.05430000000000001</v>
@@ -8679,7 +8679,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>5.397808546718669</v>
+        <v>5.335043331059148</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8687,22 +8687,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.07739007825531868</v>
+        <v>0.07726186146676207</v>
       </c>
       <c r="C88">
-        <v>2676.719903052879</v>
+        <v>2541.656420314357</v>
       </c>
       <c r="D88">
-        <v>13373.99990305288</v>
+        <v>13384.16642031436</v>
       </c>
       <c r="E88">
-        <v>8900.18</v>
+        <v>9045.41</v>
       </c>
       <c r="F88">
-        <v>12489.78</v>
+        <v>12635.01</v>
       </c>
       <c r="G88">
         <v>1792.5</v>
@@ -8723,28 +8723,28 @@
         <v>3618.2</v>
       </c>
       <c r="M88">
-        <v>678.1950540000001</v>
+        <v>686.0810430000001</v>
       </c>
       <c r="N88">
-        <v>2940.004946</v>
+        <v>2932.118957</v>
       </c>
       <c r="O88">
-        <v>646.8010881199999</v>
+        <v>645.0661705399999</v>
       </c>
       <c r="P88">
-        <v>2293.20385788</v>
+        <v>2287.05278646</v>
       </c>
       <c r="Q88">
-        <v>3239.003857879999</v>
+        <v>3232.85278646</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2926117018237048</v>
+        <v>0.3108760112827851</v>
       </c>
       <c r="T88">
-        <v>5.700039303087871</v>
+        <v>6.12184783563014</v>
       </c>
       <c r="U88">
         <v>0.05430000000000001</v>
@@ -8761,7 +8761,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>5.335043331059148</v>
+        <v>5.273720993920538</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8769,22 +8769,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.07726186146676207</v>
+        <v>0.07713364467820547</v>
       </c>
       <c r="C89">
-        <v>2541.656420314357</v>
+        <v>2406.608405902962</v>
       </c>
       <c r="D89">
-        <v>13384.16642031436</v>
+        <v>13394.34840590296</v>
       </c>
       <c r="E89">
-        <v>9045.41</v>
+        <v>9190.639999999999</v>
       </c>
       <c r="F89">
-        <v>12635.01</v>
+        <v>12780.24</v>
       </c>
       <c r="G89">
         <v>1792.5</v>
@@ -8805,28 +8805,28 @@
         <v>3618.2</v>
       </c>
       <c r="M89">
-        <v>686.0810430000001</v>
+        <v>693.9670320000001</v>
       </c>
       <c r="N89">
-        <v>2932.118957</v>
+        <v>2924.232968</v>
       </c>
       <c r="O89">
-        <v>645.0661705399999</v>
+        <v>643.3312529599999</v>
       </c>
       <c r="P89">
-        <v>2287.05278646</v>
+        <v>2280.90171504</v>
       </c>
       <c r="Q89">
-        <v>3232.85278646</v>
+        <v>3226.70171504</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3108760112827851</v>
+        <v>0.3321843723183788</v>
       </c>
       <c r="T89">
-        <v>6.12184783563014</v>
+        <v>6.61395779026279</v>
       </c>
       <c r="U89">
         <v>0.05430000000000001</v>
@@ -8843,7 +8843,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>5.273720993920538</v>
+        <v>5.21379234626235</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8851,22 +8851,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.07713364467820547</v>
+        <v>0.07700542788964884</v>
       </c>
       <c r="C90">
-        <v>2406.608405902962</v>
+        <v>2271.575895148091</v>
       </c>
       <c r="D90">
-        <v>13394.34840590296</v>
+        <v>13404.54589514809</v>
       </c>
       <c r="E90">
-        <v>9190.639999999999</v>
+        <v>9335.869999999999</v>
       </c>
       <c r="F90">
-        <v>12780.24</v>
+        <v>12925.47</v>
       </c>
       <c r="G90">
         <v>1792.5</v>
@@ -8887,28 +8887,28 @@
         <v>3618.2</v>
       </c>
       <c r="M90">
-        <v>693.9670320000001</v>
+        <v>701.853021</v>
       </c>
       <c r="N90">
-        <v>2924.232968</v>
+        <v>2916.346979</v>
       </c>
       <c r="O90">
-        <v>643.3312529599999</v>
+        <v>641.59633538</v>
       </c>
       <c r="P90">
-        <v>2280.90171504</v>
+        <v>2274.75064362</v>
       </c>
       <c r="Q90">
-        <v>3226.70171504</v>
+        <v>3220.55064362</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3321843723183788</v>
+        <v>0.3573669808149895</v>
       </c>
       <c r="T90">
-        <v>6.61395779026279</v>
+        <v>7.195542282101373</v>
       </c>
       <c r="U90">
         <v>0.05430000000000001</v>
@@ -8925,7 +8925,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>5.21379234626235</v>
+        <v>5.155210409787493</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8933,22 +8933,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.07700542788964884</v>
+        <v>0.07687721110109223</v>
       </c>
       <c r="C91">
-        <v>2271.575895148091</v>
+        <v>2136.558923486817</v>
       </c>
       <c r="D91">
-        <v>13404.54589514809</v>
+        <v>13414.75892348682</v>
       </c>
       <c r="E91">
-        <v>9335.869999999999</v>
+        <v>9481.1</v>
       </c>
       <c r="F91">
-        <v>12925.47</v>
+        <v>13070.7</v>
       </c>
       <c r="G91">
         <v>1792.5</v>
@@ -8969,28 +8969,28 @@
         <v>3618.2</v>
       </c>
       <c r="M91">
-        <v>701.853021</v>
+        <v>709.7390100000001</v>
       </c>
       <c r="N91">
-        <v>2916.346979</v>
+        <v>2908.46099</v>
       </c>
       <c r="O91">
-        <v>641.59633538</v>
+        <v>639.8614177999999</v>
       </c>
       <c r="P91">
-        <v>2274.75064362</v>
+        <v>2268.5995722</v>
       </c>
       <c r="Q91">
-        <v>3220.55064362</v>
+        <v>3214.3995722</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3573669808149895</v>
+        <v>0.3875861110109223</v>
       </c>
       <c r="T91">
-        <v>7.195542282101373</v>
+        <v>7.893443672307675</v>
       </c>
       <c r="U91">
         <v>0.05430000000000001</v>
@@ -9007,7 +9007,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>5.155210409787493</v>
+        <v>5.097930294123186</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9015,22 +9015,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.07687721110109223</v>
+        <v>0.07674899431253562</v>
       </c>
       <c r="C92">
-        <v>2136.558923486817</v>
+        <v>2001.557526464294</v>
       </c>
       <c r="D92">
-        <v>13414.75892348682</v>
+        <v>13424.98752646429</v>
       </c>
       <c r="E92">
-        <v>9481.1</v>
+        <v>9626.33</v>
       </c>
       <c r="F92">
-        <v>13070.7</v>
+        <v>13215.93</v>
       </c>
       <c r="G92">
         <v>1792.5</v>
@@ -9051,28 +9051,28 @@
         <v>3618.2</v>
       </c>
       <c r="M92">
-        <v>709.7390100000001</v>
+        <v>717.6249990000001</v>
       </c>
       <c r="N92">
-        <v>2908.46099</v>
+        <v>2900.575001</v>
       </c>
       <c r="O92">
-        <v>639.8614177999999</v>
+        <v>638.1265002199999</v>
       </c>
       <c r="P92">
-        <v>2268.5995722</v>
+        <v>2262.44850078</v>
       </c>
       <c r="Q92">
-        <v>3214.3995722</v>
+        <v>3208.24850078</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3875861110109223</v>
+        <v>0.4245206034726181</v>
       </c>
       <c r="T92">
-        <v>7.893443672307675</v>
+        <v>8.746434260337599</v>
       </c>
       <c r="U92">
         <v>0.05430000000000001</v>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>5.097930294123186</v>
+        <v>5.041909082099854</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9097,22 +9097,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.07674899431253562</v>
+        <v>0.076620777523979</v>
       </c>
       <c r="C93">
-        <v>2001.557526464294</v>
+        <v>1866.571739734167</v>
       </c>
       <c r="D93">
-        <v>13424.98752646429</v>
+        <v>13435.23173973417</v>
       </c>
       <c r="E93">
-        <v>9626.33</v>
+        <v>9771.559999999999</v>
       </c>
       <c r="F93">
-        <v>13215.93</v>
+        <v>13361.16</v>
       </c>
       <c r="G93">
         <v>1792.5</v>
@@ -9133,28 +9133,28 @@
         <v>3618.2</v>
       </c>
       <c r="M93">
-        <v>717.6249990000001</v>
+        <v>725.5109880000001</v>
       </c>
       <c r="N93">
-        <v>2900.575001</v>
+        <v>2892.689012</v>
       </c>
       <c r="O93">
-        <v>638.1265002199999</v>
+        <v>636.3915826399999</v>
       </c>
       <c r="P93">
-        <v>2262.44850078</v>
+        <v>2256.29742936</v>
       </c>
       <c r="Q93">
-        <v>3208.24850078</v>
+        <v>3202.09742936</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4245206034726181</v>
+        <v>0.4706887190497377</v>
       </c>
       <c r="T93">
-        <v>8.746434260337599</v>
+        <v>9.812672495375006</v>
       </c>
       <c r="U93">
         <v>0.05430000000000001</v>
@@ -9171,7 +9171,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>5.041909082099854</v>
+        <v>4.987105722511814</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9179,22 +9179,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.076620777523979</v>
+        <v>0.07649256073542239</v>
       </c>
       <c r="C94">
-        <v>1866.571739734167</v>
+        <v>1731.601599058989</v>
       </c>
       <c r="D94">
-        <v>13435.23173973417</v>
+        <v>13445.49159905899</v>
       </c>
       <c r="E94">
-        <v>9771.559999999999</v>
+        <v>9916.790000000001</v>
       </c>
       <c r="F94">
-        <v>13361.16</v>
+        <v>13506.39</v>
       </c>
       <c r="G94">
         <v>1792.5</v>
@@ -9215,28 +9215,28 @@
         <v>3618.2</v>
       </c>
       <c r="M94">
-        <v>725.5109880000001</v>
+        <v>733.3969770000002</v>
       </c>
       <c r="N94">
-        <v>2892.689012</v>
+        <v>2884.803022999999</v>
       </c>
       <c r="O94">
-        <v>636.3915826399999</v>
+        <v>634.6566650599999</v>
       </c>
       <c r="P94">
-        <v>2256.29742936</v>
+        <v>2250.14635794</v>
       </c>
       <c r="Q94">
-        <v>3202.09742936</v>
+        <v>3195.94635794</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4706887190497377</v>
+        <v>0.5300477247917487</v>
       </c>
       <c r="T94">
-        <v>9.812672495375006</v>
+        <v>11.18355022613738</v>
       </c>
       <c r="U94">
         <v>0.05430000000000001</v>
@@ -9253,7 +9253,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>4.987105722511814</v>
+        <v>4.933480929796631</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9261,22 +9261,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.07649256073542239</v>
+        <v>0.07636434394686578</v>
       </c>
       <c r="C95">
-        <v>1731.601599058989</v>
+        <v>1596.647140310644</v>
       </c>
       <c r="D95">
-        <v>13445.49159905899</v>
+        <v>13455.76714031065</v>
       </c>
       <c r="E95">
-        <v>9916.790000000001</v>
+        <v>10062.02</v>
       </c>
       <c r="F95">
-        <v>13506.39</v>
+        <v>13651.62</v>
       </c>
       <c r="G95">
         <v>1792.5</v>
@@ -9297,28 +9297,28 @@
         <v>3618.2</v>
       </c>
       <c r="M95">
-        <v>733.3969770000002</v>
+        <v>741.2829660000001</v>
       </c>
       <c r="N95">
-        <v>2884.803022999999</v>
+        <v>2876.917034</v>
       </c>
       <c r="O95">
-        <v>634.6566650599999</v>
+        <v>632.9217474799999</v>
       </c>
       <c r="P95">
-        <v>2250.14635794</v>
+        <v>2243.99528652</v>
       </c>
       <c r="Q95">
-        <v>3195.94635794</v>
+        <v>3189.79528652</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5300477247917487</v>
+        <v>0.6091930657810968</v>
       </c>
       <c r="T95">
-        <v>11.18355022613738</v>
+        <v>13.01138720048722</v>
       </c>
       <c r="U95">
         <v>0.05430000000000001</v>
@@ -9335,7 +9335,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>4.933480929796631</v>
+        <v>4.880997090117944</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9343,22 +9343,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.07636434394686578</v>
+        <v>0.07623612715830917</v>
       </c>
       <c r="C96">
-        <v>1596.647140310644</v>
+        <v>1461.708399470752</v>
       </c>
       <c r="D96">
-        <v>13455.76714031065</v>
+        <v>13466.05839947075</v>
       </c>
       <c r="E96">
-        <v>10062.02</v>
+        <v>10207.25</v>
       </c>
       <c r="F96">
-        <v>13651.62</v>
+        <v>13796.85</v>
       </c>
       <c r="G96">
         <v>1792.5</v>
@@ -9379,28 +9379,28 @@
         <v>3618.2</v>
       </c>
       <c r="M96">
-        <v>741.2829660000001</v>
+        <v>749.1689550000001</v>
       </c>
       <c r="N96">
-        <v>2876.917034</v>
+        <v>2869.031045</v>
       </c>
       <c r="O96">
-        <v>632.9217474799999</v>
+        <v>631.1868298999999</v>
       </c>
       <c r="P96">
-        <v>2243.99528652</v>
+        <v>2237.8442151</v>
       </c>
       <c r="Q96">
-        <v>3189.79528652</v>
+        <v>3183.6442151</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6091930657810968</v>
+        <v>0.7199965431661842</v>
       </c>
       <c r="T96">
-        <v>13.01138720048722</v>
+        <v>15.570358964577</v>
       </c>
       <c r="U96">
         <v>0.05430000000000001</v>
@@ -9417,7 +9417,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>4.880997090117944</v>
+        <v>4.829618173379862</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9425,22 +9425,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.07623612715830917</v>
+        <v>0.07610791036975256</v>
       </c>
       <c r="C97">
-        <v>1461.708399470752</v>
+        <v>1326.78541263109</v>
       </c>
       <c r="D97">
-        <v>13466.05839947075</v>
+        <v>13476.36541263109</v>
       </c>
       <c r="E97">
-        <v>10207.25</v>
+        <v>10352.48</v>
       </c>
       <c r="F97">
-        <v>13796.85</v>
+        <v>13942.08</v>
       </c>
       <c r="G97">
         <v>1792.5</v>
@@ -9461,28 +9461,28 @@
         <v>3618.2</v>
       </c>
       <c r="M97">
-        <v>749.1689550000001</v>
+        <v>757.0549440000002</v>
       </c>
       <c r="N97">
-        <v>2869.031045</v>
+        <v>2861.145055999999</v>
       </c>
       <c r="O97">
-        <v>631.1868298999999</v>
+        <v>629.4519123199999</v>
       </c>
       <c r="P97">
-        <v>2237.8442151</v>
+        <v>2231.69314368</v>
       </c>
       <c r="Q97">
-        <v>3183.6442151</v>
+        <v>3177.49314368</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7199965431661842</v>
+        <v>0.8862017592438153</v>
       </c>
       <c r="T97">
-        <v>15.570358964577</v>
+        <v>19.40881661071167</v>
       </c>
       <c r="U97">
         <v>0.05430000000000001</v>
@@ -9499,7 +9499,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>4.829618173379862</v>
+        <v>4.779309650740487</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9507,22 +9507,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.07610791036975256</v>
+        <v>0.07597969358119597</v>
       </c>
       <c r="C98">
-        <v>1326.785412631092</v>
+        <v>1191.87821599404</v>
       </c>
       <c r="D98">
-        <v>13476.36541263109</v>
+        <v>13486.68821599404</v>
       </c>
       <c r="E98">
-        <v>10352.48</v>
+        <v>10497.71</v>
       </c>
       <c r="F98">
-        <v>13942.08</v>
+        <v>14087.31</v>
       </c>
       <c r="G98">
         <v>1792.5</v>
@@ -9543,28 +9543,28 @@
         <v>3618.2</v>
       </c>
       <c r="M98">
-        <v>757.0549440000001</v>
+        <v>764.9409330000001</v>
       </c>
       <c r="N98">
-        <v>2861.145056</v>
+        <v>2853.259067</v>
       </c>
       <c r="O98">
-        <v>629.45191232</v>
+        <v>627.71699474</v>
       </c>
       <c r="P98">
-        <v>2231.69314368</v>
+        <v>2225.54207226</v>
       </c>
       <c r="Q98">
-        <v>3177.49314368</v>
+        <v>3171.34207226</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8862017592438132</v>
+        <v>1.163210452706531</v>
       </c>
       <c r="T98">
-        <v>19.40881661071162</v>
+        <v>25.80624602093604</v>
       </c>
       <c r="U98">
         <v>0.05430000000000001</v>
@@ -9581,7 +9581,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>4.779309650740488</v>
+        <v>4.7300384172277</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9589,22 +9589,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.07597969358119597</v>
+        <v>0.07585147679263934</v>
       </c>
       <c r="C99">
-        <v>1191.87821599404</v>
+        <v>1056.986845872965</v>
       </c>
       <c r="D99">
-        <v>13486.68821599404</v>
+        <v>13497.02684587296</v>
       </c>
       <c r="E99">
-        <v>10497.71</v>
+        <v>10642.94</v>
       </c>
       <c r="F99">
-        <v>14087.31</v>
+        <v>14232.54</v>
       </c>
       <c r="G99">
         <v>1792.5</v>
@@ -9625,28 +9625,28 @@
         <v>3618.2</v>
       </c>
       <c r="M99">
-        <v>764.9409330000001</v>
+        <v>772.8269220000001</v>
       </c>
       <c r="N99">
-        <v>2853.259067</v>
+        <v>2845.373078</v>
       </c>
       <c r="O99">
-        <v>627.71699474</v>
+        <v>625.9820771599999</v>
       </c>
       <c r="P99">
-        <v>2225.54207226</v>
+        <v>2219.39100084</v>
       </c>
       <c r="Q99">
-        <v>3171.34207226</v>
+        <v>3165.19100084</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.163210452706531</v>
+        <v>1.717227839631965</v>
       </c>
       <c r="T99">
-        <v>25.80624602093604</v>
+        <v>38.60110484138487</v>
       </c>
       <c r="U99">
         <v>0.05430000000000001</v>
@@ -9663,7 +9663,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>4.7300384172277</v>
+        <v>4.681772719092722</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9671,22 +9671,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.07585147679263934</v>
+        <v>0.07572326000408272</v>
       </c>
       <c r="C100">
-        <v>1056.986845872965</v>
+        <v>922.1113386926809</v>
       </c>
       <c r="D100">
-        <v>13497.02684587296</v>
+        <v>13507.38133869268</v>
       </c>
       <c r="E100">
-        <v>10642.94</v>
+        <v>10788.17</v>
       </c>
       <c r="F100">
-        <v>14232.54</v>
+        <v>14377.77</v>
       </c>
       <c r="G100">
         <v>1792.5</v>
@@ -9707,28 +9707,28 @@
         <v>3618.2</v>
       </c>
       <c r="M100">
-        <v>772.8269220000001</v>
+        <v>780.7129110000002</v>
       </c>
       <c r="N100">
-        <v>2845.373078</v>
+        <v>2837.487089</v>
       </c>
       <c r="O100">
-        <v>625.9820771599999</v>
+        <v>624.2471595799999</v>
       </c>
       <c r="P100">
-        <v>2219.39100084</v>
+        <v>2213.23992942</v>
       </c>
       <c r="Q100">
-        <v>3165.19100084</v>
+        <v>3159.03992942</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.717227839631965</v>
+        <v>3.379280000408269</v>
       </c>
       <c r="T100">
-        <v>38.60110484138487</v>
+        <v>76.98568130273139</v>
       </c>
       <c r="U100">
         <v>0.05430000000000001</v>
@@ -9745,91 +9745,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>4.681772719092722</v>
+        <v>4.634482085566534</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.07572326000408272</v>
-      </c>
-      <c r="C101">
-        <v>922.1113386926809</v>
-      </c>
-      <c r="D101">
-        <v>13507.38133869268</v>
-      </c>
-      <c r="E101">
-        <v>10788.17</v>
-      </c>
-      <c r="F101">
-        <v>14377.77</v>
-      </c>
-      <c r="G101">
-        <v>1792.5</v>
-      </c>
-      <c r="H101">
-        <v>10933.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>4564</v>
-      </c>
-      <c r="K101">
-        <v>945.8</v>
-      </c>
-      <c r="L101">
-        <v>3618.2</v>
-      </c>
-      <c r="M101">
-        <v>780.7129110000002</v>
-      </c>
-      <c r="N101">
-        <v>2837.487089</v>
-      </c>
-      <c r="O101">
-        <v>624.2471595799999</v>
-      </c>
-      <c r="P101">
-        <v>2213.23992942</v>
-      </c>
-      <c r="Q101">
-        <v>3159.03992942</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.379280000408269</v>
-      </c>
-      <c r="T101">
-        <v>76.98568130273139</v>
-      </c>
-      <c r="U101">
-        <v>0.05430000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.22</v>
-      </c>
-      <c r="W101">
-        <v>0.04235400000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A2/A</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>4.634482085566534</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
